--- a/test_cases/test_case.xlsx
+++ b/test_cases/test_case.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="自动化测试用例" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="操作类型说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="12">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -60,114 +60,36 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
+      <family val="3"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FF800080"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
       <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FF9C6500"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="0"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FF9C0006"/>
     </font>
     <font/>
   </fonts>
-  <fills count="38">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -206,192 +128,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39998"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -414,253 +156,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.49998"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -677,7 +177,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -687,74 +186,148 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.3999450666829432"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.3999450666829432"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.3999450666829432"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.3999450666829432"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.3999450666829432"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.3999450666829432"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.7999511703848384"/>
+          <bgColor theme="4" tint="0.7999511703848384"/>
         </patternFill>
       </fill>
     </dxf>
@@ -811,149 +384,32 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.3999450666829432"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -1237,6 +693,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1247,9 +704,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R123"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="25.8416666666667" customWidth="1" min="1" max="1"/>
+    <col width="25.81640625" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -1264,7 +721,7 @@
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="14.5" customWidth="1" min="17" max="17"/>
+    <col width="14.453125" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1360,7 +817,7 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>TC-LOGIN-001</t>
         </is>
@@ -1439,7 +896,7 @@
           <t>错误账号测试</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="Q2" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1531,7 +988,7 @@
           <t>错误密码测试</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="Q3" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1617,7 +1074,7 @@
           <t>必填校验</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q4" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1704,7 +1161,7 @@
       <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="Q5" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1792,7 +1249,7 @@
       <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="Q6" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1873,7 +1330,7 @@
       <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
+      <c r="Q7" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1966,7 +1423,7 @@
           <t>正常登录流程</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="inlineStr">
+      <c r="Q8" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2046,7 +1503,7 @@
       <c r="O9" t="n">
         <v>5</v>
       </c>
-      <c r="Q9" s="3" t="inlineStr">
+      <c r="Q9" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2132,7 +1589,7 @@
       <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="Q10" s="3" t="inlineStr">
+      <c r="Q10" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2143,85 +1600,85 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="28" customFormat="1" customHeight="1" s="4">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>TC-HOME-003</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>首页搜索</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>搜索-不存在的手机号</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>验证无结果提示</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>p1</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>已登录成功</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>1.在搜索框输入不存在的手机号
 2.点击搜索</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>input[placeholder='请输入关键字'], button:has-text('搜 索')</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>input,click</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>13626710399</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="J11" s="18" t="n">
+        <v>100000000000</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>展示：暂无内容</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>页面显示'暂无'</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
+      <c r="Q11" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -2274,7 +1731,7 @@
           <t>input,click</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t>t</t>
         </is>
@@ -2302,7 +1759,7 @@
       <c r="O12" t="n">
         <v>5</v>
       </c>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="Q12" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2388,7 +1845,7 @@
       <c r="O13" t="n">
         <v>5</v>
       </c>
-      <c r="Q13" s="3" t="inlineStr">
+      <c r="Q13" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2472,7 +1929,7 @@
       <c r="O14" t="n">
         <v>5</v>
       </c>
-      <c r="Q14" s="3" t="inlineStr">
+      <c r="Q14" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2556,7 +2013,7 @@
       <c r="O15" t="n">
         <v>5</v>
       </c>
-      <c r="Q15" s="3" t="inlineStr">
+      <c r="Q15" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2636,7 +2093,7 @@
       <c r="O16" t="n">
         <v>5</v>
       </c>
-      <c r="Q16" s="3" t="inlineStr">
+      <c r="Q16" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2716,7 +2173,7 @@
       <c r="O17" t="n">
         <v>5</v>
       </c>
-      <c r="Q17" s="3" t="inlineStr">
+      <c r="Q17" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2796,7 +2253,7 @@
       <c r="O18" t="n">
         <v>5</v>
       </c>
-      <c r="Q18" s="3" t="inlineStr">
+      <c r="Q18" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2876,7 +2333,7 @@
       <c r="O19" t="n">
         <v>5</v>
       </c>
-      <c r="Q19" s="3" t="inlineStr">
+      <c r="Q19" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2956,7 +2413,7 @@
       <c r="O20" t="n">
         <v>15</v>
       </c>
-      <c r="Q20" s="3" t="inlineStr">
+      <c r="Q20" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3037,7 +2494,7 @@
       <c r="O21" t="n">
         <v>10</v>
       </c>
-      <c r="Q21" s="3" t="inlineStr">
+      <c r="Q21" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3118,7 +2575,7 @@
       <c r="O22" t="n">
         <v>10</v>
       </c>
-      <c r="Q22" s="3" t="inlineStr">
+      <c r="Q22" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3199,7 +2656,7 @@
       <c r="O23" t="n">
         <v>10</v>
       </c>
-      <c r="Q23" s="3" t="inlineStr">
+      <c r="Q23" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3210,82 +2667,82 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="24" ht="28" customFormat="1" customHeight="1" s="4">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-004</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>顾客列表</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>搜索-不存在的手机号</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>验证无结果提示</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>1.在搜索框输入不存在的手机号
 2.点击搜索</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>/customer, 0.5, input[placeholder='请输入关键字'], button:has-text('搜 索')</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>nav, wait, input, click</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>|13626710399</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>|100000000000</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>展示：暂无内容</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>'暂无'</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O24" t="n">
+      <c r="O24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="Q24" s="3" t="inlineStr">
+      <c r="Q24" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R24" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -3361,7 +2818,7 @@
       <c r="O25" t="n">
         <v>10</v>
       </c>
-      <c r="Q25" s="3" t="inlineStr">
+      <c r="Q25" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3442,7 +2899,7 @@
       <c r="O26" t="n">
         <v>10</v>
       </c>
-      <c r="Q26" s="3" t="inlineStr">
+      <c r="Q26" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3523,7 +2980,7 @@
       <c r="O27" t="n">
         <v>5</v>
       </c>
-      <c r="Q27" s="3" t="inlineStr">
+      <c r="Q27" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3608,7 +3065,7 @@
       <c r="O28" t="n">
         <v>5</v>
       </c>
-      <c r="Q28" s="3" t="inlineStr">
+      <c r="Q28" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3689,7 +3146,7 @@
       <c r="O29" t="n">
         <v>5</v>
       </c>
-      <c r="Q29" s="3" t="inlineStr">
+      <c r="Q29" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3775,7 +3232,7 @@
       <c r="O30" t="n">
         <v>10</v>
       </c>
-      <c r="Q30" s="3" t="inlineStr">
+      <c r="Q30" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3861,7 +3318,7 @@
       <c r="O31" t="n">
         <v>10</v>
       </c>
-      <c r="Q31" s="3" t="inlineStr">
+      <c r="Q31" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3950,7 +3407,7 @@
       <c r="O32" t="n">
         <v>10</v>
       </c>
-      <c r="Q32" s="3" t="inlineStr">
+      <c r="Q32" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4039,7 +3496,7 @@
       <c r="O33" t="n">
         <v>10</v>
       </c>
-      <c r="Q33" s="3" t="inlineStr">
+      <c r="Q33" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4128,7 +3585,7 @@
       <c r="O34" t="n">
         <v>10</v>
       </c>
-      <c r="Q34" s="3" t="inlineStr">
+      <c r="Q34" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4217,7 +3674,7 @@
       <c r="O35" t="n">
         <v>10</v>
       </c>
-      <c r="Q35" s="3" t="inlineStr">
+      <c r="Q35" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4306,7 +3763,7 @@
       <c r="O36" t="n">
         <v>10</v>
       </c>
-      <c r="Q36" s="3" t="inlineStr">
+      <c r="Q36" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4395,7 +3852,7 @@
       <c r="O37" t="n">
         <v>10</v>
       </c>
-      <c r="Q37" s="3" t="inlineStr">
+      <c r="Q37" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4471,7 +3928,7 @@
           <t>展示符合时间范围的顾客档案</t>
         </is>
       </c>
-      <c r="M38" s="15" t="inlineStr">
+      <c r="M38" s="14" t="inlineStr">
         <is>
           <t>'详情'</t>
         </is>
@@ -4484,7 +3941,7 @@
       <c r="O38" t="n">
         <v>10</v>
       </c>
-      <c r="Q38" s="3" t="inlineStr">
+      <c r="Q38" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4562,7 +4019,7 @@
           <t>已根据实际DOM调整：删除'已为'步骤；确定按钮用.ant-popover .ant-btn-primary；备注图标用.ant-image + div .anticon</t>
         </is>
       </c>
-      <c r="Q39" s="3" t="inlineStr">
+      <c r="Q39" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4648,7 +4105,7 @@
           <t>卡片为自定义结构（非ant-list）；性别图标为图片形式无法文本断言；字段验证：姓名/年龄/手机号/上次检测时间/检测次数/详情</t>
         </is>
       </c>
-      <c r="Q40" s="3" t="inlineStr">
+      <c r="Q40" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4728,7 +4185,7 @@
       <c r="O41" t="n">
         <v>5</v>
       </c>
-      <c r="Q41" s="3" t="inlineStr">
+      <c r="Q41" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4810,7 +4267,7 @@
       <c r="O42" t="n">
         <v>10</v>
       </c>
-      <c r="Q42" s="3" t="inlineStr">
+      <c r="Q42" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4893,7 +4350,7 @@
       <c r="O43" t="n">
         <v>3</v>
       </c>
-      <c r="Q43" s="3" t="inlineStr">
+      <c r="Q43" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5071,7 +4528,7 @@
       <c r="O45" t="n">
         <v>10</v>
       </c>
-      <c r="Q45" s="3" t="inlineStr">
+      <c r="Q45" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5159,7 +4616,7 @@
       <c r="O46" t="n">
         <v>10</v>
       </c>
-      <c r="Q46" s="3" t="inlineStr">
+      <c r="Q46" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5247,7 +4704,7 @@
       <c r="O47" t="n">
         <v>10</v>
       </c>
-      <c r="Q47" s="3" t="inlineStr">
+      <c r="Q47" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5322,7 +4779,7 @@
           <t>保存成功，性别显示'保密'</t>
         </is>
       </c>
-      <c r="M48" s="15" t="inlineStr">
+      <c r="M48" s="14" t="inlineStr">
         <is>
           <t>'性别下拉显示保密'</t>
         </is>
@@ -5335,7 +4792,7 @@
       <c r="O48" t="n">
         <v>15</v>
       </c>
-      <c r="Q48" s="3" t="inlineStr">
+      <c r="Q48" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5418,7 +4875,7 @@
       <c r="O49" t="n">
         <v>15</v>
       </c>
-      <c r="Q49" s="3" t="inlineStr">
+      <c r="Q49" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5501,7 +4958,7 @@
           <t>清空家庭住址后保存</t>
         </is>
       </c>
-      <c r="Q50" s="3" t="inlineStr">
+      <c r="Q50" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5589,7 +5046,7 @@
           <t>家庭住址输入特殊字符后保存</t>
         </is>
       </c>
-      <c r="Q51" s="3" t="inlineStr">
+      <c r="Q51" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5672,7 +5129,7 @@
           <t>家庭住址输入空格后保存</t>
         </is>
       </c>
-      <c r="Q52" s="3" t="inlineStr">
+      <c r="Q52" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5754,7 +5211,7 @@
       <c r="O53" t="n">
         <v>3</v>
       </c>
-      <c r="Q53" s="3" t="inlineStr">
+      <c r="Q53" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5843,7 +5300,7 @@
       <c r="O54" t="n">
         <v>5</v>
       </c>
-      <c r="Q54" s="3" t="inlineStr">
+      <c r="Q54" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5926,7 +5383,7 @@
           <t>清空备注后保存，备注非必填</t>
         </is>
       </c>
-      <c r="Q55" s="3" t="inlineStr">
+      <c r="Q55" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6014,7 +5471,7 @@
           <t>备注输入特殊字符后保存</t>
         </is>
       </c>
-      <c r="Q56" s="3" t="inlineStr">
+      <c r="Q56" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6092,7 +5549,7 @@
       <c r="O57" t="n">
         <v>10</v>
       </c>
-      <c r="Q57" s="3" t="inlineStr">
+      <c r="Q57" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6165,7 +5622,7 @@
           <t>最新保存的标签在最前面展示</t>
         </is>
       </c>
-      <c r="M58" s="15" t="inlineStr">
+      <c r="M58" s="14" t="inlineStr">
         <is>
           <t>'自动化标签测试1'</t>
         </is>
@@ -6183,7 +5640,7 @@
           <t>nav进入顾客列表，影像编辑图标易缺失，因此改为更稳妥的div</t>
         </is>
       </c>
-      <c r="Q58" s="3" t="inlineStr">
+      <c r="Q58" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6264,7 +5721,7 @@
       <c r="O59" t="n">
         <v>15</v>
       </c>
-      <c r="Q59" s="3" t="inlineStr">
+      <c r="Q59" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6355,7 +5812,7 @@
           <t>nav改为div,输入注意去掉占位符，否则读取不到</t>
         </is>
       </c>
-      <c r="Q60" s="3" t="inlineStr">
+      <c r="Q60" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6436,7 +5893,7 @@
       <c r="O61" t="n">
         <v>15</v>
       </c>
-      <c r="Q61" s="3" t="inlineStr">
+      <c r="Q61" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6521,7 +5978,7 @@
           <t>标签「自动化标签测试1」需已存在（由 TC-DETAIL-016 生成）</t>
         </is>
       </c>
-      <c r="Q62" s="3" t="inlineStr">
+      <c r="Q62" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6611,7 +6068,7 @@
           <t>需要有历史影像</t>
         </is>
       </c>
-      <c r="Q63" s="3" t="inlineStr">
+      <c r="Q63" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6696,7 +6153,7 @@
       <c r="O64" t="n">
         <v>15</v>
       </c>
-      <c r="Q64" s="3" t="inlineStr">
+      <c r="Q64" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6781,7 +6238,7 @@
           <t>需要有历史影像</t>
         </is>
       </c>
-      <c r="Q65" s="3" t="inlineStr">
+      <c r="Q65" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6865,7 +6322,7 @@
           <t>需要有历史影像；验证管理/完成按钮来回切换</t>
         </is>
       </c>
-      <c r="Q66" s="3" t="inlineStr">
+      <c r="Q66" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -7043,7 +6500,7 @@
       <c r="O68" t="n">
         <v>15</v>
       </c>
-      <c r="Q68" s="3" t="inlineStr">
+      <c r="Q68" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -7294,7 +6751,7 @@
           <t>需要有历史影像；管理模式下不选影像直接删除应提示</t>
         </is>
       </c>
-      <c r="Q71" s="3" t="inlineStr">
+      <c r="Q71" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -7336,7 +6793,7 @@
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G72" s="11" t="inlineStr">
+      <c r="G72" s="10" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7362,7 +6819,6 @@
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K72" s="3" t="n"/>
       <c r="L72" s="3" t="inlineStr">
         <is>
           <t>诊断结果下方出现最新创建的咨询单</t>
@@ -7386,7 +6842,7 @@
           <t>需要「咨询单特定」测试用户存在且有历史影像</t>
         </is>
       </c>
-      <c r="Q72" s="3" t="inlineStr">
+      <c r="Q72" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -7428,7 +6884,7 @@
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G73" s="11" t="inlineStr">
+      <c r="G73" s="10" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7454,7 +6910,6 @@
           <t>咨询单特定|咨询单标签测试</t>
         </is>
       </c>
-      <c r="K73" s="3" t="n"/>
       <c r="L73" s="3" t="inlineStr">
         <is>
           <t>标签页出现咨询单标签测试</t>
@@ -7478,7 +6933,7 @@
           <t>需先执行 TC-DETAIL-030 创建咨询单；咨询单记录在诊断结果标签页</t>
         </is>
       </c>
-      <c r="Q73" s="3" t="inlineStr">
+      <c r="Q73" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -7520,7 +6975,7 @@
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G74" s="11" t="inlineStr">
+      <c r="G74" s="10" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7569,7 +7024,7 @@
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
       </c>
-      <c r="Q74" s="3" t="inlineStr">
+      <c r="Q74" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -7611,7 +7066,7 @@
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G75" s="11" t="inlineStr">
+      <c r="G75" s="10" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7660,7 +7115,7 @@
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
       </c>
-      <c r="Q75" s="3" t="inlineStr">
+      <c r="Q75" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -7702,7 +7157,7 @@
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G76" s="11" t="inlineStr">
+      <c r="G76" s="10" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7751,7 +7206,7 @@
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
       </c>
-      <c r="Q76" s="3" t="inlineStr">
+      <c r="Q76" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -7793,7 +7248,7 @@
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G77" s="11" t="inlineStr">
+      <c r="G77" s="10" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7841,7 +7296,7 @@
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
       </c>
-      <c r="Q77" s="3" t="inlineStr">
+      <c r="Q77" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -7883,7 +7338,7 @@
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G78" s="11" t="inlineStr">
+      <c r="G78" s="10" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7931,7 +7386,7 @@
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
       </c>
-      <c r="Q78" s="3" t="inlineStr">
+      <c r="Q78" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -7973,7 +7428,7 @@
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G79" s="11" t="inlineStr">
+      <c r="G79" s="10" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -8023,7 +7478,7 @@
           <t>自包含用例：先新增固定备注再删除，验证点固定无需随测试数据更新</t>
         </is>
       </c>
-      <c r="Q79" s="3" t="inlineStr">
+      <c r="Q79" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8108,7 +7563,7 @@
       <c r="O80" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="Q80" s="12" t="inlineStr">
+      <c r="Q80" s="11" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8193,7 +7648,7 @@
       <c r="O81" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="Q81" s="12" t="inlineStr">
+      <c r="Q81" s="11" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8278,7 +7733,7 @@
       <c r="O82" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="Q82" s="12" t="inlineStr">
+      <c r="Q82" s="11" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8363,7 +7818,7 @@
       <c r="O83" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="Q83" s="13" t="inlineStr">
+      <c r="Q83" s="12" t="inlineStr">
         <is>
           <t>fail: utils\step_executor.py:170: in _do_click
     element.click(force=True, timeout=self.timeout_ms)
@@ -8453,7 +7908,7 @@
       <c r="O84" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="Q84" s="13" t="inlineStr">
+      <c r="Q84" s="12" t="inlineStr">
         <is>
           <t>fail: utils\step_executor.py:170: in _do_click
     element.click(force=True, timeout=self.timeout_ms)
@@ -8538,7 +7993,7 @@
       <c r="O85" t="n">
         <v>5</v>
       </c>
-      <c r="Q85" s="3" t="inlineStr">
+      <c r="Q85" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8623,7 +8078,7 @@
       <c r="O86" t="n">
         <v>5</v>
       </c>
-      <c r="Q86" s="3" t="inlineStr">
+      <c r="Q86" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8708,7 +8163,7 @@
       <c r="O87" t="n">
         <v>5</v>
       </c>
-      <c r="Q87" s="3" t="inlineStr">
+      <c r="Q87" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8788,7 +8243,7 @@
       <c r="O88" t="n">
         <v>5</v>
       </c>
-      <c r="Q88" s="3" t="inlineStr">
+      <c r="Q88" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8958,7 +8413,7 @@
       <c r="O90" t="n">
         <v>3</v>
       </c>
-      <c r="Q90" s="3" t="inlineStr">
+      <c r="Q90" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -9044,7 +8499,7 @@
       <c r="O91" t="n">
         <v>3</v>
       </c>
-      <c r="Q91" s="3" t="inlineStr">
+      <c r="Q91" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -9130,7 +8585,7 @@
       <c r="O92" t="n">
         <v>3</v>
       </c>
-      <c r="Q92" s="3" t="inlineStr">
+      <c r="Q92" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -9216,7 +8671,7 @@
       <c r="O93" t="n">
         <v>3</v>
       </c>
-      <c r="Q93" s="3" t="inlineStr">
+      <c r="Q93" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -9228,7 +8683,7 @@
       </c>
     </row>
     <row r="94" ht="28" customFormat="1" customHeight="1" s="4">
-      <c r="G94" s="14" t="n"/>
+      <c r="G94" s="13" t="n"/>
     </row>
     <row r="95" ht="28" customFormat="1" customHeight="1" s="4">
       <c r="A95" s="4" t="inlineStr">
@@ -9313,7 +8768,7 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q95" s="12" t="inlineStr">
+      <c r="Q95" s="11" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -9407,7 +8862,7 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q96" s="12" t="inlineStr">
+      <c r="Q96" s="11" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -9501,7 +8956,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q97" s="4" t="n"/>
       <c r="R97" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -9591,7 +9045,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q98" s="4" t="n"/>
       <c r="R98" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -9629,7 +9082,7 @@
           <t>已登录</t>
         </is>
       </c>
-      <c r="G99" s="14" t="inlineStr">
+      <c r="G99" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9681,7 +9134,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q99" s="4" t="n"/>
       <c r="R99" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -9719,7 +9171,7 @@
           <t>已登录</t>
         </is>
       </c>
-      <c r="G100" s="14" t="inlineStr">
+      <c r="G100" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9771,7 +9223,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q100" s="4" t="n"/>
       <c r="R100" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -9809,7 +9260,7 @@
           <t>已登录</t>
         </is>
       </c>
-      <c r="G101" s="14" t="inlineStr">
+      <c r="G101" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9861,7 +9312,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q101" s="4" t="n"/>
       <c r="R101" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -9951,7 +9401,7 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q102" s="12" t="inlineStr">
+      <c r="Q102" s="11" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -10045,7 +9495,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q103" s="4" t="n"/>
       <c r="R103" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -10135,7 +9584,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q104" s="4" t="n"/>
       <c r="R104" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -10225,7 +9673,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q105" s="4" t="n"/>
       <c r="R105" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -10315,7 +9762,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q106" s="4" t="n"/>
       <c r="R106" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -10405,7 +9851,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q107" s="4" t="n"/>
       <c r="R107" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -10443,7 +9888,7 @@
           <t>已登录</t>
         </is>
       </c>
-      <c r="G108" s="14" t="inlineStr">
+      <c r="G108" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10495,7 +9940,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q108" s="4" t="n"/>
       <c r="R108" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -10533,7 +9977,7 @@
           <t>已登录</t>
         </is>
       </c>
-      <c r="G109" s="14" t="inlineStr">
+      <c r="G109" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10585,7 +10029,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q109" s="4" t="n"/>
       <c r="R109" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -10675,7 +10118,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q110" s="4" t="n"/>
       <c r="R110" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -10713,7 +10155,7 @@
           <t>已登录</t>
         </is>
       </c>
-      <c r="G111" s="14" t="inlineStr">
+      <c r="G111" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10765,7 +10207,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q111" s="4" t="n"/>
       <c r="R111" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -10855,7 +10296,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q112" s="4" t="n"/>
       <c r="R112" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -10945,7 +10385,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q113" s="4" t="n"/>
       <c r="R113" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -11035,7 +10474,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q114" s="4" t="n"/>
       <c r="R114" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -11125,7 +10563,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q115" s="4" t="n"/>
       <c r="R115" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -11215,7 +10652,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q116" s="4" t="n"/>
       <c r="R116" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -11305,7 +10741,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q117" s="4" t="n"/>
       <c r="R117" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -11343,7 +10778,7 @@
           <t>已登录</t>
         </is>
       </c>
-      <c r="G118" s="14" t="inlineStr">
+      <c r="G118" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -11395,7 +10830,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q118" s="4" t="n"/>
       <c r="R118" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -11433,7 +10867,7 @@
           <t>已登录</t>
         </is>
       </c>
-      <c r="G119" s="14" t="inlineStr">
+      <c r="G119" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -11485,7 +10919,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q119" s="4" t="n"/>
       <c r="R119" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -11575,7 +11008,6 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q120" s="4" t="n"/>
       <c r="R120" s="4" t="inlineStr">
         <is>
           <t>否</t>
@@ -11665,7 +11097,7 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q121" s="3" t="inlineStr">
+      <c r="Q121" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -11759,7 +11191,7 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q122" s="3" t="inlineStr">
+      <c r="Q122" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -11853,7 +11285,7 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q123" s="17" t="inlineStr">
+      <c r="Q123" s="21" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -11876,7 +11308,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="3"/>
@@ -12165,7 +11597,7 @@
           <t>其他说明信息</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12179,7 +11611,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -12487,7 +11919,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>

--- a/test_cases/test_case.xlsx
+++ b/test_cases/test_case.xlsx
@@ -2,9 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet name="自动化测试用例" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="字段说明" sheetId="2" state="visible" r:id="rId2"/>
@@ -12,84 +9,156 @@
     <sheet name="操作类型说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="27">
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
+      <name val="Calibri"/>
       <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <color theme="0"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
       <sz val="11"/>
     </font>
     <font/>
   </fonts>
-  <fills count="8">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -99,48 +168,181 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="10">
+    <border/>
     <border>
       <left style="thin">
         <color auto="1"/>
@@ -154,16 +356,243 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color theme="4" tint="0.49998"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="25" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="25" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="25" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="25" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -176,6 +605,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -185,149 +624,71 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="千位分隔" xfId="1"/>
+    <cellStyle name="货币" xfId="2"/>
+    <cellStyle name="百分比" xfId="3"/>
+    <cellStyle name="千位分隔[0]" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="5"/>
+    <cellStyle name="超链接" xfId="6"/>
+    <cellStyle name="已访问的超链接" xfId="7"/>
+    <cellStyle name="注释" xfId="8"/>
+    <cellStyle name="警告文本" xfId="9"/>
+    <cellStyle name="标题" xfId="10"/>
+    <cellStyle name="解释性文本" xfId="11"/>
+    <cellStyle name="标题 1" xfId="12"/>
+    <cellStyle name="标题 2" xfId="13"/>
+    <cellStyle name="标题 3" xfId="14"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="输入" xfId="16"/>
+    <cellStyle name="输出" xfId="17"/>
+    <cellStyle name="计算" xfId="18"/>
+    <cellStyle name="检查单元格" xfId="19"/>
+    <cellStyle name="链接单元格" xfId="20"/>
+    <cellStyle name="汇总" xfId="21"/>
+    <cellStyle name="好" xfId="22"/>
+    <cellStyle name="差" xfId="23"/>
+    <cellStyle name="适中" xfId="24"/>
+    <cellStyle name="强调文字颜色 1" xfId="25"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle name="强调文字颜色 2" xfId="29"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle name="强调文字颜色 3" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle name="强调文字颜色 4" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="强调文字颜色 6" xfId="45"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.3999450666829432"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.3999450666829432"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.3999450666829432"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.3999450666829432"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.3999450666829432"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.3999450666829432"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
     </dxf>
@@ -360,8 +721,7 @@
         <color theme="0"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
+        <patternFill>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
@@ -383,35 +743,120 @@
         <bottom style="thin">
           <color theme="4"/>
         </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.3999450666829432"/>
-        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39998"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39998"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39998"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39998"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39998"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39998"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
-    </tableStyle>
-  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -692,8 +1137,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -703,121 +1146,127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R123"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:S123"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="25.81640625" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="35" customWidth="1" min="12" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="14.453125" customWidth="1" min="17" max="17"/>
+    <col width="25.8166675567627" customWidth="1" style="14" min="1" max="1"/>
+    <col width="12" customWidth="1" style="14" min="2" max="2"/>
+    <col width="25" customWidth="1" style="14" min="3" max="3"/>
+    <col width="20" customWidth="1" style="14" min="4" max="4"/>
+    <col width="8" customWidth="1" style="14" min="5" max="5"/>
+    <col width="25" customWidth="1" style="14" min="6" max="6"/>
+    <col width="40" customWidth="1" style="14" min="7" max="7"/>
+    <col width="45" customWidth="1" style="14" min="8" max="8"/>
+    <col width="18" customWidth="1" style="14" min="9" max="9"/>
+    <col width="25" customWidth="1" style="14" min="10" max="10"/>
+    <col width="12" customWidth="1" style="14" min="11" max="11"/>
+    <col width="35" customWidth="1" style="14" min="12" max="13"/>
+    <col width="15" customWidth="1" style="14" min="14" max="14"/>
+    <col width="10" customWidth="1" style="14" min="15" max="15"/>
+    <col width="20" customWidth="1" style="14" min="16" max="16"/>
+    <col width="14.44999980926514" customWidth="1" style="14" min="17" max="17"/>
+    <col width="12" customWidth="1" style="14" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>用例ID</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>模块</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>测试场景</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>测试点</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>前置条件</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>操作步骤</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>元素定位器</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>操作类型</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>输入数据</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>数据类型</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>期望结果</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>验证点</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="N1" s="8" t="inlineStr">
         <is>
           <t>断言类型</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="O1" s="8" t="inlineStr">
         <is>
           <t>超时(秒)</t>
         </is>
       </c>
-      <c r="P1" s="6" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>实际结果</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>是否执行</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>执行分组</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" s="14">
+      <c r="A2" t="inlineStr">
         <is>
           <t>TC-LOGIN-001</t>
         </is>
@@ -896,7 +1345,7 @@
           <t>错误账号测试</t>
         </is>
       </c>
-      <c r="Q2" s="17" t="inlineStr">
+      <c r="Q2" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -906,8 +1355,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1" s="14">
       <c r="A3" t="inlineStr">
         <is>
           <t>TC-LOGIN-002</t>
@@ -988,7 +1442,7 @@
           <t>错误密码测试</t>
         </is>
       </c>
-      <c r="Q3" s="17" t="inlineStr">
+      <c r="Q3" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -998,8 +1452,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" s="14">
       <c r="A4" t="inlineStr">
         <is>
           <t>TC-LOGIN-003</t>
@@ -1074,7 +1533,7 @@
           <t>必填校验</t>
         </is>
       </c>
-      <c r="Q4" s="17" t="inlineStr">
+      <c r="Q4" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1084,8 +1543,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" s="14">
       <c r="A5" t="inlineStr">
         <is>
           <t>TC-LOGIN-004</t>
@@ -1161,7 +1625,7 @@
       <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="Q5" s="17" t="inlineStr">
+      <c r="Q5" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1171,8 +1635,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="56" customHeight="1">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1" s="14">
       <c r="A6" t="inlineStr">
         <is>
           <t>TC-LOGIN-005</t>
@@ -1249,7 +1718,7 @@
       <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" s="17" t="inlineStr">
+      <c r="Q6" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1259,8 +1728,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="56" customHeight="1">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1" s="14">
       <c r="A7" t="inlineStr">
         <is>
           <t>TC-LOGIN-006</t>
@@ -1330,7 +1804,7 @@
       <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="Q7" s="17" t="inlineStr">
+      <c r="Q7" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1340,8 +1814,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="56" customHeight="1">
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1" s="14">
       <c r="A8" t="inlineStr">
         <is>
           <t>TC-LOGIN-007</t>
@@ -1423,7 +1902,7 @@
           <t>正常登录流程</t>
         </is>
       </c>
-      <c r="Q8" s="17" t="inlineStr">
+      <c r="Q8" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1433,8 +1912,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" s="14">
       <c r="A9" t="inlineStr">
         <is>
           <t>TC-HOME-001</t>
@@ -1503,7 +1987,7 @@
       <c r="O9" t="n">
         <v>5</v>
       </c>
-      <c r="Q9" s="17" t="inlineStr">
+      <c r="Q9" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1513,8 +1997,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" s="14">
       <c r="A10" t="inlineStr">
         <is>
           <t>TC-HOME-002</t>
@@ -1545,7 +2034,7 @@
           <t>已登录成功</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>1.在搜索框输入不存在的用户名
 2.点击搜索</t>
@@ -1589,7 +2078,7 @@
       <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="Q10" s="17" t="inlineStr">
+      <c r="Q10" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1599,92 +2088,102 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="28" customFormat="1" customHeight="1" s="4">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" s="14">
+      <c r="A11" t="inlineStr">
         <is>
           <t>TC-HOME-003</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>首页搜索</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>搜索-不存在的手机号</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>验证无结果提示</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>p1</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>已登录成功</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>1.在搜索框输入不存在的手机号
 2.点击搜索</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>input[placeholder='请输入关键字'], button:has-text('搜 索')</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>input,click</t>
         </is>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J11" t="n">
         <v>100000000000</v>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>展示：暂无内容</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>页面显示'暂无'</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="Q11" s="21" t="inlineStr">
+      <c r="Q11" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" s="14">
       <c r="A12" t="inlineStr">
         <is>
           <t>TC-HOME-004</t>
@@ -1731,7 +2230,7 @@
           <t>input,click</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>t</t>
         </is>
@@ -1759,7 +2258,7 @@
       <c r="O12" t="n">
         <v>5</v>
       </c>
-      <c r="Q12" s="17" t="inlineStr">
+      <c r="Q12" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1769,8 +2268,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" s="14">
       <c r="A13" t="inlineStr">
         <is>
           <t>TC-HOME-005</t>
@@ -1845,7 +2349,7 @@
       <c r="O13" t="n">
         <v>5</v>
       </c>
-      <c r="Q13" s="17" t="inlineStr">
+      <c r="Q13" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1855,8 +2359,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" s="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>TC-HOME-006</t>
@@ -1929,7 +2438,7 @@
       <c r="O14" t="n">
         <v>5</v>
       </c>
-      <c r="Q14" s="17" t="inlineStr">
+      <c r="Q14" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1939,8 +2448,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" s="14">
       <c r="A15" t="inlineStr">
         <is>
           <t>TC-HOME-007</t>
@@ -2013,7 +2527,7 @@
       <c r="O15" t="n">
         <v>5</v>
       </c>
-      <c r="Q15" s="17" t="inlineStr">
+      <c r="Q15" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2023,8 +2537,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" s="14">
       <c r="A16" t="inlineStr">
         <is>
           <t>TC-HOME-008</t>
@@ -2093,7 +2612,7 @@
       <c r="O16" t="n">
         <v>5</v>
       </c>
-      <c r="Q16" s="17" t="inlineStr">
+      <c r="Q16" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2103,8 +2622,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" s="14">
       <c r="A17" t="inlineStr">
         <is>
           <t>TC-HOME-009</t>
@@ -2173,7 +2697,7 @@
       <c r="O17" t="n">
         <v>5</v>
       </c>
-      <c r="Q17" s="17" t="inlineStr">
+      <c r="Q17" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2183,8 +2707,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" s="14">
       <c r="A18" t="inlineStr">
         <is>
           <t>TC-HOME-010</t>
@@ -2253,7 +2782,7 @@
       <c r="O18" t="n">
         <v>5</v>
       </c>
-      <c r="Q18" s="17" t="inlineStr">
+      <c r="Q18" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2263,8 +2792,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" s="14">
       <c r="A19" t="inlineStr">
         <is>
           <t>TC-HOME-011</t>
@@ -2333,7 +2867,7 @@
       <c r="O19" t="n">
         <v>5</v>
       </c>
-      <c r="Q19" s="17" t="inlineStr">
+      <c r="Q19" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2343,8 +2877,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" s="14">
       <c r="A20" t="inlineStr">
         <is>
           <t>TC-HOME-012</t>
@@ -2413,7 +2952,7 @@
       <c r="O20" t="n">
         <v>15</v>
       </c>
-      <c r="Q20" s="17" t="inlineStr">
+      <c r="Q20" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2423,8 +2962,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1" s="14">
       <c r="A21" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-001</t>
@@ -2455,7 +2999,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>1.在搜索框输入不存在的用户名
 2.点击搜索</t>
@@ -2494,7 +3038,7 @@
       <c r="O21" t="n">
         <v>10</v>
       </c>
-      <c r="Q21" s="17" t="inlineStr">
+      <c r="Q21" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2504,8 +3048,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1" s="14">
       <c r="A22" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-002</t>
@@ -2536,7 +3085,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>1.在搜索框输入存在的用户名部分
 2.点击搜索</t>
@@ -2575,7 +3124,7 @@
       <c r="O22" t="n">
         <v>10</v>
       </c>
-      <c r="Q22" s="17" t="inlineStr">
+      <c r="Q22" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2585,8 +3134,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" s="14">
       <c r="A23" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-003</t>
@@ -2617,7 +3171,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>1.在搜索框输入存在的用户名
 2.点击搜索</t>
@@ -2656,7 +3210,7 @@
       <c r="O23" t="n">
         <v>10</v>
       </c>
-      <c r="Q23" s="17" t="inlineStr">
+      <c r="Q23" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2666,89 +3220,99 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="28" customFormat="1" customHeight="1" s="4">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customFormat="1" customHeight="1" s="17">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-004</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>顾客列表</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>搜索-不存在的手机号</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>验证无结果提示</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G24" s="19" t="inlineStr">
         <is>
           <t>1.在搜索框输入不存在的手机号
 2.点击搜索</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>/customer, 0.5, input[placeholder='请输入关键字'], button:has-text('搜 索')</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I24" s="17" t="inlineStr">
         <is>
           <t>nav, wait, input, click</t>
         </is>
       </c>
-      <c r="J24" s="18" t="inlineStr">
+      <c r="J24" s="17" t="inlineStr">
         <is>
           <t>|100000000000</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L24" s="17" t="inlineStr">
         <is>
           <t>展示：暂无内容</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M24" s="17" t="inlineStr">
         <is>
           <t>'暂无'</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="N24" s="17" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O24" s="4" t="n">
+      <c r="O24" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="Q24" s="21" t="inlineStr">
+      <c r="Q24" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R24" s="4" t="inlineStr">
+      <c r="R24" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
+      <c r="S24" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1" s="14">
       <c r="A25" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-005</t>
@@ -2779,7 +3343,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>1.在搜索框输入存在的手机号部分
 2.点击搜索</t>
@@ -2818,7 +3382,7 @@
       <c r="O25" t="n">
         <v>10</v>
       </c>
-      <c r="Q25" s="17" t="inlineStr">
+      <c r="Q25" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2828,8 +3392,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1" s="14">
       <c r="A26" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-006</t>
@@ -2860,7 +3429,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>1.在搜索框输入存在的手机号
 2.点击搜索</t>
@@ -2899,7 +3468,7 @@
       <c r="O26" t="n">
         <v>10</v>
       </c>
-      <c r="Q26" s="17" t="inlineStr">
+      <c r="Q26" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2909,8 +3478,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1" s="14">
       <c r="A27" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-007</t>
@@ -2941,7 +3515,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>1.选择时间范围筛选
 2.选择不存在数据的时间范围</t>
@@ -2980,7 +3554,7 @@
       <c r="O27" t="n">
         <v>5</v>
       </c>
-      <c r="Q27" s="17" t="inlineStr">
+      <c r="Q27" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -2990,8 +3564,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" s="14">
       <c r="A28" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-008</t>
@@ -3065,7 +3644,7 @@
       <c r="O28" t="n">
         <v>5</v>
       </c>
-      <c r="Q28" s="17" t="inlineStr">
+      <c r="Q28" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3075,8 +3654,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1" s="14">
       <c r="A29" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-009</t>
@@ -3146,7 +3730,7 @@
       <c r="O29" t="n">
         <v>5</v>
       </c>
-      <c r="Q29" s="17" t="inlineStr">
+      <c r="Q29" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3156,8 +3740,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" s="14">
       <c r="A30" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-010</t>
@@ -3232,7 +3821,7 @@
       <c r="O30" t="n">
         <v>10</v>
       </c>
-      <c r="Q30" s="17" t="inlineStr">
+      <c r="Q30" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3242,8 +3831,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1" s="14">
       <c r="A31" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-011</t>
@@ -3318,7 +3912,7 @@
       <c r="O31" t="n">
         <v>10</v>
       </c>
-      <c r="Q31" s="17" t="inlineStr">
+      <c r="Q31" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3328,8 +3922,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" s="14">
       <c r="A32" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-012</t>
@@ -3407,7 +4006,7 @@
       <c r="O32" t="n">
         <v>10</v>
       </c>
-      <c r="Q32" s="17" t="inlineStr">
+      <c r="Q32" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3417,8 +4016,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" s="14">
       <c r="A33" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-013</t>
@@ -3449,7 +4053,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>1.点击其他筛选
 2.选择26~35岁
@@ -3496,7 +4100,7 @@
       <c r="O33" t="n">
         <v>10</v>
       </c>
-      <c r="Q33" s="17" t="inlineStr">
+      <c r="Q33" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3506,8 +4110,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1" s="14">
       <c r="A34" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-014</t>
@@ -3538,7 +4147,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>1.点击其他筛选
 2.选择36~45岁
@@ -3585,7 +4194,7 @@
       <c r="O34" t="n">
         <v>10</v>
       </c>
-      <c r="Q34" s="17" t="inlineStr">
+      <c r="Q34" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3595,8 +4204,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1" s="14">
       <c r="A35" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-015</t>
@@ -3627,7 +4241,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>1.点击其他筛选
 2.选择45岁以上
@@ -3674,7 +4288,7 @@
       <c r="O35" t="n">
         <v>10</v>
       </c>
-      <c r="Q35" s="17" t="inlineStr">
+      <c r="Q35" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3684,8 +4298,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1" s="14">
       <c r="A36" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-016</t>
@@ -3763,7 +4382,7 @@
       <c r="O36" t="n">
         <v>10</v>
       </c>
-      <c r="Q36" s="17" t="inlineStr">
+      <c r="Q36" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3773,8 +4392,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1" s="14">
       <c r="A37" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-017</t>
@@ -3805,7 +4429,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>1.选择不存在数据的时间范围
 2.点击其他筛选
@@ -3852,7 +4476,7 @@
       <c r="O37" t="n">
         <v>10</v>
       </c>
-      <c r="Q37" s="17" t="inlineStr">
+      <c r="Q37" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3862,8 +4486,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1" s="14">
       <c r="A38" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-018</t>
@@ -3894,7 +4523,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>1.选择存在数据的时间范围
 2.点击其他筛选
@@ -3928,7 +4557,7 @@
           <t>展示符合时间范围的顾客档案</t>
         </is>
       </c>
-      <c r="M38" s="14" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>'详情'</t>
         </is>
@@ -3941,7 +4570,7 @@
       <c r="O38" t="n">
         <v>10</v>
       </c>
-      <c r="Q38" s="17" t="inlineStr">
+      <c r="Q38" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -3951,8 +4580,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1" s="14">
       <c r="A39" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-019</t>
@@ -4019,7 +4653,7 @@
           <t>已根据实际DOM调整：删除'已为'步骤；确定按钮用.ant-popover .ant-btn-primary；备注图标用.ant-image + div .anticon</t>
         </is>
       </c>
-      <c r="Q39" s="17" t="inlineStr">
+      <c r="Q39" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4029,8 +4663,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1" s="14">
       <c r="A40" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-020</t>
@@ -4061,7 +4700,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客档案列表
 2.查看顾客卡片字段信息</t>
@@ -4105,7 +4744,7 @@
           <t>卡片为自定义结构（非ant-list）；性别图标为图片形式无法文本断言；字段验证：姓名/年龄/手机号/上次检测时间/检测次数/详情</t>
         </is>
       </c>
-      <c r="Q40" s="17" t="inlineStr">
+      <c r="Q40" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4115,8 +4754,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1" s="14">
       <c r="A41" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-021</t>
@@ -4185,7 +4829,7 @@
       <c r="O41" t="n">
         <v>5</v>
       </c>
-      <c r="Q41" s="17" t="inlineStr">
+      <c r="Q41" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4195,8 +4839,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="42" customHeight="1">
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1" s="14">
       <c r="A42" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-022</t>
@@ -4267,7 +4916,7 @@
       <c r="O42" t="n">
         <v>10</v>
       </c>
-      <c r="Q42" s="17" t="inlineStr">
+      <c r="Q42" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4277,8 +4926,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="42" customHeight="1">
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1" s="14">
       <c r="A43" t="inlineStr">
         <is>
           <t>TC-DETAIL-001</t>
@@ -4309,7 +4963,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>1.点击编辑资料
 2.清空姓名
@@ -4350,7 +5004,7 @@
       <c r="O43" t="n">
         <v>3</v>
       </c>
-      <c r="Q43" s="17" t="inlineStr">
+      <c r="Q43" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4360,8 +5014,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="56" customHeight="1">
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="56" customHeight="1" s="14">
       <c r="A44" t="inlineStr">
         <is>
           <t>TC-DETAIL-002</t>
@@ -4392,7 +5051,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -4440,18 +5099,23 @@
       <c r="O44" t="n">
         <v>15</v>
       </c>
-      <c r="Q44" s="3" t="inlineStr">
+      <c r="Q44" s="17" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R44" s="9" t="inlineStr">
+      <c r="R44" s="18" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="56" customHeight="1">
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="56" customHeight="1" s="14">
       <c r="A45" t="inlineStr">
         <is>
           <t>TC-DETAIL-003</t>
@@ -4482,7 +5146,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -4528,7 +5192,7 @@
       <c r="O45" t="n">
         <v>10</v>
       </c>
-      <c r="Q45" s="17" t="inlineStr">
+      <c r="Q45" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4538,8 +5202,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="42" customHeight="1">
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1" s="14">
       <c r="A46" t="inlineStr">
         <is>
           <t>TC-DETAIL-004</t>
@@ -4570,7 +5239,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -4616,7 +5285,7 @@
       <c r="O46" t="n">
         <v>10</v>
       </c>
-      <c r="Q46" s="17" t="inlineStr">
+      <c r="Q46" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4626,8 +5295,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="42" customHeight="1">
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1" s="14">
       <c r="A47" t="inlineStr">
         <is>
           <t>TC-DETAIL-005</t>
@@ -4658,7 +5332,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -4704,7 +5378,7 @@
       <c r="O47" t="n">
         <v>10</v>
       </c>
-      <c r="Q47" s="17" t="inlineStr">
+      <c r="Q47" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4714,8 +5388,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="42" customHeight="1">
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1" s="14">
       <c r="A48" t="inlineStr">
         <is>
           <t>TC-DETAIL-006</t>
@@ -4746,7 +5425,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -4779,7 +5458,7 @@
           <t>保存成功，性别显示'保密'</t>
         </is>
       </c>
-      <c r="M48" s="14" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>'性别下拉显示保密'</t>
         </is>
@@ -4792,7 +5471,7 @@
       <c r="O48" t="n">
         <v>15</v>
       </c>
-      <c r="Q48" s="17" t="inlineStr">
+      <c r="Q48" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4802,8 +5481,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="42" customHeight="1">
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1" s="14">
       <c r="A49" t="inlineStr">
         <is>
           <t>TC-DETAIL-007</t>
@@ -4834,7 +5518,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -4875,7 +5559,7 @@
       <c r="O49" t="n">
         <v>15</v>
       </c>
-      <c r="Q49" s="17" t="inlineStr">
+      <c r="Q49" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4885,8 +5569,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="42" customHeight="1">
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1" s="14">
       <c r="A50" t="inlineStr">
         <is>
           <t>TC-DETAIL-008</t>
@@ -4917,7 +5606,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="G50" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -4958,7 +5647,7 @@
           <t>清空家庭住址后保存</t>
         </is>
       </c>
-      <c r="Q50" s="17" t="inlineStr">
+      <c r="Q50" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -4968,8 +5657,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="42" customHeight="1">
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1" s="14">
       <c r="A51" t="inlineStr">
         <is>
           <t>TC-DETAIL-009</t>
@@ -5000,7 +5694,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="G51" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -5046,7 +5740,7 @@
           <t>家庭住址输入特殊字符后保存</t>
         </is>
       </c>
-      <c r="Q51" s="17" t="inlineStr">
+      <c r="Q51" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5056,8 +5750,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="52" ht="42" customHeight="1">
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1" s="14">
       <c r="A52" t="inlineStr">
         <is>
           <t>TC-DETAIL-010</t>
@@ -5088,7 +5787,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -5129,7 +5828,7 @@
           <t>家庭住址输入空格后保存</t>
         </is>
       </c>
-      <c r="Q52" s="17" t="inlineStr">
+      <c r="Q52" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5139,8 +5838,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="53" ht="42" customHeight="1">
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="42" customHeight="1" s="14">
       <c r="A53" t="inlineStr">
         <is>
           <t>TC-DETAIL-011</t>
@@ -5171,7 +5875,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G53" s="8" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr">
         <is>
           <t>1.点击编辑资料
 2.清空手机号
@@ -5211,7 +5915,7 @@
       <c r="O53" t="n">
         <v>3</v>
       </c>
-      <c r="Q53" s="17" t="inlineStr">
+      <c r="Q53" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5221,8 +5925,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="54" ht="42" customHeight="1">
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1" s="14">
       <c r="A54" t="inlineStr">
         <is>
           <t>TC-DETAIL-012</t>
@@ -5253,7 +5962,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="G54" s="12" t="inlineStr">
         <is>
           <t>1.已登录，进入顾客详情页
 2.点击右侧所有影像中的一个影像的右下角编辑图标
@@ -5300,7 +6009,7 @@
       <c r="O54" t="n">
         <v>5</v>
       </c>
-      <c r="Q54" s="17" t="inlineStr">
+      <c r="Q54" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5310,8 +6019,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="55" ht="42" customHeight="1">
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="42" customHeight="1" s="14">
       <c r="A55" t="inlineStr">
         <is>
           <t>TC-DETAIL-013</t>
@@ -5342,7 +6056,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -5383,7 +6097,7 @@
           <t>清空备注后保存，备注非必填</t>
         </is>
       </c>
-      <c r="Q55" s="17" t="inlineStr">
+      <c r="Q55" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5393,8 +6107,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="56" ht="42" customHeight="1">
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42" customHeight="1" s="14">
       <c r="A56" t="inlineStr">
         <is>
           <t>TC-DETAIL-014</t>
@@ -5425,7 +6144,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="G56" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -5471,7 +6190,7 @@
           <t>备注输入特殊字符后保存</t>
         </is>
       </c>
-      <c r="Q56" s="17" t="inlineStr">
+      <c r="Q56" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5481,8 +6200,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="57" ht="42" customHeight="1">
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1" s="14">
       <c r="A57" t="inlineStr">
         <is>
           <t>TC-DETAIL-015</t>
@@ -5513,7 +6237,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G57" s="8" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -5549,7 +6273,7 @@
       <c r="O57" t="n">
         <v>10</v>
       </c>
-      <c r="Q57" s="17" t="inlineStr">
+      <c r="Q57" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5559,8 +6283,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1" s="14">
       <c r="A58" t="inlineStr">
         <is>
           <t>TC-DETAIL-016</t>
@@ -5591,7 +6320,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G58" s="8" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -5622,7 +6351,7 @@
           <t>最新保存的标签在最前面展示</t>
         </is>
       </c>
-      <c r="M58" s="14" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>'自动化标签测试1'</t>
         </is>
@@ -5640,7 +6369,7 @@
           <t>nav进入顾客列表，影像编辑图标易缺失，因此改为更稳妥的div</t>
         </is>
       </c>
-      <c r="Q58" s="17" t="inlineStr">
+      <c r="Q58" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5650,8 +6379,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="59" ht="28" customHeight="1">
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1" s="14">
       <c r="A59" t="inlineStr">
         <is>
           <t>TC-DETAIL-017</t>
@@ -5682,7 +6416,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G59" s="8" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -5721,7 +6455,7 @@
       <c r="O59" t="n">
         <v>15</v>
       </c>
-      <c r="Q59" s="17" t="inlineStr">
+      <c r="Q59" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5731,8 +6465,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1" s="14">
       <c r="A60" t="inlineStr">
         <is>
           <t>TC-DETAIL-018</t>
@@ -5763,7 +6502,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G60" s="8" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -5812,7 +6551,7 @@
           <t>nav改为div,输入注意去掉占位符，否则读取不到</t>
         </is>
       </c>
-      <c r="Q60" s="17" t="inlineStr">
+      <c r="Q60" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5822,8 +6561,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="61" ht="28" customHeight="1">
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1" s="14">
       <c r="A61" t="inlineStr">
         <is>
           <t>TC-DETAIL-019</t>
@@ -5854,7 +6598,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G61" s="8" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -5893,7 +6637,7 @@
       <c r="O61" t="n">
         <v>15</v>
       </c>
-      <c r="Q61" s="17" t="inlineStr">
+      <c r="Q61" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5903,8 +6647,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="62" ht="42" customHeight="1">
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="42" customHeight="1" s="14">
       <c r="A62" t="inlineStr">
         <is>
           <t>TC-DETAIL-020</t>
@@ -5935,7 +6684,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G62" s="8" t="inlineStr">
+      <c r="G62" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -5978,7 +6727,7 @@
           <t>标签「自动化标签测试1」需已存在（由 TC-DETAIL-016 生成）</t>
         </is>
       </c>
-      <c r="Q62" s="17" t="inlineStr">
+      <c r="Q62" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -5988,8 +6737,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="63" ht="42" customHeight="1">
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1" s="14">
       <c r="A63" t="inlineStr">
         <is>
           <t>TC-DETAIL-021</t>
@@ -6020,7 +6774,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr">
+      <c r="G63" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -6068,7 +6822,7 @@
           <t>需要有历史影像</t>
         </is>
       </c>
-      <c r="Q63" s="17" t="inlineStr">
+      <c r="Q63" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6078,8 +6832,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="64" ht="42" customHeight="1">
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1" s="14">
       <c r="A64" t="inlineStr">
         <is>
           <t>TC-DETAIL-022</t>
@@ -6110,7 +6869,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -6153,7 +6912,7 @@
       <c r="O64" t="n">
         <v>15</v>
       </c>
-      <c r="Q64" s="17" t="inlineStr">
+      <c r="Q64" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6163,8 +6922,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="65" ht="42" customHeight="1">
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1" s="14">
       <c r="A65" t="inlineStr">
         <is>
           <t>TC-DETAIL-023</t>
@@ -6195,7 +6959,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G65" s="8" t="inlineStr">
+      <c r="G65" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -6238,7 +7002,7 @@
           <t>需要有历史影像</t>
         </is>
       </c>
-      <c r="Q65" s="17" t="inlineStr">
+      <c r="Q65" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6248,8 +7012,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="66" ht="42" customHeight="1">
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1" s="14">
       <c r="A66" t="inlineStr">
         <is>
           <t>TC-DETAIL-024</t>
@@ -6280,7 +7049,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="G66" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.查找有检测记录顾客
@@ -6322,7 +7091,7 @@
           <t>需要有历史影像；验证管理/完成按钮来回切换</t>
         </is>
       </c>
-      <c r="Q66" s="17" t="inlineStr">
+      <c r="Q66" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6332,8 +7101,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="67" ht="42" customHeight="1">
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1" s="14">
       <c r="A67" t="inlineStr">
         <is>
           <t>TC-DETAIL-025</t>
@@ -6364,7 +7138,7 @@
           <t>已登录</t>
         </is>
       </c>
-      <c r="G67" s="8" t="inlineStr">
+      <c r="G67" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.查找有检测记录顾客
@@ -6422,13 +7196,18 @@
     self._do_find_</t>
         </is>
       </c>
-      <c r="R67" s="9" t="inlineStr">
+      <c r="R67" s="18" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="68" ht="42" customHeight="1">
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="42" customHeight="1" s="14">
       <c r="A68" t="inlineStr">
         <is>
           <t>TC-DETAIL-026</t>
@@ -6459,7 +7238,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G68" s="8" t="inlineStr">
+      <c r="G68" s="12" t="inlineStr">
         <is>
           <t>1.点击影像详情
 2.点击编辑资料
@@ -6500,7 +7279,7 @@
       <c r="O68" t="n">
         <v>15</v>
       </c>
-      <c r="Q68" s="17" t="inlineStr">
+      <c r="Q68" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6510,8 +7289,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="69" ht="42" customHeight="1">
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="42" customHeight="1" s="14">
       <c r="A69" t="inlineStr">
         <is>
           <t>TC-DETAIL-027</t>
@@ -6586,7 +7370,7 @@
       <c r="O69" t="n">
         <v>15</v>
       </c>
-      <c r="Q69" s="17" t="inlineStr">
+      <c r="Q69" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6596,8 +7380,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="70" ht="28" customHeight="1">
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1" s="14">
       <c r="A70" t="inlineStr">
         <is>
           <t>TC-DETAIL-028</t>
@@ -6628,7 +7417,7 @@
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G70" s="8" t="inlineStr">
+      <c r="G70" s="12" t="inlineStr">
         <is>
           <t>1.点击右下角显示'共检测N次',N&gt;1的卡片的详情按钮
 2.点击管理
@@ -6648,7 +7437,7 @@
           <t>nav, wait, find_click, click, click, click, click, nav, wait</t>
         </is>
       </c>
-      <c r="L70" s="8" t="inlineStr">
+      <c r="L70" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">
 该顾客的卡片右下角显示共检测n次,n=详情页中所有历史影像个数</t>
@@ -6672,13 +7461,18 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="R70" s="9" t="inlineStr">
+      <c r="R70" s="18" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="71" ht="28" customHeight="1">
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1" s="14">
       <c r="A71" t="inlineStr">
         <is>
           <t>TC-DETAIL-029</t>
@@ -6709,7 +7503,7 @@
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G71" s="8" t="inlineStr">
+      <c r="G71" s="12" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.查找有检测记录顾客
@@ -6751,7 +7545,7 @@
           <t>需要有历史影像；管理模式下不选影像直接删除应提示</t>
         </is>
       </c>
-      <c r="Q71" s="17" t="inlineStr">
+      <c r="Q71" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -6761,39 +7555,44 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="72" ht="28" customFormat="1" customHeight="1" s="3">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customFormat="1" customHeight="1" s="17">
+      <c r="A72" s="17" t="inlineStr">
         <is>
           <t>TC-DETAIL-030</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B72" s="17" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="17" t="inlineStr">
         <is>
           <t>咨询单-添加咨询单</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="17" t="inlineStr">
         <is>
           <t>验证咨询单添加功能</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E72" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F72" s="17" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G72" s="10" t="inlineStr">
+      <c r="G72" s="19" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -6804,87 +7603,92 @@
 7.然后点击前往弹框中的前往顾客档案</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="H72" s="17" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=查看报告|text=完 成|[data-layout="column"][data-layout-align="center center"], 2, text=完 成, 5, text=前往顾客档案</t>
         </is>
       </c>
-      <c r="I72" s="3" t="inlineStr">
+      <c r="I72" s="17" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, retry_report, wait, click, wait, click</t>
         </is>
       </c>
-      <c r="J72" s="3" t="inlineStr">
+      <c r="J72" s="17" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="L72" s="3" t="inlineStr">
+      <c r="L72" s="17" t="inlineStr">
         <is>
           <t>诊断结果下方出现最新创建的咨询单</t>
         </is>
       </c>
-      <c r="M72" s="3" t="inlineStr">
+      <c r="M72" s="17" t="inlineStr">
         <is>
           <t>咨询单</t>
         </is>
       </c>
-      <c r="N72" s="3" t="inlineStr">
+      <c r="N72" s="17" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O72" s="3" t="n">
+      <c r="O72" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="P72" s="3" t="inlineStr">
+      <c r="P72" s="17" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户存在且有历史影像</t>
         </is>
       </c>
-      <c r="Q72" s="21" t="inlineStr">
+      <c r="Q72" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R72" s="3" t="inlineStr">
+      <c r="R72" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="73" ht="28" customFormat="1" customHeight="1" s="3">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28" customFormat="1" customHeight="1" s="17">
+      <c r="A73" s="17" t="inlineStr">
         <is>
           <t>TC-DETAIL-031</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B73" s="17" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C73" s="17" t="inlineStr">
         <is>
           <t>咨询单-备注标签添加</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D73" s="17" t="inlineStr">
         <is>
           <t>验证咨询单的备注标签添加功能</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E73" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F73" s="17" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G73" s="10" t="inlineStr">
+      <c r="G73" s="19" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -6895,87 +7699,92 @@
 7.点击保存</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H73" s="17" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 2, .ant-tag:has-text('添加标签'), .ant-tag:has-text('添加标签'), input[placeholder='请输入标签内容'], input[placeholder='请输入标签内容'], button:has-text('保 存')</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="I73" s="17" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify, click, verify, input, click</t>
         </is>
       </c>
-      <c r="J73" s="3" t="inlineStr">
+      <c r="J73" s="17" t="inlineStr">
         <is>
           <t>咨询单特定|咨询单标签测试</t>
         </is>
       </c>
-      <c r="L73" s="3" t="inlineStr">
+      <c r="L73" s="17" t="inlineStr">
         <is>
           <t>标签页出现咨询单标签测试</t>
         </is>
       </c>
-      <c r="M73" s="3" t="inlineStr">
+      <c r="M73" s="17" t="inlineStr">
         <is>
           <t>咨询单标签测试</t>
         </is>
       </c>
-      <c r="N73" s="3" t="inlineStr">
+      <c r="N73" s="17" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O73" s="3" t="n">
+      <c r="O73" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="P73" s="3" t="inlineStr">
+      <c r="P73" s="17" t="inlineStr">
         <is>
           <t>需先执行 TC-DETAIL-030 创建咨询单；咨询单记录在诊断结果标签页</t>
         </is>
       </c>
-      <c r="Q73" s="21" t="inlineStr">
+      <c r="Q73" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R73" s="3" t="inlineStr">
+      <c r="R73" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="74" ht="28" customFormat="1" customHeight="1" s="3">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28" customFormat="1" customHeight="1" s="17">
+      <c r="A74" s="17" t="inlineStr">
         <is>
           <t>TC-DETAIL-032</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" s="17" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="17" t="inlineStr">
         <is>
           <t>咨询单-备注标签为空格</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="17" t="inlineStr">
         <is>
           <t>验证咨询单的备注标签添加功能</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E74" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="F74" s="17" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G74" s="10" t="inlineStr">
+      <c r="G74" s="19" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -6986,87 +7795,92 @@
 7.点击保存</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H74" s="17" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 2, .ant-tag:has-text('添加标签'), .ant-tag:has-text('添加标签'), input[placeholder='请输入标签内容'], input[placeholder='请输入标签内容'], button:has-text('保 存')</t>
         </is>
       </c>
-      <c r="I74" s="3" t="inlineStr">
+      <c r="I74" s="17" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify, click, verify, input, click</t>
         </is>
       </c>
-      <c r="J74" s="3" t="inlineStr">
+      <c r="J74" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">咨询单特定| </t>
         </is>
       </c>
-      <c r="L74" s="3" t="inlineStr">
+      <c r="L74" s="17" t="inlineStr">
         <is>
           <t>提示：请输入标签内容</t>
         </is>
       </c>
-      <c r="M74" s="3" t="inlineStr">
+      <c r="M74" s="17" t="inlineStr">
         <is>
           <t>请输入标签内容</t>
         </is>
       </c>
-      <c r="N74" s="3" t="inlineStr">
+      <c r="N74" s="17" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O74" s="3" t="n">
+      <c r="O74" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="P74" s="3" t="inlineStr">
+      <c r="P74" s="17" t="inlineStr">
         <is>
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
       </c>
-      <c r="Q74" s="21" t="inlineStr">
+      <c r="Q74" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R74" s="3" t="inlineStr">
+      <c r="R74" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="75" ht="28" customFormat="1" customHeight="1" s="3">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="28" customFormat="1" customHeight="1" s="17">
+      <c r="A75" s="17" t="inlineStr">
         <is>
           <t>TC-DETAIL-033</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="17" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="17" t="inlineStr">
         <is>
           <t>咨询单-备注标签特殊字符</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D75" s="17" t="inlineStr">
         <is>
           <t>验证咨询单的备注标签添加功能</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E75" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F75" s="17" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G75" s="10" t="inlineStr">
+      <c r="G75" s="19" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7077,87 +7891,92 @@
 7.点击保存</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="H75" s="17" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 2, .ant-tag:has-text('添加标签'), .ant-tag:has-text('添加标签'), input[placeholder='请输入标签内容'], input[placeholder='请输入标签内容'], button:has-text('保 存')</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr">
+      <c r="I75" s="17" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify, click, verify, input, click</t>
         </is>
       </c>
-      <c r="J75" s="3" t="inlineStr">
+      <c r="J75" s="17" t="inlineStr">
         <is>
           <t>咨询单特定|%……&amp;*</t>
         </is>
       </c>
-      <c r="L75" s="3" t="inlineStr">
+      <c r="L75" s="17" t="inlineStr">
         <is>
           <t>标签页出现%……&amp;*</t>
         </is>
       </c>
-      <c r="M75" s="3" t="inlineStr">
+      <c r="M75" s="17" t="inlineStr">
         <is>
           <t>%……&amp;*</t>
         </is>
       </c>
-      <c r="N75" s="3" t="inlineStr">
+      <c r="N75" s="17" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O75" s="3" t="n">
+      <c r="O75" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="P75" s="3" t="inlineStr">
+      <c r="P75" s="17" t="inlineStr">
         <is>
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
       </c>
-      <c r="Q75" s="21" t="inlineStr">
+      <c r="Q75" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R75" s="3" t="inlineStr">
+      <c r="R75" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="76" ht="28" customFormat="1" customHeight="1" s="3">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="28" customFormat="1" customHeight="1" s="17">
+      <c r="A76" s="17" t="inlineStr">
         <is>
           <t>TC-DETAIL-034</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" s="17" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C76" s="17" t="inlineStr">
         <is>
           <t>咨询单-备注标签为空</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>验证标签非空校验</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E76" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="F76" s="17" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G76" s="10" t="inlineStr">
+      <c r="G76" s="19" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7168,87 +7987,92 @@
 7.点击保存</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
+      <c r="H76" s="17" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 3, .ant-tag:has-text('添加标签'), .ant-tag:has-text('添加标签'), input[placeholder='请输入标签内容'], input[placeholder='请输入标签内容'], button:has-text('保 存')</t>
         </is>
       </c>
-      <c r="I76" s="3" t="inlineStr">
+      <c r="I76" s="17" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify, click, verify, input, click</t>
         </is>
       </c>
-      <c r="J76" s="3" t="inlineStr">
+      <c r="J76" s="17" t="inlineStr">
         <is>
           <t>咨询单特定|</t>
         </is>
       </c>
-      <c r="L76" s="3" t="inlineStr">
+      <c r="L76" s="17" t="inlineStr">
         <is>
           <t>提示：请输入标签内容</t>
         </is>
       </c>
-      <c r="M76" s="3" t="inlineStr">
+      <c r="M76" s="17" t="inlineStr">
         <is>
           <t>请输入标签内容</t>
         </is>
       </c>
-      <c r="N76" s="3" t="inlineStr">
+      <c r="N76" s="17" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O76" s="3" t="n">
+      <c r="O76" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="P76" s="3" t="inlineStr">
+      <c r="P76" s="17" t="inlineStr">
         <is>
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
       </c>
-      <c r="Q76" s="21" t="inlineStr">
+      <c r="Q76" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R76" s="3" t="inlineStr">
+      <c r="R76" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="77" ht="28" customFormat="1" customHeight="1" s="3">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="28" customFormat="1" customHeight="1" s="17">
+      <c r="A77" s="17" t="inlineStr">
         <is>
           <t>TC-DETAIL-035</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B77" s="17" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="17" t="inlineStr">
         <is>
           <t>咨询单-备注输入</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="17" t="inlineStr">
         <is>
           <t>验证备注内容添加</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E77" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="F77" s="17" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G77" s="10" t="inlineStr">
+      <c r="G77" s="19" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7258,87 +8082,92 @@
 6.点击保存</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="H77" s="17" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 2, textarea, textarea, button:has-text('提 交'), text=咨询单备注测试</t>
         </is>
       </c>
-      <c r="I77" s="3" t="inlineStr">
+      <c r="I77" s="17" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify, input, click, verify</t>
         </is>
       </c>
-      <c r="J77" s="3" t="inlineStr">
+      <c r="J77" s="17" t="inlineStr">
         <is>
           <t>咨询单特定|咨询单备注测试</t>
         </is>
       </c>
-      <c r="L77" s="3" t="inlineStr">
+      <c r="L77" s="17" t="inlineStr">
         <is>
           <t>备注记录出现最新的备注</t>
         </is>
       </c>
-      <c r="M77" s="3" t="inlineStr">
+      <c r="M77" s="17" t="inlineStr">
         <is>
           <t>咨询单备注测试</t>
         </is>
       </c>
-      <c r="N77" s="3" t="inlineStr">
+      <c r="N77" s="17" t="inlineStr">
         <is>
           <t>element_visible</t>
         </is>
       </c>
-      <c r="O77" s="3" t="n">
+      <c r="O77" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="P77" s="3" t="inlineStr">
+      <c r="P77" s="17" t="inlineStr">
         <is>
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
       </c>
-      <c r="Q77" s="21" t="inlineStr">
+      <c r="Q77" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R77" s="3" t="inlineStr">
+      <c r="R77" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="78" ht="28" customFormat="1" customHeight="1" s="3">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28" customFormat="1" customHeight="1" s="17">
+      <c r="A78" s="17" t="inlineStr">
         <is>
           <t>TC-DETAIL-036</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B78" s="17" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C78" s="17" t="inlineStr">
         <is>
           <t>咨询单-备注空格</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D78" s="17" t="inlineStr">
         <is>
           <t>验证备注内容添加</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E78" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F78" s="17" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G78" s="10" t="inlineStr">
+      <c r="G78" s="19" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7348,87 +8177,92 @@
 6.点击提交</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="H78" s="17" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 2, textarea, textarea, button:has-text('提 交')</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="I78" s="17" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify, input, verify</t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr">
+      <c r="J78" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">咨询单特定| </t>
         </is>
       </c>
-      <c r="L78" s="3" t="inlineStr">
+      <c r="L78" s="17" t="inlineStr">
         <is>
           <t>提交按钮为灰色，无法提交</t>
         </is>
       </c>
-      <c r="M78" s="3" t="inlineStr">
+      <c r="M78" s="17" t="inlineStr">
         <is>
           <t>提交按钮禁用</t>
         </is>
       </c>
-      <c r="N78" s="3" t="inlineStr">
+      <c r="N78" s="17" t="inlineStr">
         <is>
           <t>element_disabled</t>
         </is>
       </c>
-      <c r="O78" s="3" t="n">
+      <c r="O78" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="P78" s="3" t="inlineStr">
+      <c r="P78" s="17" t="inlineStr">
         <is>
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
       </c>
-      <c r="Q78" s="21" t="inlineStr">
+      <c r="Q78" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R78" s="3" t="inlineStr">
+      <c r="R78" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="79" ht="28" customFormat="1" customHeight="1" s="3">
-      <c r="A79" s="3" t="inlineStr">
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customFormat="1" customHeight="1" s="17">
+      <c r="A79" s="17" t="inlineStr">
         <is>
           <t>TC-DETAIL-037</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" s="17" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C79" s="17" t="inlineStr">
         <is>
           <t>咨询单-删除备注</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D79" s="17" t="inlineStr">
         <is>
           <t>验证备注内容删除</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E79" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F79" s="17" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G79" s="10" t="inlineStr">
+      <c r="G79" s="19" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7440,385 +8274,405 @@
 8.点击确定</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="H79" s="17" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 5, textarea, textarea, button:has-text('提 交'), text=自动化删除测试, .ant-timeline .anticon, 2, text=确定</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr">
+      <c r="I79" s="17" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify, input, click, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J79" s="3" t="inlineStr">
+      <c r="J79" s="17" t="inlineStr">
         <is>
           <t>咨询单特定|自动化删除测试</t>
         </is>
       </c>
-      <c r="L79" s="3" t="inlineStr">
+      <c r="L79" s="17" t="inlineStr">
         <is>
           <t>备注被删除</t>
         </is>
       </c>
-      <c r="M79" s="3" t="inlineStr">
+      <c r="M79" s="17" t="inlineStr">
         <is>
           <t>自动化删除测试</t>
         </is>
       </c>
-      <c r="N79" s="3" t="inlineStr">
+      <c r="N79" s="17" t="inlineStr">
         <is>
           <t>text_hidden</t>
         </is>
       </c>
-      <c r="O79" s="3" t="n">
+      <c r="O79" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="P79" s="3" t="inlineStr">
+      <c r="P79" s="17" t="inlineStr">
         <is>
           <t>自包含用例：先新增固定备注再删除，验证点固定无需随测试数据更新</t>
         </is>
       </c>
-      <c r="Q79" s="21" t="inlineStr">
+      <c r="Q79" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R79" s="3" t="inlineStr">
+      <c r="R79" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="80" ht="28" customFormat="1" customHeight="1" s="4">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="28" customFormat="1" customHeight="1" s="7">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-001</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>进入影像阅览</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>验证页面跳转</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="F80" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="G80" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表，选择有检测记录的顾客 2.点击历史影像条目进入影像阅览</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
+      <c r="H80" s="7" t="inlineStr">
         <is>
           <t>0.5, , 2, 共检测, [data-layout="column"][data-layout-align="center center"]</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr">
+      <c r="I80" s="7" t="inlineStr">
         <is>
           <t>wait, nav, wait, find_click, click</t>
         </is>
       </c>
-      <c r="J80" s="4" t="inlineStr">
+      <c r="J80" s="7" t="inlineStr">
         <is>
           <t>/customer</t>
         </is>
       </c>
-      <c r="K80" s="4" t="inlineStr">
+      <c r="K80" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L80" s="4" t="inlineStr">
+      <c r="L80" s="7" t="inlineStr">
         <is>
           <t>进入影像阅览/皮肤分析页</t>
         </is>
       </c>
-      <c r="M80" s="4" t="inlineStr">
+      <c r="M80" s="7" t="inlineStr">
         <is>
           <t>URL包含'customerModel'</t>
         </is>
       </c>
-      <c r="N80" s="4" t="inlineStr">
+      <c r="N80" s="7" t="inlineStr">
         <is>
           <t>url_contains</t>
         </is>
       </c>
-      <c r="O80" s="4" t="n">
+      <c r="O80" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Q80" s="11" t="inlineStr">
+      <c r="Q80" s="20" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R80" s="4" t="inlineStr">
+      <c r="R80" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="81" ht="28" customFormat="1" customHeight="1" s="4">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="28" customFormat="1" customHeight="1" s="7">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-002</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>分屏对比</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>验证模式图切换</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G81" s="4" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>1.点击模式对比中的分屏对比</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr">
+      <c r="H81" s="7" t="inlineStr">
         <is>
           <t>0.5, , 2, 共检测, [data-layout="column"][data-layout-align="center center"], text=分屏对比</t>
         </is>
       </c>
-      <c r="I81" s="4" t="inlineStr">
+      <c r="I81" s="7" t="inlineStr">
         <is>
           <t>wait, nav, wait, find_click, click, click</t>
         </is>
       </c>
-      <c r="J81" s="4" t="inlineStr">
+      <c r="J81" s="7" t="inlineStr">
         <is>
           <t>/customer</t>
         </is>
       </c>
-      <c r="K81" s="4" t="inlineStr">
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L81" s="4" t="inlineStr">
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>影像展示分屏对比模式</t>
         </is>
       </c>
-      <c r="M81" s="4" t="inlineStr">
+      <c r="M81" s="7" t="inlineStr">
         <is>
           <t>'分屏对比'</t>
         </is>
       </c>
-      <c r="N81" s="4" t="inlineStr">
+      <c r="N81" s="7" t="inlineStr">
         <is>
           <t>text_contains</t>
         </is>
       </c>
-      <c r="O81" s="4" t="n">
+      <c r="O81" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Q81" s="11" t="inlineStr">
+      <c r="Q81" s="20" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R81" s="4" t="inlineStr">
+      <c r="R81" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="82" ht="27" customFormat="1" customHeight="1" s="4">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="27" customFormat="1" customHeight="1" s="7">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-003</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>镜像对比</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>验证分屏对比功能</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="E82" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="F82" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="G82" s="7" t="inlineStr">
         <is>
           <t>1.点击模式对比中的镜像对比</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="H82" s="7" t="inlineStr">
         <is>
           <t>0.5, , 2, 共检测, [data-layout="column"][data-layout-align="center center"], text=镜像对比</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr">
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>wait, nav, wait, find_click, click, click</t>
         </is>
       </c>
-      <c r="J82" s="4" t="inlineStr">
+      <c r="J82" s="7" t="inlineStr">
         <is>
           <t>/customer</t>
         </is>
       </c>
-      <c r="K82" s="4" t="inlineStr">
+      <c r="K82" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L82" s="4" t="inlineStr">
+      <c r="L82" s="7" t="inlineStr">
         <is>
           <t>影像展示镜像对比模式</t>
         </is>
       </c>
-      <c r="M82" s="4" t="inlineStr">
+      <c r="M82" s="7" t="inlineStr">
         <is>
           <t>'镜像对比'</t>
         </is>
       </c>
-      <c r="N82" s="4" t="inlineStr">
+      <c r="N82" s="7" t="inlineStr">
         <is>
           <t>text_contains</t>
         </is>
       </c>
-      <c r="O82" s="4" t="n">
+      <c r="O82" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Q82" s="11" t="inlineStr">
+      <c r="Q82" s="20" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R82" s="4" t="inlineStr">
+      <c r="R82" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="83" ht="28" customFormat="1" customHeight="1" s="4">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="28" customFormat="1" customHeight="1" s="7">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-004</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B83" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>历史分屏对比</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>验证镜像对比功能</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="F83" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="G83" s="7" t="inlineStr">
         <is>
           <t>1.点击历史对比中的分屏对比 2.在弹窗中选择一张历史影像 3.点击确定</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr">
+      <c r="H83" s="7" t="inlineStr">
         <is>
           <t>0.5, , 2, 共检测, [data-layout="column"][data-layout-align="center center"], label:has(input[value="historysplitScene"]), text=请选择, [class*="PFozf"], button.ant-btn-primary, 10</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr">
+      <c r="I83" s="7" t="inlineStr">
         <is>
           <t>wait, nav, wait, find_click, click, click, click, click, click, wait</t>
         </is>
       </c>
-      <c r="J83" s="4" t="inlineStr">
+      <c r="J83" s="7" t="inlineStr">
         <is>
           <t>/customer</t>
         </is>
       </c>
-      <c r="K83" s="4" t="inlineStr">
+      <c r="K83" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L83" s="4" t="inlineStr">
+      <c r="L83" s="7" t="inlineStr">
         <is>
           <t>左侧历史影像，右侧当前影像，各有独立模式图</t>
         </is>
       </c>
-      <c r="M83" s="4" t="inlineStr">
+      <c r="M83" s="7" t="inlineStr">
         <is>
           <t>URL包含'customerModel'</t>
         </is>
       </c>
-      <c r="N83" s="4" t="inlineStr">
+      <c r="N83" s="7" t="inlineStr">
         <is>
           <t>url_contains</t>
         </is>
       </c>
-      <c r="O83" s="4" t="n">
+      <c r="O83" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Q83" s="12" t="inlineStr">
+      <c r="Q83" s="21" t="inlineStr">
         <is>
           <t>fail: utils\step_executor.py:170: in _do_click
     element.click(force=True, timeout=self.timeout_ms)
@@ -7828,87 +8682,92 @@
     return await self._frame._click(self._selec</t>
         </is>
       </c>
-      <c r="R83" s="4" t="inlineStr">
+      <c r="R83" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="84" ht="28" customFormat="1" customHeight="1" s="4">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28" customFormat="1" customHeight="1" s="7">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-005</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>历史镜像对比</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>验证历史对比功能</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="G84" s="7" t="inlineStr">
         <is>
           <t>1.点击历史对比中的镜像对比 2.在弹窗中选择一张历史影像 3.点击确定</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr">
+      <c r="H84" s="7" t="inlineStr">
         <is>
           <t>0.5, , 3, 共检测, [data-layout="column"][data-layout-align="center center"], label:has(input[value="historymirror"]), text=请选择, [class*="PFozf"], button.ant-btn-primary, 10</t>
         </is>
       </c>
-      <c r="I84" s="4" t="inlineStr">
+      <c r="I84" s="7" t="inlineStr">
         <is>
           <t>wait, nav, wait, find_click, click, click, click, click, click, wait</t>
         </is>
       </c>
-      <c r="J84" s="4" t="inlineStr">
+      <c r="J84" s="7" t="inlineStr">
         <is>
           <t>/customer</t>
         </is>
       </c>
-      <c r="K84" s="4" t="inlineStr">
+      <c r="K84" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L84" s="4" t="inlineStr">
+      <c r="L84" s="7" t="inlineStr">
         <is>
           <t>展示历史镜像对比模式</t>
         </is>
       </c>
-      <c r="M84" s="4" t="inlineStr">
+      <c r="M84" s="7" t="inlineStr">
         <is>
           <t>URL包含'customerModel'</t>
         </is>
       </c>
-      <c r="N84" s="4" t="inlineStr">
+      <c r="N84" s="7" t="inlineStr">
         <is>
           <t>url_contains</t>
         </is>
       </c>
-      <c r="O84" s="4" t="n">
+      <c r="O84" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Q84" s="12" t="inlineStr">
+      <c r="Q84" s="21" t="inlineStr">
         <is>
           <t>fail: utils\step_executor.py:170: in _do_click
     element.click(force=True, timeout=self.timeout_ms)
@@ -7918,13 +8777,18 @@
     return await self._frame._click(self._selec</t>
         </is>
       </c>
-      <c r="R84" s="4" t="inlineStr">
+      <c r="R84" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="85" ht="28" customHeight="1">
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="28" customHeight="1" s="14">
       <c r="A85" t="inlineStr">
         <is>
           <t>TC-CASE-001</t>
@@ -7993,7 +8857,7 @@
       <c r="O85" t="n">
         <v>5</v>
       </c>
-      <c r="Q85" s="21" t="inlineStr">
+      <c r="Q85" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8003,8 +8867,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="86" ht="28" customHeight="1">
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1" s="14">
       <c r="A86" t="inlineStr">
         <is>
           <t>TC-CASE-002</t>
@@ -8078,7 +8947,7 @@
       <c r="O86" t="n">
         <v>5</v>
       </c>
-      <c r="Q86" s="21" t="inlineStr">
+      <c r="Q86" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8088,8 +8957,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="87" ht="28" customHeight="1">
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1" s="14">
       <c r="A87" t="inlineStr">
         <is>
           <t>TC-CASE-003</t>
@@ -8163,7 +9037,7 @@
       <c r="O87" t="n">
         <v>5</v>
       </c>
-      <c r="Q87" s="21" t="inlineStr">
+      <c r="Q87" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8173,8 +9047,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="88" ht="28" customHeight="1">
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="28" customHeight="1" s="14">
       <c r="A88" t="inlineStr">
         <is>
           <t>TC-CASE-004</t>
@@ -8243,7 +9122,7 @@
       <c r="O88" t="n">
         <v>5</v>
       </c>
-      <c r="Q88" s="21" t="inlineStr">
+      <c r="Q88" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8253,8 +9132,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="89" ht="42" customHeight="1">
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="42" customHeight="1" s="14">
       <c r="A89" t="inlineStr">
         <is>
           <t>TC-CASE-005</t>
@@ -8332,13 +9216,18 @@
 utils\assertion_executor.py:41: in a</t>
         </is>
       </c>
-      <c r="R89" s="9" t="inlineStr">
+      <c r="R89" s="18" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="90" ht="42" customHeight="1">
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="42" customHeight="1" s="14">
       <c r="A90" t="inlineStr">
         <is>
           <t>TC-PROFILE-001</t>
@@ -8413,7 +9302,7 @@
       <c r="O90" t="n">
         <v>3</v>
       </c>
-      <c r="Q90" s="21" t="inlineStr">
+      <c r="Q90" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8423,8 +9312,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="91" ht="28" customHeight="1">
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="28" customHeight="1" s="14">
       <c r="A91" t="inlineStr">
         <is>
           <t>TC-PROFILE-002</t>
@@ -8499,7 +9393,7 @@
       <c r="O91" t="n">
         <v>3</v>
       </c>
-      <c r="Q91" s="21" t="inlineStr">
+      <c r="Q91" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8509,8 +9403,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="92" ht="42" customHeight="1">
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="42" customHeight="1" s="14">
       <c r="A92" t="inlineStr">
         <is>
           <t>TC-PROFILE-003</t>
@@ -8585,7 +9484,7 @@
       <c r="O92" t="n">
         <v>3</v>
       </c>
-      <c r="Q92" s="21" t="inlineStr">
+      <c r="Q92" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8595,8 +9494,13 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="93" ht="28" customHeight="1">
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="28" customHeight="1" s="14">
       <c r="A93" t="inlineStr">
         <is>
           <t>TC-PROFILE-004</t>
@@ -8671,7 +9575,7 @@
       <c r="O93" t="n">
         <v>3</v>
       </c>
-      <c r="Q93" s="21" t="inlineStr">
+      <c r="Q93" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -8681,42 +9585,48 @@
           <t>是</t>
         </is>
       </c>
-    </row>
-    <row r="94" ht="28" customFormat="1" customHeight="1" s="4">
-      <c r="G94" s="13" t="n"/>
-    </row>
-    <row r="95" ht="28" customFormat="1" customHeight="1" s="4">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="28" customFormat="1" customHeight="1" s="7">
+      <c r="G94" s="22" t="n"/>
+      <c r="S94" t="inlineStr"/>
+    </row>
+    <row r="95" ht="28" customFormat="1" customHeight="1" s="7">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-006</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>阅览页加载冒烟</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>验证阅览页加载冒烟</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G95" s="4" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -8725,92 +9635,97 @@
 5.阅览页加载冒烟</t>
         </is>
       </c>
-      <c r="H95" s="4" t="inlineStr">
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=查看案例</t>
         </is>
       </c>
-      <c r="I95" s="4" t="inlineStr">
+      <c r="I95" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify</t>
         </is>
       </c>
-      <c r="J95" s="4" t="inlineStr">
+      <c r="J95" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K95" s="4" t="inlineStr">
+      <c r="K95" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L95" s="4" t="inlineStr">
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>阅览页正常加载，查看案例/查看报告/返回按钮可见</t>
         </is>
       </c>
-      <c r="M95" s="4" t="inlineStr">
+      <c r="M95" s="7" t="inlineStr">
         <is>
           <t>影像阅览页加载成功</t>
         </is>
       </c>
-      <c r="N95" s="4" t="inlineStr">
+      <c r="N95" s="7" t="inlineStr">
         <is>
           <t>element_visible</t>
         </is>
       </c>
-      <c r="O95" s="4" t="n">
+      <c r="O95" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P95" s="4" t="inlineStr">
+      <c r="P95" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q95" s="11" t="inlineStr">
+      <c r="Q95" s="20" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R95" s="4" t="inlineStr">
+      <c r="R95" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="96" ht="28" customFormat="1" customHeight="1" s="4">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="28" customFormat="1" customHeight="1" s="7">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-007</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>视角切换-视角回正</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>验证视角切换-视角回正</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G96" s="4" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -8819,92 +9734,97 @@
 5.视角切换-视角回正</t>
         </is>
       </c>
-      <c r="H96" s="4" t="inlineStr">
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=视角回正</t>
         </is>
       </c>
-      <c r="I96" s="4" t="inlineStr">
+      <c r="I96" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J96" s="4" t="inlineStr">
+      <c r="J96" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K96" s="4" t="inlineStr">
+      <c r="K96" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L96" s="4" t="inlineStr">
+      <c r="L96" s="7" t="inlineStr">
         <is>
           <t>点击「视角回正」视角切换成功</t>
         </is>
       </c>
-      <c r="M96" s="4" t="inlineStr">
+      <c r="M96" s="7" t="inlineStr">
         <is>
           <t>视角回正</t>
         </is>
       </c>
-      <c r="N96" s="4" t="inlineStr">
+      <c r="N96" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O96" s="4" t="n">
+      <c r="O96" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P96" s="4" t="inlineStr">
+      <c r="P96" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q96" s="11" t="inlineStr">
+      <c r="Q96" s="20" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R96" s="4" t="inlineStr">
+      <c r="R96" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="97" ht="28" customFormat="1" customHeight="1" s="4">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="28" customFormat="1" customHeight="1" s="7">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-008</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>视角切换-正面0度</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>验证视角切换-正面0度</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G97" s="4" t="inlineStr">
+      <c r="G97" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -8913,87 +9833,92 @@
 5.视角切换-正面0度</t>
         </is>
       </c>
-      <c r="H97" s="4" t="inlineStr">
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=0°</t>
         </is>
       </c>
-      <c r="I97" s="4" t="inlineStr">
+      <c r="I97" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J97" s="4" t="inlineStr">
+      <c r="J97" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K97" s="4" t="inlineStr">
+      <c r="K97" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L97" s="4" t="inlineStr">
+      <c r="L97" s="7" t="inlineStr">
         <is>
           <t>点击「0°」视角切换成功</t>
         </is>
       </c>
-      <c r="M97" s="4" t="inlineStr">
+      <c r="M97" s="7" t="inlineStr">
         <is>
           <t>0°</t>
         </is>
       </c>
-      <c r="N97" s="4" t="inlineStr">
+      <c r="N97" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O97" s="4" t="n">
+      <c r="O97" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P97" s="4" t="inlineStr">
+      <c r="P97" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R97" s="4" t="inlineStr">
+      <c r="R97" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="98" ht="28" customFormat="1" customHeight="1" s="4">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="28" customFormat="1" customHeight="1" s="7">
+      <c r="A98" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-009</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C98" s="7" t="inlineStr">
         <is>
           <t>视角切换-右45度</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>验证视角切换-右45度</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="F98" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G98" s="4" t="inlineStr">
+      <c r="G98" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9002,87 +9927,92 @@
 5.视角切换-右45度</t>
         </is>
       </c>
-      <c r="H98" s="4" t="inlineStr">
+      <c r="H98" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=R45°</t>
         </is>
       </c>
-      <c r="I98" s="4" t="inlineStr">
+      <c r="I98" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J98" s="4" t="inlineStr">
+      <c r="J98" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K98" s="4" t="inlineStr">
+      <c r="K98" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L98" s="4" t="inlineStr">
+      <c r="L98" s="7" t="inlineStr">
         <is>
           <t>点击「R45°」视角切换成功</t>
         </is>
       </c>
-      <c r="M98" s="4" t="inlineStr">
+      <c r="M98" s="7" t="inlineStr">
         <is>
           <t>R45°</t>
         </is>
       </c>
-      <c r="N98" s="4" t="inlineStr">
+      <c r="N98" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O98" s="4" t="n">
+      <c r="O98" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P98" s="4" t="inlineStr">
+      <c r="P98" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R98" s="4" t="inlineStr">
+      <c r="R98" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="99" ht="28" customFormat="1" customHeight="1" s="4">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="28" customFormat="1" customHeight="1" s="7">
+      <c r="A99" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-010</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>视角切换-左45度</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>验证视角切换-左45度</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G99" s="13" t="inlineStr">
+      <c r="G99" s="22" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9091,87 +10021,92 @@
 5.视角切换-左45度</t>
         </is>
       </c>
-      <c r="H99" s="4" t="inlineStr">
+      <c r="H99" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=L45°</t>
         </is>
       </c>
-      <c r="I99" s="4" t="inlineStr">
+      <c r="I99" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J99" s="4" t="inlineStr">
+      <c r="J99" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K99" s="4" t="inlineStr">
+      <c r="K99" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L99" s="4" t="inlineStr">
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>点击「L45°」视角切换成功</t>
         </is>
       </c>
-      <c r="M99" s="4" t="inlineStr">
+      <c r="M99" s="7" t="inlineStr">
         <is>
           <t>L45°</t>
         </is>
       </c>
-      <c r="N99" s="4" t="inlineStr">
+      <c r="N99" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O99" s="4" t="n">
+      <c r="O99" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P99" s="4" t="inlineStr">
+      <c r="P99" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R99" s="4" t="inlineStr">
+      <c r="R99" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="100" ht="42" customFormat="1" customHeight="1" s="4">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="42" customFormat="1" customHeight="1" s="7">
+      <c r="A100" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-011</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr">
         <is>
           <t>视角切换-右90度</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>验证视角切换-右90度</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="F100" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G100" s="13" t="inlineStr">
+      <c r="G100" s="22" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9180,87 +10115,92 @@
 5.视角切换-右90度</t>
         </is>
       </c>
-      <c r="H100" s="4" t="inlineStr">
+      <c r="H100" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=R90°</t>
         </is>
       </c>
-      <c r="I100" s="4" t="inlineStr">
+      <c r="I100" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J100" s="4" t="inlineStr">
+      <c r="J100" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K100" s="4" t="inlineStr">
+      <c r="K100" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L100" s="4" t="inlineStr">
+      <c r="L100" s="7" t="inlineStr">
         <is>
           <t>点击「R90°」视角切换成功</t>
         </is>
       </c>
-      <c r="M100" s="4" t="inlineStr">
+      <c r="M100" s="7" t="inlineStr">
         <is>
           <t>R90°</t>
         </is>
       </c>
-      <c r="N100" s="4" t="inlineStr">
+      <c r="N100" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O100" s="4" t="n">
+      <c r="O100" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P100" s="4" t="inlineStr">
+      <c r="P100" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R100" s="4" t="inlineStr">
+      <c r="R100" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="101" ht="42" customFormat="1" customHeight="1" s="4">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="42" customFormat="1" customHeight="1" s="7">
+      <c r="A101" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-012</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>视角切换-左90度</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>验证视角切换-左90度</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G101" s="13" t="inlineStr">
+      <c r="G101" s="22" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9269,87 +10209,92 @@
 5.视角切换-左90度</t>
         </is>
       </c>
-      <c r="H101" s="4" t="inlineStr">
+      <c r="H101" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=L90°</t>
         </is>
       </c>
-      <c r="I101" s="4" t="inlineStr">
+      <c r="I101" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J101" s="4" t="inlineStr">
+      <c r="J101" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K101" s="4" t="inlineStr">
+      <c r="K101" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L101" s="4" t="inlineStr">
+      <c r="L101" s="7" t="inlineStr">
         <is>
           <t>点击「L90°」视角切换成功</t>
         </is>
       </c>
-      <c r="M101" s="4" t="inlineStr">
+      <c r="M101" s="7" t="inlineStr">
         <is>
           <t>L90°</t>
         </is>
       </c>
-      <c r="N101" s="4" t="inlineStr">
+      <c r="N101" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O101" s="4" t="n">
+      <c r="O101" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P101" s="4" t="inlineStr">
+      <c r="P101" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R101" s="4" t="inlineStr">
+      <c r="R101" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="102" ht="42" customFormat="1" customHeight="1" s="4">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="42" customFormat="1" customHeight="1" s="7">
+      <c r="A102" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-013</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C102" s="7" t="inlineStr">
         <is>
           <t>光影增强-冷光模式</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-冷光模式</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
+      <c r="E102" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr">
+      <c r="F102" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G102" s="4" t="inlineStr">
+      <c r="G102" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9358,92 +10303,97 @@
 5.光影增强-冷光模式</t>
         </is>
       </c>
-      <c r="H102" s="4" t="inlineStr">
+      <c r="H102" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=冷光</t>
         </is>
       </c>
-      <c r="I102" s="4" t="inlineStr">
+      <c r="I102" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J102" s="4" t="inlineStr">
+      <c r="J102" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K102" s="4" t="inlineStr">
+      <c r="K102" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L102" s="4" t="inlineStr">
+      <c r="L102" s="7" t="inlineStr">
         <is>
           <t>切换到「冷光」图谱模式成功</t>
         </is>
       </c>
-      <c r="M102" s="4" t="inlineStr">
+      <c r="M102" s="7" t="inlineStr">
         <is>
           <t>冷光</t>
         </is>
       </c>
-      <c r="N102" s="4" t="inlineStr">
+      <c r="N102" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O102" s="4" t="n">
+      <c r="O102" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P102" s="4" t="inlineStr">
+      <c r="P102" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q102" s="11" t="inlineStr">
+      <c r="Q102" s="20" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R102" s="4" t="inlineStr">
+      <c r="R102" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="103" customFormat="1" s="4">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" customFormat="1" s="7">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-014</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>光影增强-自然光模式</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-自然光模式</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="F103" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G103" s="4" t="inlineStr">
+      <c r="G103" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9452,87 +10402,92 @@
 5.光影增强-自然光模式</t>
         </is>
       </c>
-      <c r="H103" s="4" t="inlineStr">
+      <c r="H103" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=自然光</t>
         </is>
       </c>
-      <c r="I103" s="4" t="inlineStr">
+      <c r="I103" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J103" s="4" t="inlineStr">
+      <c r="J103" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K103" s="4" t="inlineStr">
+      <c r="K103" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L103" s="4" t="inlineStr">
+      <c r="L103" s="7" t="inlineStr">
         <is>
           <t>切换到「自然光」图谱模式成功</t>
         </is>
       </c>
-      <c r="M103" s="4" t="inlineStr">
+      <c r="M103" s="7" t="inlineStr">
         <is>
           <t>自然光</t>
         </is>
       </c>
-      <c r="N103" s="4" t="inlineStr">
+      <c r="N103" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O103" s="4" t="n">
+      <c r="O103" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P103" s="4" t="inlineStr">
+      <c r="P103" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R103" s="4" t="inlineStr">
+      <c r="R103" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="104" customFormat="1" s="4">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" customFormat="1" s="7">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-015</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>光影增强-红血丝模式</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-红血丝模式</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G104" s="4" t="inlineStr">
+      <c r="G104" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9541,87 +10496,92 @@
 5.光影增强-红血丝模式</t>
         </is>
       </c>
-      <c r="H104" s="4" t="inlineStr">
+      <c r="H104" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=红血丝</t>
         </is>
       </c>
-      <c r="I104" s="4" t="inlineStr">
+      <c r="I104" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J104" s="4" t="inlineStr">
+      <c r="J104" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K104" s="4" t="inlineStr">
+      <c r="K104" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L104" s="4" t="inlineStr">
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>切换到「红血丝」图谱模式成功</t>
         </is>
       </c>
-      <c r="M104" s="4" t="inlineStr">
+      <c r="M104" s="7" t="inlineStr">
         <is>
           <t>红血丝</t>
         </is>
       </c>
-      <c r="N104" s="4" t="inlineStr">
+      <c r="N104" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O104" s="4" t="n">
+      <c r="O104" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P104" s="4" t="inlineStr">
+      <c r="P104" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R104" s="4" t="inlineStr">
+      <c r="R104" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="105" customFormat="1" s="4">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" customFormat="1" s="7">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-016</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="B105" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr">
         <is>
           <t>光影增强-标准红区模式</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-标准红区模式</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr">
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr">
+      <c r="F105" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G105" s="4" t="inlineStr">
+      <c r="G105" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9630,87 +10590,92 @@
 5.光影增强-标准红区模式</t>
         </is>
       </c>
-      <c r="H105" s="4" t="inlineStr">
+      <c r="H105" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=标准红区</t>
         </is>
       </c>
-      <c r="I105" s="4" t="inlineStr">
+      <c r="I105" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J105" s="4" t="inlineStr">
+      <c r="J105" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K105" s="4" t="inlineStr">
+      <c r="K105" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L105" s="4" t="inlineStr">
+      <c r="L105" s="7" t="inlineStr">
         <is>
           <t>切换到「标准红区」图谱模式成功</t>
         </is>
       </c>
-      <c r="M105" s="4" t="inlineStr">
+      <c r="M105" s="7" t="inlineStr">
         <is>
           <t>标准红区</t>
         </is>
       </c>
-      <c r="N105" s="4" t="inlineStr">
+      <c r="N105" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O105" s="4" t="n">
+      <c r="O105" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P105" s="4" t="inlineStr">
+      <c r="P105" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R105" s="4" t="inlineStr">
+      <c r="R105" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="106" customFormat="1" s="4">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" customFormat="1" s="7">
+      <c r="A106" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-017</t>
         </is>
       </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="B106" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr">
         <is>
           <t>光影增强-增强红区模式</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
+      <c r="D106" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-增强红区模式</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
+      <c r="E106" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr">
+      <c r="F106" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G106" s="4" t="inlineStr">
+      <c r="G106" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9719,87 +10684,92 @@
 5.光影增强-增强红区模式</t>
         </is>
       </c>
-      <c r="H106" s="4" t="inlineStr">
+      <c r="H106" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=增强红区</t>
         </is>
       </c>
-      <c r="I106" s="4" t="inlineStr">
+      <c r="I106" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J106" s="4" t="inlineStr">
+      <c r="J106" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K106" s="4" t="inlineStr">
+      <c r="K106" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L106" s="4" t="inlineStr">
+      <c r="L106" s="7" t="inlineStr">
         <is>
           <t>切换到「增强红区」图谱模式成功</t>
         </is>
       </c>
-      <c r="M106" s="4" t="inlineStr">
+      <c r="M106" s="7" t="inlineStr">
         <is>
           <t>增强红区</t>
         </is>
       </c>
-      <c r="N106" s="4" t="inlineStr">
+      <c r="N106" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O106" s="4" t="n">
+      <c r="O106" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P106" s="4" t="inlineStr">
+      <c r="P106" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R106" s="4" t="inlineStr">
+      <c r="R106" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="107" customFormat="1" s="4">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" customFormat="1" s="7">
+      <c r="A107" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-018</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B107" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr">
         <is>
           <t>光影增强-红区热力模式</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="D107" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-红区热力模式</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr">
+      <c r="F107" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G107" s="4" t="inlineStr">
+      <c r="G107" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9808,87 +10778,92 @@
 5.光影增强-红区热力模式</t>
         </is>
       </c>
-      <c r="H107" s="4" t="inlineStr">
+      <c r="H107" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=红区热力</t>
         </is>
       </c>
-      <c r="I107" s="4" t="inlineStr">
+      <c r="I107" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J107" s="4" t="inlineStr">
+      <c r="J107" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K107" s="4" t="inlineStr">
+      <c r="K107" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L107" s="4" t="inlineStr">
+      <c r="L107" s="7" t="inlineStr">
         <is>
           <t>切换到「红区热力」图谱模式成功</t>
         </is>
       </c>
-      <c r="M107" s="4" t="inlineStr">
+      <c r="M107" s="7" t="inlineStr">
         <is>
           <t>红区热力</t>
         </is>
       </c>
-      <c r="N107" s="4" t="inlineStr">
+      <c r="N107" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O107" s="4" t="n">
+      <c r="O107" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P107" s="4" t="inlineStr">
+      <c r="P107" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R107" s="4" t="inlineStr">
+      <c r="R107" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="108" ht="67.5" customFormat="1" customHeight="1" s="4">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="67.5" customFormat="1" customHeight="1" s="7">
+      <c r="A108" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-019</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B108" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C108" s="7" t="inlineStr">
         <is>
           <t>光影增强-标准棕区模式</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="D108" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-标准棕区模式</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
+      <c r="E108" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr">
+      <c r="F108" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G108" s="13" t="inlineStr">
+      <c r="G108" s="22" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9897,87 +10872,92 @@
 5.光影增强-标准棕区模式</t>
         </is>
       </c>
-      <c r="H108" s="4" t="inlineStr">
+      <c r="H108" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=标准棕区</t>
         </is>
       </c>
-      <c r="I108" s="4" t="inlineStr">
+      <c r="I108" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J108" s="4" t="inlineStr">
+      <c r="J108" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K108" s="4" t="inlineStr">
+      <c r="K108" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L108" s="4" t="inlineStr">
+      <c r="L108" s="7" t="inlineStr">
         <is>
           <t>切换到「标准棕区」图谱模式成功</t>
         </is>
       </c>
-      <c r="M108" s="4" t="inlineStr">
+      <c r="M108" s="7" t="inlineStr">
         <is>
           <t>标准棕区</t>
         </is>
       </c>
-      <c r="N108" s="4" t="inlineStr">
+      <c r="N108" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O108" s="4" t="n">
+      <c r="O108" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P108" s="4" t="inlineStr">
+      <c r="P108" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R108" s="4" t="inlineStr">
+      <c r="R108" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="109" ht="67.5" customFormat="1" customHeight="1" s="4">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="67.5" customFormat="1" customHeight="1" s="7">
+      <c r="A109" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-020</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B109" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C109" s="7" t="inlineStr">
         <is>
           <t>光影增强-增强棕区模式</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D109" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-增强棕区模式</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
+      <c r="E109" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr">
+      <c r="F109" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G109" s="13" t="inlineStr">
+      <c r="G109" s="22" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9986,87 +10966,92 @@
 5.光影增强-增强棕区模式</t>
         </is>
       </c>
-      <c r="H109" s="4" t="inlineStr">
+      <c r="H109" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=增强棕区</t>
         </is>
       </c>
-      <c r="I109" s="4" t="inlineStr">
+      <c r="I109" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J109" s="4" t="inlineStr">
+      <c r="J109" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K109" s="4" t="inlineStr">
+      <c r="K109" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L109" s="4" t="inlineStr">
+      <c r="L109" s="7" t="inlineStr">
         <is>
           <t>切换到「增强棕区」图谱模式成功</t>
         </is>
       </c>
-      <c r="M109" s="4" t="inlineStr">
+      <c r="M109" s="7" t="inlineStr">
         <is>
           <t>增强棕区</t>
         </is>
       </c>
-      <c r="N109" s="4" t="inlineStr">
+      <c r="N109" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O109" s="4" t="n">
+      <c r="O109" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P109" s="4" t="inlineStr">
+      <c r="P109" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R109" s="4" t="inlineStr">
+      <c r="R109" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="110" customFormat="1" s="4">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" customFormat="1" s="7">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-021</t>
         </is>
       </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C110" s="7" t="inlineStr">
         <is>
           <t>光影增强-深层棕区模式</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
+      <c r="D110" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-深层棕区模式</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
+      <c r="E110" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr">
+      <c r="F110" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G110" s="4" t="inlineStr">
+      <c r="G110" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10075,87 +11060,92 @@
 5.光影增强-深层棕区模式</t>
         </is>
       </c>
-      <c r="H110" s="4" t="inlineStr">
+      <c r="H110" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=深层棕区</t>
         </is>
       </c>
-      <c r="I110" s="4" t="inlineStr">
+      <c r="I110" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J110" s="4" t="inlineStr">
+      <c r="J110" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K110" s="4" t="inlineStr">
+      <c r="K110" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L110" s="4" t="inlineStr">
+      <c r="L110" s="7" t="inlineStr">
         <is>
           <t>切换到「深层棕区」图谱模式成功</t>
         </is>
       </c>
-      <c r="M110" s="4" t="inlineStr">
+      <c r="M110" s="7" t="inlineStr">
         <is>
           <t>深层棕区</t>
         </is>
       </c>
-      <c r="N110" s="4" t="inlineStr">
+      <c r="N110" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O110" s="4" t="n">
+      <c r="O110" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P110" s="4" t="inlineStr">
+      <c r="P110" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R110" s="4" t="inlineStr">
+      <c r="R110" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="111" ht="67.5" customFormat="1" customHeight="1" s="4">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="67.5" customFormat="1" customHeight="1" s="7">
+      <c r="A111" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-022</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B111" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C111" s="7" t="inlineStr">
         <is>
           <t>光影增强-浅层棕区模式</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="D111" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-浅层棕区模式</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
+      <c r="E111" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr">
+      <c r="F111" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G111" s="13" t="inlineStr">
+      <c r="G111" s="22" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10164,87 +11154,92 @@
 5.光影增强-浅层棕区模式</t>
         </is>
       </c>
-      <c r="H111" s="4" t="inlineStr">
+      <c r="H111" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=浅层棕区</t>
         </is>
       </c>
-      <c r="I111" s="4" t="inlineStr">
+      <c r="I111" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J111" s="4" t="inlineStr">
+      <c r="J111" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K111" s="4" t="inlineStr">
+      <c r="K111" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L111" s="4" t="inlineStr">
+      <c r="L111" s="7" t="inlineStr">
         <is>
           <t>切换到「浅层棕区」图谱模式成功</t>
         </is>
       </c>
-      <c r="M111" s="4" t="inlineStr">
+      <c r="M111" s="7" t="inlineStr">
         <is>
           <t>浅层棕区</t>
         </is>
       </c>
-      <c r="N111" s="4" t="inlineStr">
+      <c r="N111" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O111" s="4" t="n">
+      <c r="O111" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P111" s="4" t="inlineStr">
+      <c r="P111" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R111" s="4" t="inlineStr">
+      <c r="R111" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="112" customFormat="1" s="4">
-      <c r="A112" s="4" t="inlineStr">
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" customFormat="1" s="7">
+      <c r="A112" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-023</t>
         </is>
       </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="B112" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
+      <c r="C112" s="7" t="inlineStr">
         <is>
           <t>光影增强-棕区热力模式</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="D112" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-棕区热力模式</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
+      <c r="E112" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F112" s="4" t="inlineStr">
+      <c r="F112" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G112" s="4" t="inlineStr">
+      <c r="G112" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10253,87 +11248,92 @@
 5.光影增强-棕区热力模式</t>
         </is>
       </c>
-      <c r="H112" s="4" t="inlineStr">
+      <c r="H112" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=棕区热力</t>
         </is>
       </c>
-      <c r="I112" s="4" t="inlineStr">
+      <c r="I112" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J112" s="4" t="inlineStr">
+      <c r="J112" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K112" s="4" t="inlineStr">
+      <c r="K112" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L112" s="4" t="inlineStr">
+      <c r="L112" s="7" t="inlineStr">
         <is>
           <t>切换到「棕区热力」图谱模式成功</t>
         </is>
       </c>
-      <c r="M112" s="4" t="inlineStr">
+      <c r="M112" s="7" t="inlineStr">
         <is>
           <t>棕区热力</t>
         </is>
       </c>
-      <c r="N112" s="4" t="inlineStr">
+      <c r="N112" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O112" s="4" t="n">
+      <c r="O112" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P112" s="4" t="inlineStr">
+      <c r="P112" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R112" s="4" t="inlineStr">
+      <c r="R112" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="113" customFormat="1" s="4">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" customFormat="1" s="7">
+      <c r="A113" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-024</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B113" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C113" s="7" t="inlineStr">
         <is>
           <t>光影增强-紫外线模式</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D113" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-紫外线模式</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
+      <c r="E113" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="F113" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G113" s="4" t="inlineStr">
+      <c r="G113" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10342,87 +11342,92 @@
 5.光影增强-紫外线模式</t>
         </is>
       </c>
-      <c r="H113" s="4" t="inlineStr">
+      <c r="H113" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=紫外线</t>
         </is>
       </c>
-      <c r="I113" s="4" t="inlineStr">
+      <c r="I113" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J113" s="4" t="inlineStr">
+      <c r="J113" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K113" s="4" t="inlineStr">
+      <c r="K113" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L113" s="4" t="inlineStr">
+      <c r="L113" s="7" t="inlineStr">
         <is>
           <t>切换到「紫外线」图谱模式成功</t>
         </is>
       </c>
-      <c r="M113" s="4" t="inlineStr">
+      <c r="M113" s="7" t="inlineStr">
         <is>
           <t>紫外线</t>
         </is>
       </c>
-      <c r="N113" s="4" t="inlineStr">
+      <c r="N113" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O113" s="4" t="n">
+      <c r="O113" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P113" s="4" t="inlineStr">
+      <c r="P113" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R113" s="4" t="inlineStr">
+      <c r="R113" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="114" customFormat="1" s="4">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" customFormat="1" s="7">
+      <c r="A114" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-025</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B114" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C114" s="7" t="inlineStr">
         <is>
           <t>光影增强-紫外线斑模式</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="D114" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-紫外线斑模式</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
+      <c r="E114" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr">
+      <c r="F114" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G114" s="4" t="inlineStr">
+      <c r="G114" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10431,87 +11436,92 @@
 5.光影增强-紫外线斑模式</t>
         </is>
       </c>
-      <c r="H114" s="4" t="inlineStr">
+      <c r="H114" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=紫外线斑</t>
         </is>
       </c>
-      <c r="I114" s="4" t="inlineStr">
+      <c r="I114" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J114" s="4" t="inlineStr">
+      <c r="J114" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K114" s="4" t="inlineStr">
+      <c r="K114" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L114" s="4" t="inlineStr">
+      <c r="L114" s="7" t="inlineStr">
         <is>
           <t>切换到「紫外线斑」图谱模式成功</t>
         </is>
       </c>
-      <c r="M114" s="4" t="inlineStr">
+      <c r="M114" s="7" t="inlineStr">
         <is>
           <t>紫外线斑</t>
         </is>
       </c>
-      <c r="N114" s="4" t="inlineStr">
+      <c r="N114" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O114" s="4" t="n">
+      <c r="O114" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P114" s="4" t="inlineStr">
+      <c r="P114" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R114" s="4" t="inlineStr">
+      <c r="R114" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="115" customFormat="1" s="4">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" customFormat="1" s="7">
+      <c r="A115" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-026</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B115" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C115" s="7" t="inlineStr">
         <is>
           <t>光影增强-平行偏振模式</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D115" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-平行偏振模式</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
+      <c r="E115" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr">
+      <c r="F115" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G115" s="4" t="inlineStr">
+      <c r="G115" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10520,87 +11530,92 @@
 5.光影增强-平行偏振模式</t>
         </is>
       </c>
-      <c r="H115" s="4" t="inlineStr">
+      <c r="H115" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=平行偏振</t>
         </is>
       </c>
-      <c r="I115" s="4" t="inlineStr">
+      <c r="I115" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J115" s="4" t="inlineStr">
+      <c r="J115" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K115" s="4" t="inlineStr">
+      <c r="K115" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L115" s="4" t="inlineStr">
+      <c r="L115" s="7" t="inlineStr">
         <is>
           <t>切换到「平行偏振」图谱模式成功</t>
         </is>
       </c>
-      <c r="M115" s="4" t="inlineStr">
+      <c r="M115" s="7" t="inlineStr">
         <is>
           <t>平行偏振</t>
         </is>
       </c>
-      <c r="N115" s="4" t="inlineStr">
+      <c r="N115" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O115" s="4" t="n">
+      <c r="O115" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P115" s="4" t="inlineStr">
+      <c r="P115" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R115" s="4" t="inlineStr">
+      <c r="R115" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="116" customFormat="1" s="4">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" customFormat="1" s="7">
+      <c r="A116" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-027</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B116" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C116" s="7" t="inlineStr">
         <is>
           <t>光影增强-交叉偏振模式</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D116" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-交叉偏振模式</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
+      <c r="E116" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr">
+      <c r="F116" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G116" s="4" t="inlineStr">
+      <c r="G116" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10609,87 +11624,92 @@
 5.光影增强-交叉偏振模式</t>
         </is>
       </c>
-      <c r="H116" s="4" t="inlineStr">
+      <c r="H116" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=交叉偏振</t>
         </is>
       </c>
-      <c r="I116" s="4" t="inlineStr">
+      <c r="I116" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J116" s="4" t="inlineStr">
+      <c r="J116" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K116" s="4" t="inlineStr">
+      <c r="K116" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L116" s="4" t="inlineStr">
+      <c r="L116" s="7" t="inlineStr">
         <is>
           <t>切换到「交叉偏振」图谱模式成功</t>
         </is>
       </c>
-      <c r="M116" s="4" t="inlineStr">
+      <c r="M116" s="7" t="inlineStr">
         <is>
           <t>交叉偏振</t>
         </is>
       </c>
-      <c r="N116" s="4" t="inlineStr">
+      <c r="N116" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O116" s="4" t="n">
+      <c r="O116" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P116" s="4" t="inlineStr">
+      <c r="P116" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R116" s="4" t="inlineStr">
+      <c r="R116" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="117" customFormat="1" s="4">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" customFormat="1" s="7">
+      <c r="A117" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-028</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B117" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C117" s="7" t="inlineStr">
         <is>
           <t>光影增强-灰度模式</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D117" s="7" t="inlineStr">
         <is>
           <t>验证光影增强-灰度模式</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
+      <c r="E117" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F117" s="4" t="inlineStr">
+      <c r="F117" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G117" s="4" t="inlineStr">
+      <c r="G117" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10698,87 +11718,92 @@
 5.光影增强-灰度模式</t>
         </is>
       </c>
-      <c r="H117" s="4" t="inlineStr">
+      <c r="H117" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=灰度</t>
         </is>
       </c>
-      <c r="I117" s="4" t="inlineStr">
+      <c r="I117" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J117" s="4" t="inlineStr">
+      <c r="J117" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K117" s="4" t="inlineStr">
+      <c r="K117" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L117" s="4" t="inlineStr">
+      <c r="L117" s="7" t="inlineStr">
         <is>
           <t>切换到「灰度」图谱模式成功</t>
         </is>
       </c>
-      <c r="M117" s="4" t="inlineStr">
+      <c r="M117" s="7" t="inlineStr">
         <is>
           <t>灰度</t>
         </is>
       </c>
-      <c r="N117" s="4" t="inlineStr">
+      <c r="N117" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O117" s="4" t="n">
+      <c r="O117" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P117" s="4" t="inlineStr">
+      <c r="P117" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R117" s="4" t="inlineStr">
+      <c r="R117" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="118" ht="67.5" customFormat="1" customHeight="1" s="4">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="67.5" customFormat="1" customHeight="1" s="7">
+      <c r="A118" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-029</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C118" s="7" t="inlineStr">
         <is>
           <t>模式对比-无对比</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D118" s="7" t="inlineStr">
         <is>
           <t>验证模式对比-无对比</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
+      <c r="E118" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F118" s="4" t="inlineStr">
+      <c r="F118" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G118" s="13" t="inlineStr">
+      <c r="G118" s="22" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10787,87 +11812,92 @@
 5.模式对比-无对比</t>
         </is>
       </c>
-      <c r="H118" s="4" t="inlineStr">
+      <c r="H118" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=无对比</t>
         </is>
       </c>
-      <c r="I118" s="4" t="inlineStr">
+      <c r="I118" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J118" s="4" t="inlineStr">
+      <c r="J118" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K118" s="4" t="inlineStr">
+      <c r="K118" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L118" s="4" t="inlineStr">
+      <c r="L118" s="7" t="inlineStr">
         <is>
           <t>默认无对比模式正常</t>
         </is>
       </c>
-      <c r="M118" s="4" t="inlineStr">
+      <c r="M118" s="7" t="inlineStr">
         <is>
           <t>无对比</t>
         </is>
       </c>
-      <c r="N118" s="4" t="inlineStr">
+      <c r="N118" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O118" s="4" t="n">
+      <c r="O118" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P118" s="4" t="inlineStr">
+      <c r="P118" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R118" s="4" t="inlineStr">
+      <c r="R118" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="119" ht="67.5" customFormat="1" customHeight="1" s="4">
-      <c r="A119" s="4" t="inlineStr">
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="67.5" customFormat="1" customHeight="1" s="7">
+      <c r="A119" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-030</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B119" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C119" s="7" t="inlineStr">
         <is>
           <t>AI综合分析-评分显示</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D119" s="7" t="inlineStr">
         <is>
           <t>验证AI综合分析-评分显示</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
+      <c r="E119" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F119" s="4" t="inlineStr">
+      <c r="F119" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G119" s="13" t="inlineStr">
+      <c r="G119" s="22" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10876,87 +11906,92 @@
 5.AI综合分析-评分显示</t>
         </is>
       </c>
-      <c r="H119" s="4" t="inlineStr">
+      <c r="H119" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=AI综合分析</t>
         </is>
       </c>
-      <c r="I119" s="4" t="inlineStr">
+      <c r="I119" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J119" s="4" t="inlineStr">
+      <c r="J119" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K119" s="4" t="inlineStr">
+      <c r="K119" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L119" s="4" t="inlineStr">
+      <c r="L119" s="7" t="inlineStr">
         <is>
           <t>AI综合分析评分（炎敏/肤色/色素/亮度/红区）正常显示</t>
         </is>
       </c>
-      <c r="M119" s="4" t="inlineStr">
+      <c r="M119" s="7" t="inlineStr">
         <is>
           <t>炎敏</t>
         </is>
       </c>
-      <c r="N119" s="4" t="inlineStr">
+      <c r="N119" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O119" s="4" t="n">
+      <c r="O119" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P119" s="4" t="inlineStr">
+      <c r="P119" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R119" s="4" t="inlineStr">
+      <c r="R119" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-    </row>
-    <row r="120" customFormat="1" s="4">
-      <c r="A120" s="4" t="inlineStr">
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" customFormat="1" s="7">
+      <c r="A120" s="7" t="inlineStr">
         <is>
           <t>TC-IMAGE-031</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B120" s="7" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C120" s="7" t="inlineStr">
         <is>
           <t>AI综合分析-图谱说明</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="D120" s="7" t="inlineStr">
         <is>
           <t>验证AI综合分析-图谱说明</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
+      <c r="E120" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr">
+      <c r="F120" s="7" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G120" s="4" t="inlineStr">
+      <c r="G120" s="7" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10965,52 +12000,57 @@
 5.AI综合分析-图谱说明</t>
         </is>
       </c>
-      <c r="H120" s="4" t="inlineStr">
+      <c r="H120" s="7" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=图谱说明</t>
         </is>
       </c>
-      <c r="I120" s="4" t="inlineStr">
+      <c r="I120" s="7" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J120" s="4" t="inlineStr">
+      <c r="J120" s="7" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K120" s="4" t="inlineStr">
+      <c r="K120" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L120" s="4" t="inlineStr">
+      <c r="L120" s="7" t="inlineStr">
         <is>
           <t>图谱说明面板正常打开</t>
         </is>
       </c>
-      <c r="M120" s="4" t="inlineStr">
+      <c r="M120" s="7" t="inlineStr">
         <is>
           <t>图谱说明</t>
         </is>
       </c>
-      <c r="N120" s="4" t="inlineStr">
+      <c r="N120" s="7" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O120" s="4" t="n">
+      <c r="O120" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="P120" s="4" t="inlineStr">
+      <c r="P120" s="7" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R120" s="4" t="inlineStr">
+      <c r="R120" s="7" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -11097,7 +12137,7 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q121" s="21" t="inlineStr">
+      <c r="Q121" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -11105,6 +12145,11 @@
       <c r="R121" t="inlineStr">
         <is>
           <t>是</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -11191,7 +12236,7 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q122" s="21" t="inlineStr">
+      <c r="Q122" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -11199,6 +12244,11 @@
       <c r="R122" t="inlineStr">
         <is>
           <t>是</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -11285,7 +12335,7 @@
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q123" s="21" t="inlineStr">
+      <c r="Q123" s="23" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -11295,8 +12345,18 @@
           <t>是</t>
         </is>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="S2:S123" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"A,B,SERIAL,AUTO"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11307,11 +12367,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="3"/>
+    <col width="15" customWidth="1" style="14" min="1" max="1"/>
+    <col width="40" customWidth="1" style="14" min="2" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11598,6 +12658,23 @@
         </is>
       </c>
       <c r="C17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="34" customHeight="1" s="14">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>执行分组</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>并发分组：A/B；共享数据用 SERIAL；AUTO 或空值按模块自动分配</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11611,11 +12688,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" style="14" min="1" max="1"/>
+    <col width="30" customWidth="1" style="14" min="2" max="2"/>
+    <col width="50" customWidth="1" style="14" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11919,11 +12996,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" style="14" min="1" max="1"/>
+    <col width="20" customWidth="1" style="14" min="2" max="2"/>
+    <col width="50" customWidth="1" style="14" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/test_cases/test_case.xlsx
+++ b/test_cases/test_case.xlsx
@@ -2,6 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet name="自动化测试用例" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="字段说明" sheetId="2" state="visible" r:id="rId2"/>
@@ -9,13 +12,14 @@
     <sheet name="操作类型说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="27">
+  <fonts count="32">
     <font>
       <name val="宋体"/>
       <color theme="1"/>
@@ -23,142 +27,201 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="15"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FF3F3F76"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FF3F3F3F"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FF9C6500"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color theme="0"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+    </font>
     <font/>
+    <font>
+      <b val="1"/>
+      <color rgb="FF9C0006"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -227,17 +290,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998"/>
+        <fgColor theme="4" tint="0.7999511703848384"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999"/>
+        <fgColor theme="4" tint="0.5999633777886288"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39998"/>
+        <fgColor theme="4" tint="0.3999755851924192"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
@@ -247,17 +313,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998"/>
+        <fgColor theme="5" tint="0.7999511703848384"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999"/>
+        <fgColor theme="5" tint="0.5999633777886288"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39998"/>
+        <fgColor theme="5" tint="0.3999755851924192"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
@@ -267,17 +336,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998"/>
+        <fgColor theme="6" tint="0.7999511703848384"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999"/>
+        <fgColor theme="6" tint="0.5999633777886288"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39998"/>
+        <fgColor theme="6" tint="0.3999755851924192"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
@@ -287,17 +359,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998"/>
+        <fgColor theme="7" tint="0.7999511703848384"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999"/>
+        <fgColor theme="7" tint="0.5999633777886288"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39998"/>
+        <fgColor theme="7" tint="0.3999755851924192"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
@@ -307,17 +382,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998"/>
+        <fgColor theme="8" tint="0.7999511703848384"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999"/>
+        <fgColor theme="8" tint="0.5999633777886288"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39998"/>
+        <fgColor theme="8" tint="0.3999755851924192"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
@@ -327,22 +405,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998"/>
+        <fgColor theme="9" tint="0.7999511703848384"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999"/>
+        <fgColor theme="9" tint="0.5999633777886288"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39998"/>
+        <fgColor theme="9" tint="0.3999755851924192"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="10">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color auto="1"/>
@@ -356,6 +455,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -370,16 +470,25 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.49998"/>
+        <color theme="4" tint="0.499954222235786"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -394,6 +503,7 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -408,6 +518,7 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -422,45 +533,56 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="25" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="25" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="44" fontId="24" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="24" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="25" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="41" fontId="24" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="25" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="42" fontId="24" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
@@ -469,130 +591,125 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -602,32 +719,31 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1"/>
     <cellStyle name="货币" xfId="2"/>
     <cellStyle name="百分比" xfId="3"/>
@@ -677,186 +793,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39998"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39998"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39998"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39998"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39998"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39998"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -1137,6 +1074,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1147,114 +1086,114 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S123"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="25.8166675567627" customWidth="1" style="14" min="1" max="1"/>
-    <col width="12" customWidth="1" style="14" min="2" max="2"/>
-    <col width="25" customWidth="1" style="14" min="3" max="3"/>
-    <col width="20" customWidth="1" style="14" min="4" max="4"/>
-    <col width="8" customWidth="1" style="14" min="5" max="5"/>
-    <col width="25" customWidth="1" style="14" min="6" max="6"/>
-    <col width="40" customWidth="1" style="14" min="7" max="7"/>
-    <col width="45" customWidth="1" style="14" min="8" max="8"/>
-    <col width="18" customWidth="1" style="14" min="9" max="9"/>
-    <col width="25" customWidth="1" style="14" min="10" max="10"/>
-    <col width="12" customWidth="1" style="14" min="11" max="11"/>
-    <col width="35" customWidth="1" style="14" min="12" max="13"/>
-    <col width="15" customWidth="1" style="14" min="14" max="14"/>
-    <col width="10" customWidth="1" style="14" min="15" max="15"/>
-    <col width="20" customWidth="1" style="14" min="16" max="16"/>
-    <col width="14.44999980926514" customWidth="1" style="14" min="17" max="17"/>
-    <col width="12" customWidth="1" style="14" min="19" max="19"/>
+    <col width="25.81640625" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="12" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="14.453125" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>用例ID</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>模块</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>测试场景</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>测试点</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>前置条件</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>操作步骤</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>元素定位器</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>操作类型</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>输入数据</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>数据类型</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>期望结果</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>验证点</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>断言类型</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>超时(秒)</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="Q1" s="8" t="inlineStr">
         <is>
           <t>实际结果</t>
         </is>
       </c>
-      <c r="R1" s="7" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>是否执行</t>
         </is>
@@ -1265,7 +1204,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" s="14">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>TC-LOGIN-001</t>
@@ -1361,7 +1300,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1" s="14">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>TC-LOGIN-002</t>
@@ -1458,7 +1397,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" s="14">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>TC-LOGIN-003</t>
@@ -1549,7 +1488,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1" s="14">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>TC-LOGIN-004</t>
@@ -1641,7 +1580,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1" s="14">
+    <row r="6" ht="56" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>TC-LOGIN-005</t>
@@ -1734,7 +1673,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1" s="14">
+    <row r="7" ht="56" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>TC-LOGIN-006</t>
@@ -1820,7 +1759,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1" s="14">
+    <row r="8" ht="56" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>TC-LOGIN-007</t>
@@ -1918,7 +1857,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1" s="14">
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>TC-HOME-001</t>
@@ -2003,7 +1942,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1" s="14">
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>TC-HOME-002</t>
@@ -2034,7 +1973,7 @@
           <t>已登录成功</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>1.在搜索框输入不存在的用户名
 2.点击搜索</t>
@@ -2094,7 +2033,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1" s="14">
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>TC-HOME-003</t>
@@ -2125,7 +2064,7 @@
           <t>已登录成功</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>1.在搜索框输入不存在的手机号
 2.点击搜索</t>
@@ -2183,7 +2122,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1" s="14">
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>TC-HOME-004</t>
@@ -2274,7 +2213,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1" s="14">
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>TC-HOME-005</t>
@@ -2365,7 +2304,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1" s="14">
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>TC-HOME-006</t>
@@ -2454,7 +2393,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1" s="14">
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
           <t>TC-HOME-007</t>
@@ -2543,7 +2482,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1" s="14">
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>TC-HOME-008</t>
@@ -2628,7 +2567,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1" s="14">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>TC-HOME-009</t>
@@ -2713,7 +2652,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1" s="14">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
           <t>TC-HOME-010</t>
@@ -2798,7 +2737,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1" s="14">
+    <row r="19" ht="28" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
           <t>TC-HOME-011</t>
@@ -2883,7 +2822,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1" s="14">
+    <row r="20" ht="28" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
           <t>TC-HOME-012</t>
@@ -2921,7 +2860,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>text=美际学院, , 5</t>
+          <t>text=美际学院, , 3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2968,7 +2907,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1" s="14">
+    <row r="21" ht="28" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-001</t>
@@ -2999,7 +2938,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>1.在搜索框输入不存在的用户名
 2.点击搜索</t>
@@ -3054,7 +2993,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1" s="14">
+    <row r="22" ht="28" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-002</t>
@@ -3085,7 +3024,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>1.在搜索框输入存在的用户名部分
 2.点击搜索</t>
@@ -3140,7 +3079,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1" s="14">
+    <row r="23" ht="28" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-003</t>
@@ -3171,7 +3110,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>1.在搜索框输入存在的用户名
 2.点击搜索</t>
@@ -3226,74 +3165,74 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customFormat="1" customHeight="1" s="17">
-      <c r="A24" s="17" t="inlineStr">
+    <row r="24" ht="28" customFormat="1" customHeight="1" s="4">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-004</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>顾客列表</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>搜索-不存在的手机号</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>验证无结果提示</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>1.在搜索框输入不存在的手机号
 2.点击搜索</t>
         </is>
       </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>/customer, 0.5, input[placeholder='请输入关键字'], button:has-text('搜 索')</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>nav, wait, input, click</t>
         </is>
       </c>
-      <c r="J24" s="17" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>|100000000000</t>
         </is>
       </c>
-      <c r="L24" s="17" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>展示：暂无内容</t>
         </is>
       </c>
-      <c r="M24" s="17" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>'暂无'</t>
         </is>
       </c>
-      <c r="N24" s="17" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O24" s="17" t="n">
+      <c r="O24" s="4" t="n">
         <v>10</v>
       </c>
       <c r="Q24" s="23" t="inlineStr">
@@ -3301,18 +3240,18 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="R24" s="17" t="inlineStr">
+      <c r="R24" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="S24" s="17" t="inlineStr">
+      <c r="S24" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1" s="14">
+    <row r="25" ht="28" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-005</t>
@@ -3343,7 +3282,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>1.在搜索框输入存在的手机号部分
 2.点击搜索</t>
@@ -3398,7 +3337,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1" s="14">
+    <row r="26" ht="28" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-006</t>
@@ -3429,7 +3368,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>1.在搜索框输入存在的手机号
 2.点击搜索</t>
@@ -3484,7 +3423,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1" s="14">
+    <row r="27" ht="28" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-007</t>
@@ -3515,7 +3454,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>1.选择时间范围筛选
 2.选择不存在数据的时间范围</t>
@@ -3570,7 +3509,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1" s="14">
+    <row r="28" ht="28" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-008</t>
@@ -3660,7 +3599,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1" s="14">
+    <row r="29" ht="28" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-009</t>
@@ -3746,7 +3685,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1" s="14">
+    <row r="30" ht="28" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-010</t>
@@ -3823,7 +3762,7 @@
       </c>
       <c r="Q30" s="23" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>pass（全量失败后复跑通过，判定为偶发）</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3837,7 +3776,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1" s="14">
+    <row r="31" ht="28" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-011</t>
@@ -3876,12 +3815,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>/customer, 0.5, button:has-text('其他筛选'), text=保密, .ant-popover .ant-btn-primary, a:has-text('详情')</t>
+          <t>/customer, 0.5, button:has-text('其他筛选'), text=保密, .ant-popover .ant-btn-primary, 3, a:has-text('详情')</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>nav, wait, click, click, click, click</t>
+          <t>nav, wait, click, click, click, wait, click</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3928,7 +3867,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1" s="14">
+    <row r="32" ht="28" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-012</t>
@@ -3970,12 +3909,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>/customer, 0.5, button:has-text('其他筛选'), text=18~25岁, .ant-popover .ant-btn-primary, a:has-text('详情')</t>
+          <t>/customer, 0.5, button:has-text('其他筛选'), text=18~25岁, .ant-popover .ant-btn-primary, 3, a:has-text('详情')</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>nav, wait, click, click, click, click</t>
+          <t>nav, wait, click, click, click, wait, click</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4022,7 +3961,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1" s="14">
+    <row r="33" ht="28" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-013</t>
@@ -4053,7 +3992,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>1.点击其他筛选
 2.选择26~35岁
@@ -4116,8 +4055,8 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="28" customHeight="1" s="14">
-      <c r="A34" t="inlineStr">
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-014</t>
         </is>
@@ -4147,7 +4086,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>1.点击其他筛选
 2.选择36~45岁
@@ -4158,12 +4097,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>/customer, 0.5, button:has-text('其他筛选'), text=36~45岁, .ant-popover .ant-btn-primary, a:has-text('详情')</t>
+          <t>/customer, 0.5, button:has-text('其他筛选'), text=36~45岁, .ant-popover .ant-btn-primary, 3, a:has-text('详情')</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>nav, wait, click, click, click, click</t>
+          <t>nav, wait, click, click, click, wait, click</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4210,7 +4149,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="28" customHeight="1" s="14">
+    <row r="35" ht="28" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-015</t>
@@ -4241,7 +4180,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>1.点击其他筛选
 2.选择45岁以上
@@ -4304,7 +4243,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="28" customHeight="1" s="14">
+    <row r="36" ht="28" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-016</t>
@@ -4398,7 +4337,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1" s="14">
+    <row r="37" ht="28" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-017</t>
@@ -4429,7 +4368,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>1.选择不存在数据的时间范围
 2.点击其他筛选
@@ -4492,7 +4431,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="28" customHeight="1" s="14">
+    <row r="38" ht="28" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-018</t>
@@ -4523,7 +4462,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>1.选择存在数据的时间范围
 2.点击其他筛选
@@ -4586,69 +4525,71 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="28" customHeight="1" s="14">
-      <c r="A39" t="inlineStr">
+    <row r="39" ht="28" customFormat="1" customHeight="1" s="21">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-019</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>顾客列表</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>备注筛选</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="21" t="inlineStr">
         <is>
           <t>验证备注筛选</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="21" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="21" t="inlineStr">
         <is>
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>1.点击其他筛选 2.输入备注'123' 3.点击确定 4.点击详情 5.在历史影像中点击影像右侧备注图标 6.验证备注内容'123'</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>div:text-is('顾客档案'), 0.5, button:has-text('其他筛选'), input[placeholder='备注'], .ant-popover .ant-btn-primary, a:has-text('详情'), .ant-image + div .anticon</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>click, wait, click, input, click, click, click</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.点击其他筛选 2.输入备注'123' 3.点击确定 4.点击详情 5.在历史影像中点击影像右侧备注图标 </t>
+        </is>
+      </c>
+      <c r="H39" s="21" t="inlineStr">
+        <is>
+          <t>div:text-is('顾客档案'), 0.5, button:has-text('其他筛选'), input[placeholder='备注'], .ant-popover .ant-btn-primary</t>
+        </is>
+      </c>
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t>click, wait, click, input, click</t>
+        </is>
+      </c>
+      <c r="J39" s="21" t="inlineStr">
         <is>
           <t>123</t>
         </is>
       </c>
-      <c r="M39" t="n">
-        <v>123</v>
-      </c>
-      <c r="N39" t="inlineStr">
+      <c r="M39" s="21" t="inlineStr">
+        <is>
+          <t>咨询单特定</t>
+        </is>
+      </c>
+      <c r="N39" s="21" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O39" t="n">
-        <v>10</v>
-      </c>
-      <c r="P39" t="inlineStr">
+      <c r="O39" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P39" s="21" t="inlineStr">
         <is>
           <t>已根据实际DOM调整：删除'已为'步骤；确定按钮用.ant-popover .ant-btn-primary；备注图标用.ant-image + div .anticon</t>
         </is>
@@ -4658,18 +4599,18 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R39" s="21" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S39" s="21" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1" s="14">
+    <row r="40" ht="28" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-020</t>
@@ -4700,7 +4641,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客档案列表
 2.查看顾客卡片字段信息</t>
@@ -4760,8 +4701,8 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="28" customHeight="1" s="14">
-      <c r="A41" t="inlineStr">
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-021</t>
         </is>
@@ -4845,7 +4786,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="42" customHeight="1" s="14">
+    <row r="42" ht="42" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
           <t>TC-CUSTOMER-022</t>
@@ -4932,7 +4873,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="42" customHeight="1" s="14">
+    <row r="43" ht="42" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
           <t>TC-DETAIL-001</t>
@@ -4963,7 +4904,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>1.点击编辑资料
 2.清空姓名
@@ -5020,7 +4961,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="56" customHeight="1" s="14">
+    <row r="44" ht="56" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
           <t>TC-DETAIL-002</t>
@@ -5051,7 +4992,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -5099,12 +5040,12 @@
       <c r="O44" t="n">
         <v>15</v>
       </c>
-      <c r="Q44" s="17" t="inlineStr">
+      <c r="Q44" s="4" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R44" s="18" t="inlineStr">
+      <c r="R44" s="10" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -5115,7 +5056,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="56" customHeight="1" s="14">
+    <row r="45" ht="56" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
           <t>TC-DETAIL-003</t>
@@ -5146,7 +5087,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -5208,7 +5149,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="42" customHeight="1" s="14">
+    <row r="46" ht="42" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
           <t>TC-DETAIL-004</t>
@@ -5239,7 +5180,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -5301,7 +5242,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="42" customHeight="1" s="14">
+    <row r="47" ht="42" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
           <t>TC-DETAIL-005</t>
@@ -5332,7 +5273,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G47" s="12" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -5394,7 +5335,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="42" customHeight="1" s="14">
+    <row r="48" ht="42" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
           <t>TC-DETAIL-006</t>
@@ -5425,7 +5366,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -5487,8 +5428,8 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="42" customHeight="1" s="14">
-      <c r="A49" t="inlineStr">
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>TC-DETAIL-007</t>
         </is>
@@ -5518,7 +5459,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G49" s="12" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -5575,8 +5516,8 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="42" customHeight="1" s="14">
-      <c r="A50" t="inlineStr">
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>TC-DETAIL-008</t>
         </is>
@@ -5606,7 +5547,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -5663,7 +5604,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="42" customHeight="1" s="14">
+    <row r="51" ht="42" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
           <t>TC-DETAIL-009</t>
@@ -5694,7 +5635,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G51" s="12" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -5756,7 +5697,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="42" customHeight="1" s="14">
+    <row r="52" ht="42" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
           <t>TC-DETAIL-010</t>
@@ -5787,7 +5728,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -5830,7 +5771,7 @@
       </c>
       <c r="Q52" s="23" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>pass（全量失败后复跑通过，判定为偶发）</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5844,7 +5785,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="42" customHeight="1" s="14">
+    <row r="53" ht="42" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
           <t>TC-DETAIL-011</t>
@@ -5875,7 +5816,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G53" s="12" t="inlineStr">
+      <c r="G53" s="15" t="inlineStr">
         <is>
           <t>1.点击编辑资料
 2.清空手机号
@@ -5931,8 +5872,8 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="42" customHeight="1" s="14">
-      <c r="A54" t="inlineStr">
+    <row r="54" ht="42" customHeight="1">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>TC-DETAIL-012</t>
         </is>
@@ -5962,7 +5903,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G54" s="12" t="inlineStr">
+      <c r="G54" s="15" t="inlineStr">
         <is>
           <t>1.已登录，进入顾客详情页
 2.点击右侧所有影像中的一个影像的右下角编辑图标
@@ -5981,10 +5922,8 @@
           <t>wait, click, find_click, click, input, click</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>测试备注内容</t>
-        </is>
+      <c r="J54" t="n">
+        <v>123</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -5996,14 +5935,14 @@
           <t>备注记录中显示最新的提交记录</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>'测试备注内容'</t>
+      <c r="M54" s="17" t="inlineStr">
+        <is>
+          <t>123</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>text_contains</t>
+          <t>text_visible</t>
         </is>
       </c>
       <c r="O54" t="n">
@@ -6025,7 +5964,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="42" customHeight="1" s="14">
+    <row r="55" ht="42" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
           <t>TC-DETAIL-013</t>
@@ -6056,7 +5995,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G55" s="12" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -6113,7 +6052,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="42" customHeight="1" s="14">
+    <row r="56" ht="42" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
           <t>TC-DETAIL-014</t>
@@ -6144,7 +6083,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -6206,7 +6145,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="42" customHeight="1" s="14">
+    <row r="57" ht="42" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
           <t>TC-DETAIL-015</t>
@@ -6237,7 +6176,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G57" s="12" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.点击编辑资料
@@ -6289,7 +6228,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="28" customHeight="1" s="14">
+    <row r="58" ht="28" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
           <t>TC-DETAIL-016</t>
@@ -6320,7 +6259,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G58" s="12" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -6385,7 +6324,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="28" customHeight="1" s="14">
+    <row r="59" ht="28" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
           <t>TC-DETAIL-017</t>
@@ -6416,7 +6355,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G59" s="12" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -6429,7 +6368,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>div:text-is('顾客档案'), 5, a:has-text('详情'), 2, 共检测|.ant-image + div .anticon, 3, .ant-image + div .anticon, .ant-image + div .anticon, .ant-tag:has-text('添加标签'), .ant-tag:has-text('添加标签'), input[placeholder='请输入标签内容'], button:has-text('保 存')</t>
+          <t>div:text-is('顾客档案'), 3, a:has-text('详情'), 2, 共检测|.ant-image + div .anticon, 3, .ant-image + div .anticon, .ant-image + div .anticon, .ant-tag:has-text('添加标签'), .ant-tag:has-text('添加标签'), input[placeholder='请输入标签内容'], button:has-text('保 存')</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6471,8 +6410,8 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="28" customHeight="1" s="14">
-      <c r="A60" t="inlineStr">
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="14" t="inlineStr">
         <is>
           <t>TC-DETAIL-018</t>
         </is>
@@ -6502,7 +6441,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr">
+      <c r="G60" s="15" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -6546,7 +6485,7 @@
       <c r="O60" t="n">
         <v>15</v>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P60" s="14" t="inlineStr">
         <is>
           <t>nav改为div,输入注意去掉占位符，否则读取不到</t>
         </is>
@@ -6567,7 +6506,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="28" customHeight="1" s="14">
+    <row r="61" ht="28" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
           <t>TC-DETAIL-019</t>
@@ -6598,7 +6537,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G61" s="12" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -6653,7 +6592,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="42" customHeight="1" s="14">
+    <row r="62" ht="42" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
           <t>TC-DETAIL-020</t>
@@ -6684,7 +6623,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G62" s="12" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -6743,7 +6682,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="42" customHeight="1" s="14">
+    <row r="63" ht="42" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
           <t>TC-DETAIL-021</t>
@@ -6774,7 +6713,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G63" s="12" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -6838,7 +6777,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="42" customHeight="1" s="14">
+    <row r="64" ht="42" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
           <t>TC-DETAIL-022</t>
@@ -6869,7 +6808,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G64" s="12" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -6928,7 +6867,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="42" customHeight="1" s="14">
+    <row r="65" ht="42" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
           <t>TC-DETAIL-023</t>
@@ -6959,7 +6898,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G65" s="12" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客详情页
 2.查找有检测记录顾客
@@ -7018,7 +6957,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="42" customHeight="1" s="14">
+    <row r="66" ht="42" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
           <t>TC-DETAIL-024</t>
@@ -7049,7 +6988,7 @@
           <t>已登录并进入顾客列表页</t>
         </is>
       </c>
-      <c r="G66" s="12" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.查找有检测记录顾客
@@ -7107,7 +7046,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="42" customHeight="1" s="14">
+    <row r="67" ht="42" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
           <t>TC-DETAIL-025</t>
@@ -7138,7 +7077,7 @@
           <t>已登录</t>
         </is>
       </c>
-      <c r="G67" s="12" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.查找有检测记录顾客
@@ -7196,7 +7135,7 @@
     self._do_find_</t>
         </is>
       </c>
-      <c r="R67" s="18" t="inlineStr">
+      <c r="R67" s="10" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -7207,7 +7146,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="42" customHeight="1" s="14">
+    <row r="68" ht="42" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
           <t>TC-DETAIL-026</t>
@@ -7238,7 +7177,7 @@
           <t>已登录，进入顾客详情页</t>
         </is>
       </c>
-      <c r="G68" s="12" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>1.点击影像详情
 2.点击编辑资料
@@ -7295,7 +7234,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="42" customHeight="1" s="14">
+    <row r="69" ht="42" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
           <t>TC-DETAIL-027</t>
@@ -7339,17 +7278,17 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, button:has-text('编辑资料'), 2, input[placeholder='请输入手机号'], button:has-text('保 存'), /customer, 3</t>
+          <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, button:has-text('编辑资料'), 2, input[placeholder='请输入手机号'], button:has-text('保 存')</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>click, wait, verify, input, click, wait, verify, click, wait, click, wait, input, click, nav, wait</t>
+          <t>click, wait, verify, input, click, wait, verify, click, wait, click, wait, input, click</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>咨询单特定|13626710399</t>
+          <t>13760228924|13760228924</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7359,7 +7298,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>'13626710399'</t>
+          <t>保存成功</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7386,7 +7325,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="28" customHeight="1" s="14">
+    <row r="70" ht="28" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
           <t>TC-DETAIL-028</t>
@@ -7417,7 +7356,7 @@
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G70" s="12" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>1.点击右下角显示'共检测N次',N&gt;1的卡片的详情按钮
 2.点击管理
@@ -7437,7 +7376,7 @@
           <t>nav, wait, find_click, click, click, click, click, nav, wait</t>
         </is>
       </c>
-      <c r="L70" s="12" t="inlineStr">
+      <c r="L70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">
 该顾客的卡片右下角显示共检测n次,n=详情页中所有历史影像个数</t>
@@ -7461,7 +7400,7 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="R70" s="18" t="inlineStr">
+      <c r="R70" s="10" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -7472,7 +7411,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="28" customHeight="1" s="14">
+    <row r="71" ht="28" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
           <t>TC-DETAIL-029</t>
@@ -7503,7 +7442,7 @@
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G71" s="12" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.查找有检测记录顾客
@@ -7561,38 +7500,38 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="28" customFormat="1" customHeight="1" s="17">
-      <c r="A72" s="17" t="inlineStr">
+    <row r="72" ht="28" customFormat="1" customHeight="1" s="4">
+      <c r="A72" s="16" t="inlineStr">
         <is>
           <t>TC-DETAIL-030</t>
         </is>
       </c>
-      <c r="B72" s="17" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C72" s="17" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>咨询单-添加咨询单</t>
         </is>
       </c>
-      <c r="D72" s="17" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>验证咨询单添加功能</t>
         </is>
       </c>
-      <c r="E72" s="17" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F72" s="17" t="inlineStr">
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G72" s="19" t="inlineStr">
+      <c r="G72" s="9" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7603,40 +7542,40 @@
 7.然后点击前往弹框中的前往顾客档案</t>
         </is>
       </c>
-      <c r="H72" s="17" t="inlineStr">
-        <is>
-          <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=查看报告|text=完 成|[data-layout="column"][data-layout-align="center center"], 2, text=完 成, 5, text=前往顾客档案</t>
-        </is>
-      </c>
-      <c r="I72" s="17" t="inlineStr">
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=查看报告|text=完 成|[data-layout="column"][data-layout-align="center center"], 2, text=完 成, 3, text=前往顾客档案</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, retry_report, wait, click, wait, click</t>
         </is>
       </c>
-      <c r="J72" s="17" t="inlineStr">
+      <c r="J72" s="4" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="L72" s="17" t="inlineStr">
+      <c r="L72" s="4" t="inlineStr">
         <is>
           <t>诊断结果下方出现最新创建的咨询单</t>
         </is>
       </c>
-      <c r="M72" s="17" t="inlineStr">
+      <c r="M72" s="4" t="inlineStr">
         <is>
           <t>咨询单</t>
         </is>
       </c>
-      <c r="N72" s="17" t="inlineStr">
+      <c r="N72" s="4" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O72" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="P72" s="17" t="inlineStr">
+      <c r="O72" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="P72" s="4" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户存在且有历史影像</t>
         </is>
@@ -7646,7 +7585,7 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="R72" s="17" t="inlineStr">
+      <c r="R72" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -7657,38 +7596,38 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="28" customFormat="1" customHeight="1" s="17">
-      <c r="A73" s="17" t="inlineStr">
+    <row r="73" ht="28" customFormat="1" customHeight="1" s="4">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>TC-DETAIL-031</t>
         </is>
       </c>
-      <c r="B73" s="17" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C73" s="17" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>咨询单-备注标签添加</t>
         </is>
       </c>
-      <c r="D73" s="17" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>验证咨询单的备注标签添加功能</t>
         </is>
       </c>
-      <c r="E73" s="17" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F73" s="17" t="inlineStr">
+      <c r="F73" s="4" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G73" s="19" t="inlineStr">
+      <c r="G73" s="9" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7699,40 +7638,40 @@
 7.点击保存</t>
         </is>
       </c>
-      <c r="H73" s="17" t="inlineStr">
+      <c r="H73" s="4" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 2, .ant-tag:has-text('添加标签'), .ant-tag:has-text('添加标签'), input[placeholder='请输入标签内容'], input[placeholder='请输入标签内容'], button:has-text('保 存')</t>
         </is>
       </c>
-      <c r="I73" s="17" t="inlineStr">
+      <c r="I73" s="4" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify, click, verify, input, click</t>
         </is>
       </c>
-      <c r="J73" s="17" t="inlineStr">
+      <c r="J73" s="4" t="inlineStr">
         <is>
           <t>咨询单特定|咨询单标签测试</t>
         </is>
       </c>
-      <c r="L73" s="17" t="inlineStr">
+      <c r="L73" s="4" t="inlineStr">
         <is>
           <t>标签页出现咨询单标签测试</t>
         </is>
       </c>
-      <c r="M73" s="17" t="inlineStr">
+      <c r="M73" s="4" t="inlineStr">
         <is>
           <t>咨询单标签测试</t>
         </is>
       </c>
-      <c r="N73" s="17" t="inlineStr">
+      <c r="N73" s="4" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O73" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="P73" s="17" t="inlineStr">
+      <c r="O73" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="P73" s="4" t="inlineStr">
         <is>
           <t>需先执行 TC-DETAIL-030 创建咨询单；咨询单记录在诊断结果标签页</t>
         </is>
@@ -7742,7 +7681,7 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="R73" s="17" t="inlineStr">
+      <c r="R73" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -7753,38 +7692,38 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="28" customFormat="1" customHeight="1" s="17">
-      <c r="A74" s="17" t="inlineStr">
+    <row r="74" ht="28" customFormat="1" customHeight="1" s="4">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>TC-DETAIL-032</t>
         </is>
       </c>
-      <c r="B74" s="17" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C74" s="17" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>咨询单-备注标签为空格</t>
         </is>
       </c>
-      <c r="D74" s="17" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>验证咨询单的备注标签添加功能</t>
         </is>
       </c>
-      <c r="E74" s="17" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F74" s="17" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G74" s="19" t="inlineStr">
+      <c r="G74" s="9" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7795,40 +7734,40 @@
 7.点击保存</t>
         </is>
       </c>
-      <c r="H74" s="17" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 2, .ant-tag:has-text('添加标签'), .ant-tag:has-text('添加标签'), input[placeholder='请输入标签内容'], input[placeholder='请输入标签内容'], button:has-text('保 存')</t>
         </is>
       </c>
-      <c r="I74" s="17" t="inlineStr">
+      <c r="I74" s="4" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify, click, verify, input, click</t>
         </is>
       </c>
-      <c r="J74" s="17" t="inlineStr">
+      <c r="J74" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">咨询单特定| </t>
         </is>
       </c>
-      <c r="L74" s="17" t="inlineStr">
+      <c r="L74" s="4" t="inlineStr">
         <is>
           <t>提示：请输入标签内容</t>
         </is>
       </c>
-      <c r="M74" s="17" t="inlineStr">
+      <c r="M74" s="4" t="inlineStr">
         <is>
           <t>请输入标签内容</t>
         </is>
       </c>
-      <c r="N74" s="17" t="inlineStr">
+      <c r="N74" s="4" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O74" s="17" t="n">
+      <c r="O74" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="P74" s="17" t="inlineStr">
+      <c r="P74" s="4" t="inlineStr">
         <is>
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
@@ -7838,7 +7777,7 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="R74" s="17" t="inlineStr">
+      <c r="R74" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -7849,38 +7788,38 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="28" customFormat="1" customHeight="1" s="17">
-      <c r="A75" s="17" t="inlineStr">
+    <row r="75" ht="28" customFormat="1" customHeight="1" s="4">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>TC-DETAIL-033</t>
         </is>
       </c>
-      <c r="B75" s="17" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C75" s="17" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>咨询单-备注标签特殊字符</t>
         </is>
       </c>
-      <c r="D75" s="17" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>验证咨询单的备注标签添加功能</t>
         </is>
       </c>
-      <c r="E75" s="17" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F75" s="17" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G75" s="19" t="inlineStr">
+      <c r="G75" s="9" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7891,40 +7830,40 @@
 7.点击保存</t>
         </is>
       </c>
-      <c r="H75" s="17" t="inlineStr">
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 2, .ant-tag:has-text('添加标签'), .ant-tag:has-text('添加标签'), input[placeholder='请输入标签内容'], input[placeholder='请输入标签内容'], button:has-text('保 存')</t>
         </is>
       </c>
-      <c r="I75" s="17" t="inlineStr">
+      <c r="I75" s="4" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify, click, verify, input, click</t>
         </is>
       </c>
-      <c r="J75" s="17" t="inlineStr">
+      <c r="J75" s="4" t="inlineStr">
         <is>
           <t>咨询单特定|%……&amp;*</t>
         </is>
       </c>
-      <c r="L75" s="17" t="inlineStr">
+      <c r="L75" s="4" t="inlineStr">
         <is>
           <t>标签页出现%……&amp;*</t>
         </is>
       </c>
-      <c r="M75" s="17" t="inlineStr">
+      <c r="M75" s="4" t="inlineStr">
         <is>
           <t>%……&amp;*</t>
         </is>
       </c>
-      <c r="N75" s="17" t="inlineStr">
+      <c r="N75" s="4" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O75" s="17" t="n">
+      <c r="O75" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="P75" s="17" t="inlineStr">
+      <c r="P75" s="4" t="inlineStr">
         <is>
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
@@ -7934,7 +7873,7 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="R75" s="17" t="inlineStr">
+      <c r="R75" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -7945,38 +7884,38 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="28" customFormat="1" customHeight="1" s="17">
-      <c r="A76" s="17" t="inlineStr">
+    <row r="76" ht="28" customFormat="1" customHeight="1" s="4">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>TC-DETAIL-034</t>
         </is>
       </c>
-      <c r="B76" s="17" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C76" s="17" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>咨询单-备注标签为空</t>
         </is>
       </c>
-      <c r="D76" s="17" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>验证标签非空校验</t>
         </is>
       </c>
-      <c r="E76" s="17" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F76" s="17" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G76" s="19" t="inlineStr">
+      <c r="G76" s="9" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -7987,40 +7926,40 @@
 7.点击保存</t>
         </is>
       </c>
-      <c r="H76" s="17" t="inlineStr">
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 3, .ant-tag:has-text('添加标签'), .ant-tag:has-text('添加标签'), input[placeholder='请输入标签内容'], input[placeholder='请输入标签内容'], button:has-text('保 存')</t>
         </is>
       </c>
-      <c r="I76" s="17" t="inlineStr">
+      <c r="I76" s="4" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify, click, verify, input, click</t>
         </is>
       </c>
-      <c r="J76" s="17" t="inlineStr">
+      <c r="J76" s="4" t="inlineStr">
         <is>
           <t>咨询单特定|</t>
         </is>
       </c>
-      <c r="L76" s="17" t="inlineStr">
+      <c r="L76" s="4" t="inlineStr">
         <is>
           <t>提示：请输入标签内容</t>
         </is>
       </c>
-      <c r="M76" s="17" t="inlineStr">
+      <c r="M76" s="4" t="inlineStr">
         <is>
           <t>请输入标签内容</t>
         </is>
       </c>
-      <c r="N76" s="17" t="inlineStr">
+      <c r="N76" s="4" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O76" s="17" t="n">
+      <c r="O76" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="P76" s="17" t="inlineStr">
+      <c r="P76" s="4" t="inlineStr">
         <is>
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
@@ -8030,7 +7969,7 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="R76" s="17" t="inlineStr">
+      <c r="R76" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -8041,38 +7980,38 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="28" customFormat="1" customHeight="1" s="17">
-      <c r="A77" s="17" t="inlineStr">
+    <row r="77" ht="28" customFormat="1" customHeight="1" s="4">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>TC-DETAIL-035</t>
         </is>
       </c>
-      <c r="B77" s="17" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C77" s="17" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>咨询单-备注输入</t>
         </is>
       </c>
-      <c r="D77" s="17" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>验证备注内容添加</t>
         </is>
       </c>
-      <c r="E77" s="17" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F77" s="17" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G77" s="19" t="inlineStr">
+      <c r="G77" s="9" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -8082,40 +8021,40 @@
 6.点击保存</t>
         </is>
       </c>
-      <c r="H77" s="17" t="inlineStr">
+      <c r="H77" s="4" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 2, textarea, textarea, button:has-text('提 交'), text=咨询单备注测试</t>
         </is>
       </c>
-      <c r="I77" s="17" t="inlineStr">
+      <c r="I77" s="4" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify, input, click, verify</t>
         </is>
       </c>
-      <c r="J77" s="17" t="inlineStr">
+      <c r="J77" s="4" t="inlineStr">
         <is>
           <t>咨询单特定|咨询单备注测试</t>
         </is>
       </c>
-      <c r="L77" s="17" t="inlineStr">
+      <c r="L77" s="4" t="inlineStr">
         <is>
           <t>备注记录出现最新的备注</t>
         </is>
       </c>
-      <c r="M77" s="17" t="inlineStr">
+      <c r="M77" s="4" t="inlineStr">
         <is>
           <t>咨询单备注测试</t>
         </is>
       </c>
-      <c r="N77" s="17" t="inlineStr">
+      <c r="N77" s="4" t="inlineStr">
         <is>
           <t>element_visible</t>
         </is>
       </c>
-      <c r="O77" s="17" t="n">
+      <c r="O77" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="P77" s="17" t="inlineStr">
+      <c r="P77" s="4" t="inlineStr">
         <is>
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
@@ -8125,7 +8064,7 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="R77" s="17" t="inlineStr">
+      <c r="R77" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -8136,38 +8075,38 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="28" customFormat="1" customHeight="1" s="17">
-      <c r="A78" s="17" t="inlineStr">
+    <row r="78" ht="28" customFormat="1" customHeight="1" s="4">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>TC-DETAIL-036</t>
         </is>
       </c>
-      <c r="B78" s="17" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C78" s="17" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>咨询单-备注空格</t>
         </is>
       </c>
-      <c r="D78" s="17" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>验证备注内容添加</t>
         </is>
       </c>
-      <c r="E78" s="17" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F78" s="17" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G78" s="19" t="inlineStr">
+      <c r="G78" s="9" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -8177,40 +8116,40 @@
 6.点击提交</t>
         </is>
       </c>
-      <c r="H78" s="17" t="inlineStr">
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 2, textarea, textarea, button:has-text('提 交')</t>
         </is>
       </c>
-      <c r="I78" s="17" t="inlineStr">
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify, input, verify</t>
         </is>
       </c>
-      <c r="J78" s="17" t="inlineStr">
+      <c r="J78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">咨询单特定| </t>
         </is>
       </c>
-      <c r="L78" s="17" t="inlineStr">
+      <c r="L78" s="4" t="inlineStr">
         <is>
           <t>提交按钮为灰色，无法提交</t>
         </is>
       </c>
-      <c r="M78" s="17" t="inlineStr">
+      <c r="M78" s="4" t="inlineStr">
         <is>
           <t>提交按钮禁用</t>
         </is>
       </c>
-      <c r="N78" s="17" t="inlineStr">
+      <c r="N78" s="4" t="inlineStr">
         <is>
           <t>element_disabled</t>
         </is>
       </c>
-      <c r="O78" s="17" t="n">
+      <c r="O78" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="P78" s="17" t="inlineStr">
+      <c r="P78" s="4" t="inlineStr">
         <is>
           <t>需先执行 TC-DETAIL-030 创建咨询单</t>
         </is>
@@ -8220,7 +8159,7 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="R78" s="17" t="inlineStr">
+      <c r="R78" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -8231,38 +8170,38 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="28" customFormat="1" customHeight="1" s="17">
-      <c r="A79" s="17" t="inlineStr">
+    <row r="79" ht="28" customFormat="1" customHeight="1" s="4">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>TC-DETAIL-037</t>
         </is>
       </c>
-      <c r="B79" s="17" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>顾客详情</t>
         </is>
       </c>
-      <c r="C79" s="17" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>咨询单-删除备注</t>
         </is>
       </c>
-      <c r="D79" s="17" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>验证备注内容删除</t>
         </is>
       </c>
-      <c r="E79" s="17" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F79" s="17" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>已登录，进入顾客列表页</t>
         </is>
       </c>
-      <c r="G79" s="19" t="inlineStr">
+      <c r="G79" s="9" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.在搜索框搜索咨询单特定用户
@@ -8274,40 +8213,40 @@
 8.点击确定</t>
         </is>
       </c>
-      <c r="H79" s="17" t="inlineStr">
-        <is>
-          <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 5, textarea, textarea, button:has-text('提 交'), text=自动化删除测试, .ant-timeline .anticon, 2, text=确定</t>
-        </is>
-      </c>
-      <c r="I79" s="17" t="inlineStr">
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [role='tabpanel'] .anticon, [role='tabpanel'] .anticon, 3, textarea, textarea, button:has-text('提 交'), text=自动化删除测试${TIMESTAMP}, .ant-timeline .anticon, 2, text=确定</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify, input, click, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J79" s="17" t="inlineStr">
-        <is>
-          <t>咨询单特定|自动化删除测试</t>
-        </is>
-      </c>
-      <c r="L79" s="17" t="inlineStr">
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>咨询单特定|自动化删除测试${TIMESTAMP}</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
         <is>
           <t>备注被删除</t>
         </is>
       </c>
-      <c r="M79" s="17" t="inlineStr">
-        <is>
-          <t>自动化删除测试</t>
-        </is>
-      </c>
-      <c r="N79" s="17" t="inlineStr">
+      <c r="M79" s="4" t="inlineStr">
+        <is>
+          <t>自动化删除测试${TIMESTAMP}</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="inlineStr">
         <is>
           <t>text_hidden</t>
         </is>
       </c>
-      <c r="O79" s="17" t="n">
+      <c r="O79" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="P79" s="17" t="inlineStr">
+      <c r="P79" s="4" t="inlineStr">
         <is>
           <t>自包含用例：先新增固定备注再删除，验证点固定无需随测试数据更新</t>
         </is>
@@ -8317,7 +8256,7 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="R79" s="17" t="inlineStr">
+      <c r="R79" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -8328,86 +8267,86 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="28" customFormat="1" customHeight="1" s="7">
-      <c r="A80" s="7" t="inlineStr">
+    <row r="80" ht="28" customFormat="1" customHeight="1" s="5">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-001</t>
         </is>
       </c>
-      <c r="B80" s="7" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>进入影像阅览</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>验证页面跳转</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F80" s="7" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G80" s="7" t="inlineStr">
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表，选择有检测记录的顾客 2.点击历史影像条目进入影像阅览</t>
         </is>
       </c>
-      <c r="H80" s="7" t="inlineStr">
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>0.5, , 2, 共检测, [data-layout="column"][data-layout-align="center center"]</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>wait, nav, wait, find_click, click</t>
         </is>
       </c>
-      <c r="J80" s="7" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>/customer</t>
         </is>
       </c>
-      <c r="K80" s="7" t="inlineStr">
+      <c r="K80" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L80" s="7" t="inlineStr">
+      <c r="L80" s="5" t="inlineStr">
         <is>
           <t>进入影像阅览/皮肤分析页</t>
         </is>
       </c>
-      <c r="M80" s="7" t="inlineStr">
+      <c r="M80" s="5" t="inlineStr">
         <is>
           <t>URL包含'customerModel'</t>
         </is>
       </c>
-      <c r="N80" s="7" t="inlineStr">
+      <c r="N80" s="5" t="inlineStr">
         <is>
           <t>url_contains</t>
         </is>
       </c>
-      <c r="O80" s="7" t="n">
+      <c r="O80" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q80" s="20" t="inlineStr">
+      <c r="Q80" s="11" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R80" s="7" t="inlineStr">
+      <c r="R80" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -8418,86 +8357,86 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="28" customFormat="1" customHeight="1" s="7">
-      <c r="A81" s="7" t="inlineStr">
+    <row r="81" ht="28" customFormat="1" customHeight="1" s="5">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-002</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>分屏对比</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>验证模式图切换</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr">
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>1.点击模式对比中的分屏对比</t>
         </is>
       </c>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>0.5, , 2, 共检测, [data-layout="column"][data-layout-align="center center"], text=分屏对比</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>wait, nav, wait, find_click, click, click</t>
         </is>
       </c>
-      <c r="J81" s="7" t="inlineStr">
+      <c r="J81" s="5" t="inlineStr">
         <is>
           <t>/customer</t>
         </is>
       </c>
-      <c r="K81" s="7" t="inlineStr">
+      <c r="K81" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L81" s="7" t="inlineStr">
+      <c r="L81" s="5" t="inlineStr">
         <is>
           <t>影像展示分屏对比模式</t>
         </is>
       </c>
-      <c r="M81" s="7" t="inlineStr">
+      <c r="M81" s="5" t="inlineStr">
         <is>
           <t>'分屏对比'</t>
         </is>
       </c>
-      <c r="N81" s="7" t="inlineStr">
+      <c r="N81" s="5" t="inlineStr">
         <is>
           <t>text_contains</t>
         </is>
       </c>
-      <c r="O81" s="7" t="n">
+      <c r="O81" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q81" s="20" t="inlineStr">
+      <c r="Q81" s="11" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R81" s="7" t="inlineStr">
+      <c r="R81" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -8508,86 +8447,86 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="27" customFormat="1" customHeight="1" s="7">
-      <c r="A82" s="7" t="inlineStr">
+    <row r="82" ht="27" customFormat="1" customHeight="1" s="5">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-003</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>镜像对比</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>验证分屏对比功能</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F82" s="7" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G82" s="7" t="inlineStr">
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>1.点击模式对比中的镜像对比</t>
         </is>
       </c>
-      <c r="H82" s="7" t="inlineStr">
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>0.5, , 2, 共检测, [data-layout="column"][data-layout-align="center center"], text=镜像对比</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>wait, nav, wait, find_click, click, click</t>
         </is>
       </c>
-      <c r="J82" s="7" t="inlineStr">
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>/customer</t>
         </is>
       </c>
-      <c r="K82" s="7" t="inlineStr">
+      <c r="K82" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L82" s="7" t="inlineStr">
+      <c r="L82" s="5" t="inlineStr">
         <is>
           <t>影像展示镜像对比模式</t>
         </is>
       </c>
-      <c r="M82" s="7" t="inlineStr">
+      <c r="M82" s="5" t="inlineStr">
         <is>
           <t>'镜像对比'</t>
         </is>
       </c>
-      <c r="N82" s="7" t="inlineStr">
+      <c r="N82" s="5" t="inlineStr">
         <is>
           <t>text_contains</t>
         </is>
       </c>
-      <c r="O82" s="7" t="n">
+      <c r="O82" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q82" s="20" t="inlineStr">
+      <c r="Q82" s="11" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R82" s="7" t="inlineStr">
+      <c r="R82" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -8598,81 +8537,81 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="28" customFormat="1" customHeight="1" s="7">
-      <c r="A83" s="7" t="inlineStr">
+    <row r="83" ht="28" customFormat="1" customHeight="1" s="5">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-004</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>历史分屏对比</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>验证镜像对比功能</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F83" s="7" t="inlineStr">
+      <c r="F83" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr">
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>1.点击历史对比中的分屏对比 2.在弹窗中选择一张历史影像 3.点击确定</t>
         </is>
       </c>
-      <c r="H83" s="7" t="inlineStr">
+      <c r="H83" s="5" t="inlineStr">
         <is>
           <t>0.5, , 2, 共检测, [data-layout="column"][data-layout-align="center center"], label:has(input[value="historysplitScene"]), text=请选择, [class*="PFozf"], button.ant-btn-primary, 10</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
+      <c r="I83" s="5" t="inlineStr">
         <is>
           <t>wait, nav, wait, find_click, click, click, click, click, click, wait</t>
         </is>
       </c>
-      <c r="J83" s="7" t="inlineStr">
+      <c r="J83" s="5" t="inlineStr">
         <is>
           <t>/customer</t>
         </is>
       </c>
-      <c r="K83" s="7" t="inlineStr">
+      <c r="K83" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L83" s="7" t="inlineStr">
+      <c r="L83" s="5" t="inlineStr">
         <is>
           <t>左侧历史影像，右侧当前影像，各有独立模式图</t>
         </is>
       </c>
-      <c r="M83" s="7" t="inlineStr">
+      <c r="M83" s="5" t="inlineStr">
         <is>
           <t>URL包含'customerModel'</t>
         </is>
       </c>
-      <c r="N83" s="7" t="inlineStr">
+      <c r="N83" s="5" t="inlineStr">
         <is>
           <t>url_contains</t>
         </is>
       </c>
-      <c r="O83" s="7" t="n">
+      <c r="O83" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q83" s="21" t="inlineStr">
+      <c r="Q83" s="12" t="inlineStr">
         <is>
           <t>fail: utils\step_executor.py:170: in _do_click
     element.click(force=True, timeout=self.timeout_ms)
@@ -8682,7 +8621,7 @@
     return await self._frame._click(self._selec</t>
         </is>
       </c>
-      <c r="R83" s="7" t="inlineStr">
+      <c r="R83" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -8693,81 +8632,81 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="28" customFormat="1" customHeight="1" s="7">
-      <c r="A84" s="7" t="inlineStr">
+    <row r="84" ht="28" customFormat="1" customHeight="1" s="5">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-005</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>历史镜像对比</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>验证历史对比功能</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F84" s="7" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G84" s="7" t="inlineStr">
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>1.点击历史对比中的镜像对比 2.在弹窗中选择一张历史影像 3.点击确定</t>
         </is>
       </c>
-      <c r="H84" s="7" t="inlineStr">
+      <c r="H84" s="5" t="inlineStr">
         <is>
           <t>0.5, , 3, 共检测, [data-layout="column"][data-layout-align="center center"], label:has(input[value="historymirror"]), text=请选择, [class*="PFozf"], button.ant-btn-primary, 10</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
+      <c r="I84" s="5" t="inlineStr">
         <is>
           <t>wait, nav, wait, find_click, click, click, click, click, click, wait</t>
         </is>
       </c>
-      <c r="J84" s="7" t="inlineStr">
+      <c r="J84" s="5" t="inlineStr">
         <is>
           <t>/customer</t>
         </is>
       </c>
-      <c r="K84" s="7" t="inlineStr">
+      <c r="K84" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L84" s="7" t="inlineStr">
+      <c r="L84" s="5" t="inlineStr">
         <is>
           <t>展示历史镜像对比模式</t>
         </is>
       </c>
-      <c r="M84" s="7" t="inlineStr">
+      <c r="M84" s="5" t="inlineStr">
         <is>
           <t>URL包含'customerModel'</t>
         </is>
       </c>
-      <c r="N84" s="7" t="inlineStr">
+      <c r="N84" s="5" t="inlineStr">
         <is>
           <t>url_contains</t>
         </is>
       </c>
-      <c r="O84" s="7" t="n">
+      <c r="O84" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q84" s="21" t="inlineStr">
+      <c r="Q84" s="12" t="inlineStr">
         <is>
           <t>fail: utils\step_executor.py:170: in _do_click
     element.click(force=True, timeout=self.timeout_ms)
@@ -8777,7 +8716,7 @@
     return await self._frame._click(self._selec</t>
         </is>
       </c>
-      <c r="R84" s="7" t="inlineStr">
+      <c r="R84" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -8788,7 +8727,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="28" customHeight="1" s="14">
+    <row r="85" ht="28" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
           <t>TC-CASE-001</t>
@@ -8873,7 +8812,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="28" customHeight="1" s="14">
+    <row r="86" ht="28" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
           <t>TC-CASE-002</t>
@@ -8963,7 +8902,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="28" customHeight="1" s="14">
+    <row r="87" ht="28" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
           <t>TC-CASE-003</t>
@@ -9053,7 +8992,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="28" customHeight="1" s="14">
+    <row r="88" ht="28" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
           <t>TC-CASE-004</t>
@@ -9138,7 +9077,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="42" customHeight="1" s="14">
+    <row r="89" ht="42" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
           <t>TC-CASE-005</t>
@@ -9216,7 +9155,7 @@
 utils\assertion_executor.py:41: in a</t>
         </is>
       </c>
-      <c r="R89" s="18" t="inlineStr">
+      <c r="R89" s="10" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -9227,7 +9166,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="42" customHeight="1" s="14">
+    <row r="90" ht="42" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
           <t>TC-PROFILE-001</t>
@@ -9318,7 +9257,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="28" customHeight="1" s="14">
+    <row r="91" ht="28" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
           <t>TC-PROFILE-002</t>
@@ -9409,7 +9348,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="42" customHeight="1" s="14">
+    <row r="92" ht="42" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
           <t>TC-PROFILE-003</t>
@@ -9500,7 +9439,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="28" customHeight="1" s="14">
+    <row r="93" ht="28" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
           <t>TC-PROFILE-004</t>
@@ -9591,42 +9530,41 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="28" customFormat="1" customHeight="1" s="7">
-      <c r="G94" s="22" t="n"/>
-      <c r="S94" t="inlineStr"/>
-    </row>
-    <row r="95" ht="28" customFormat="1" customHeight="1" s="7">
-      <c r="A95" s="7" t="inlineStr">
+    <row r="94" ht="28" customFormat="1" customHeight="1" s="5">
+      <c r="G94" s="13" t="n"/>
+    </row>
+    <row r="95" ht="28" customFormat="1" customHeight="1" s="5">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-006</t>
         </is>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>阅览页加载冒烟</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>验证阅览页加载冒烟</t>
         </is>
       </c>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="E95" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
+      <c r="F95" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr">
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9635,55 +9573,55 @@
 5.阅览页加载冒烟</t>
         </is>
       </c>
-      <c r="H95" s="7" t="inlineStr">
+      <c r="H95" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=查看案例</t>
         </is>
       </c>
-      <c r="I95" s="7" t="inlineStr">
+      <c r="I95" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, verify</t>
         </is>
       </c>
-      <c r="J95" s="7" t="inlineStr">
+      <c r="J95" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K95" s="7" t="inlineStr">
+      <c r="K95" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L95" s="7" t="inlineStr">
+      <c r="L95" s="5" t="inlineStr">
         <is>
           <t>阅览页正常加载，查看案例/查看报告/返回按钮可见</t>
         </is>
       </c>
-      <c r="M95" s="7" t="inlineStr">
+      <c r="M95" s="5" t="inlineStr">
         <is>
           <t>影像阅览页加载成功</t>
         </is>
       </c>
-      <c r="N95" s="7" t="inlineStr">
+      <c r="N95" s="5" t="inlineStr">
         <is>
           <t>element_visible</t>
         </is>
       </c>
-      <c r="O95" s="7" t="n">
+      <c r="O95" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P95" s="7" t="inlineStr">
+      <c r="P95" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q95" s="20" t="inlineStr">
+      <c r="Q95" s="11" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R95" s="7" t="inlineStr">
+      <c r="R95" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -9694,38 +9632,38 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="28" customFormat="1" customHeight="1" s="7">
-      <c r="A96" s="7" t="inlineStr">
+    <row r="96" ht="28" customFormat="1" customHeight="1" s="5">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-007</t>
         </is>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>视角切换-视角回正</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>验证视角切换-视角回正</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G96" s="7" t="inlineStr">
+      <c r="G96" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9734,55 +9672,55 @@
 5.视角切换-视角回正</t>
         </is>
       </c>
-      <c r="H96" s="7" t="inlineStr">
+      <c r="H96" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=视角回正</t>
         </is>
       </c>
-      <c r="I96" s="7" t="inlineStr">
+      <c r="I96" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J96" s="7" t="inlineStr">
+      <c r="J96" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K96" s="7" t="inlineStr">
+      <c r="K96" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L96" s="7" t="inlineStr">
+      <c r="L96" s="5" t="inlineStr">
         <is>
           <t>点击「视角回正」视角切换成功</t>
         </is>
       </c>
-      <c r="M96" s="7" t="inlineStr">
+      <c r="M96" s="5" t="inlineStr">
         <is>
           <t>视角回正</t>
         </is>
       </c>
-      <c r="N96" s="7" t="inlineStr">
+      <c r="N96" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O96" s="7" t="n">
+      <c r="O96" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P96" s="7" t="inlineStr">
+      <c r="P96" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q96" s="20" t="inlineStr">
+      <c r="Q96" s="11" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R96" s="7" t="inlineStr">
+      <c r="R96" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -9793,38 +9731,38 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="28" customFormat="1" customHeight="1" s="7">
-      <c r="A97" s="7" t="inlineStr">
+    <row r="97" ht="28" customFormat="1" customHeight="1" s="5">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-008</t>
         </is>
       </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>视角切换-正面0度</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>验证视角切换-正面0度</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F97" s="7" t="inlineStr">
+      <c r="F97" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G97" s="7" t="inlineStr">
+      <c r="G97" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9833,50 +9771,50 @@
 5.视角切换-正面0度</t>
         </is>
       </c>
-      <c r="H97" s="7" t="inlineStr">
+      <c r="H97" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=0°</t>
         </is>
       </c>
-      <c r="I97" s="7" t="inlineStr">
+      <c r="I97" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J97" s="7" t="inlineStr">
+      <c r="J97" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K97" s="7" t="inlineStr">
+      <c r="K97" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L97" s="7" t="inlineStr">
+      <c r="L97" s="5" t="inlineStr">
         <is>
           <t>点击「0°」视角切换成功</t>
         </is>
       </c>
-      <c r="M97" s="7" t="inlineStr">
+      <c r="M97" s="5" t="inlineStr">
         <is>
           <t>0°</t>
         </is>
       </c>
-      <c r="N97" s="7" t="inlineStr">
+      <c r="N97" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O97" s="7" t="n">
+      <c r="O97" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P97" s="7" t="inlineStr">
+      <c r="P97" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R97" s="7" t="inlineStr">
+      <c r="R97" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -9887,38 +9825,38 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="28" customFormat="1" customHeight="1" s="7">
-      <c r="A98" s="7" t="inlineStr">
+    <row r="98" ht="28" customFormat="1" customHeight="1" s="5">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-009</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>视角切换-右45度</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>验证视角切换-右45度</t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F98" s="7" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G98" s="7" t="inlineStr">
+      <c r="G98" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -9927,50 +9865,50 @@
 5.视角切换-右45度</t>
         </is>
       </c>
-      <c r="H98" s="7" t="inlineStr">
+      <c r="H98" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=R45°</t>
         </is>
       </c>
-      <c r="I98" s="7" t="inlineStr">
+      <c r="I98" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J98" s="7" t="inlineStr">
+      <c r="J98" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K98" s="7" t="inlineStr">
+      <c r="K98" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L98" s="7" t="inlineStr">
+      <c r="L98" s="5" t="inlineStr">
         <is>
           <t>点击「R45°」视角切换成功</t>
         </is>
       </c>
-      <c r="M98" s="7" t="inlineStr">
+      <c r="M98" s="5" t="inlineStr">
         <is>
           <t>R45°</t>
         </is>
       </c>
-      <c r="N98" s="7" t="inlineStr">
+      <c r="N98" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O98" s="7" t="n">
+      <c r="O98" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P98" s="7" t="inlineStr">
+      <c r="P98" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R98" s="7" t="inlineStr">
+      <c r="R98" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -9981,38 +9919,38 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="28" customFormat="1" customHeight="1" s="7">
-      <c r="A99" s="7" t="inlineStr">
+    <row r="99" ht="28" customFormat="1" customHeight="1" s="5">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-010</t>
         </is>
       </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>视角切换-左45度</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>验证视角切换-左45度</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F99" s="7" t="inlineStr">
+      <c r="F99" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G99" s="22" t="inlineStr">
+      <c r="G99" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10021,50 +9959,50 @@
 5.视角切换-左45度</t>
         </is>
       </c>
-      <c r="H99" s="7" t="inlineStr">
+      <c r="H99" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=L45°</t>
         </is>
       </c>
-      <c r="I99" s="7" t="inlineStr">
+      <c r="I99" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J99" s="7" t="inlineStr">
+      <c r="J99" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K99" s="7" t="inlineStr">
+      <c r="K99" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L99" s="7" t="inlineStr">
+      <c r="L99" s="5" t="inlineStr">
         <is>
           <t>点击「L45°」视角切换成功</t>
         </is>
       </c>
-      <c r="M99" s="7" t="inlineStr">
+      <c r="M99" s="5" t="inlineStr">
         <is>
           <t>L45°</t>
         </is>
       </c>
-      <c r="N99" s="7" t="inlineStr">
+      <c r="N99" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O99" s="7" t="n">
+      <c r="O99" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P99" s="7" t="inlineStr">
+      <c r="P99" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R99" s="7" t="inlineStr">
+      <c r="R99" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -10075,38 +10013,38 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="42" customFormat="1" customHeight="1" s="7">
-      <c r="A100" s="7" t="inlineStr">
+    <row r="100" ht="42" customFormat="1" customHeight="1" s="5">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-011</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>视角切换-右90度</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>验证视角切换-右90度</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr">
+      <c r="F100" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G100" s="22" t="inlineStr">
+      <c r="G100" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10115,50 +10053,50 @@
 5.视角切换-右90度</t>
         </is>
       </c>
-      <c r="H100" s="7" t="inlineStr">
+      <c r="H100" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=R90°</t>
         </is>
       </c>
-      <c r="I100" s="7" t="inlineStr">
+      <c r="I100" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J100" s="7" t="inlineStr">
+      <c r="J100" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K100" s="7" t="inlineStr">
+      <c r="K100" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L100" s="7" t="inlineStr">
+      <c r="L100" s="5" t="inlineStr">
         <is>
           <t>点击「R90°」视角切换成功</t>
         </is>
       </c>
-      <c r="M100" s="7" t="inlineStr">
+      <c r="M100" s="5" t="inlineStr">
         <is>
           <t>R90°</t>
         </is>
       </c>
-      <c r="N100" s="7" t="inlineStr">
+      <c r="N100" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O100" s="7" t="n">
+      <c r="O100" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P100" s="7" t="inlineStr">
+      <c r="P100" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R100" s="7" t="inlineStr">
+      <c r="R100" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -10169,38 +10107,38 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="42" customFormat="1" customHeight="1" s="7">
-      <c r="A101" s="7" t="inlineStr">
+    <row r="101" ht="42" customFormat="1" customHeight="1" s="5">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-012</t>
         </is>
       </c>
-      <c r="B101" s="7" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C101" s="7" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>视角切换-左90度</t>
         </is>
       </c>
-      <c r="D101" s="7" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>验证视角切换-左90度</t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
+      <c r="E101" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F101" s="7" t="inlineStr">
+      <c r="F101" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G101" s="22" t="inlineStr">
+      <c r="G101" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10209,50 +10147,50 @@
 5.视角切换-左90度</t>
         </is>
       </c>
-      <c r="H101" s="7" t="inlineStr">
+      <c r="H101" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=L90°</t>
         </is>
       </c>
-      <c r="I101" s="7" t="inlineStr">
+      <c r="I101" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J101" s="7" t="inlineStr">
+      <c r="J101" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K101" s="7" t="inlineStr">
+      <c r="K101" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L101" s="7" t="inlineStr">
+      <c r="L101" s="5" t="inlineStr">
         <is>
           <t>点击「L90°」视角切换成功</t>
         </is>
       </c>
-      <c r="M101" s="7" t="inlineStr">
+      <c r="M101" s="5" t="inlineStr">
         <is>
           <t>L90°</t>
         </is>
       </c>
-      <c r="N101" s="7" t="inlineStr">
+      <c r="N101" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O101" s="7" t="n">
+      <c r="O101" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P101" s="7" t="inlineStr">
+      <c r="P101" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R101" s="7" t="inlineStr">
+      <c r="R101" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -10263,38 +10201,38 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="42" customFormat="1" customHeight="1" s="7">
-      <c r="A102" s="7" t="inlineStr">
+    <row r="102" ht="42" customFormat="1" customHeight="1" s="5">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-013</t>
         </is>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>光影增强-冷光模式</t>
         </is>
       </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-冷光模式</t>
         </is>
       </c>
-      <c r="E102" s="7" t="inlineStr">
+      <c r="E102" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F102" s="7" t="inlineStr">
+      <c r="F102" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G102" s="7" t="inlineStr">
+      <c r="G102" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10303,55 +10241,55 @@
 5.光影增强-冷光模式</t>
         </is>
       </c>
-      <c r="H102" s="7" t="inlineStr">
+      <c r="H102" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=冷光</t>
         </is>
       </c>
-      <c r="I102" s="7" t="inlineStr">
+      <c r="I102" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J102" s="7" t="inlineStr">
+      <c r="J102" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K102" s="7" t="inlineStr">
+      <c r="K102" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L102" s="7" t="inlineStr">
+      <c r="L102" s="5" t="inlineStr">
         <is>
           <t>切换到「冷光」图谱模式成功</t>
         </is>
       </c>
-      <c r="M102" s="7" t="inlineStr">
+      <c r="M102" s="5" t="inlineStr">
         <is>
           <t>冷光</t>
         </is>
       </c>
-      <c r="N102" s="7" t="inlineStr">
+      <c r="N102" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O102" s="7" t="n">
+      <c r="O102" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P102" s="7" t="inlineStr">
+      <c r="P102" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="Q102" s="20" t="inlineStr">
+      <c r="Q102" s="11" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="R102" s="7" t="inlineStr">
+      <c r="R102" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -10362,38 +10300,38 @@
         </is>
       </c>
     </row>
-    <row r="103" customFormat="1" s="7">
-      <c r="A103" s="7" t="inlineStr">
+    <row r="103" customFormat="1" s="5">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-014</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>光影增强-自然光模式</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-自然光模式</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E103" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F103" s="7" t="inlineStr">
+      <c r="F103" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G103" s="7" t="inlineStr">
+      <c r="G103" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10402,50 +10340,50 @@
 5.光影增强-自然光模式</t>
         </is>
       </c>
-      <c r="H103" s="7" t="inlineStr">
+      <c r="H103" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=自然光</t>
         </is>
       </c>
-      <c r="I103" s="7" t="inlineStr">
+      <c r="I103" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J103" s="7" t="inlineStr">
+      <c r="J103" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K103" s="7" t="inlineStr">
+      <c r="K103" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L103" s="7" t="inlineStr">
+      <c r="L103" s="5" t="inlineStr">
         <is>
           <t>切换到「自然光」图谱模式成功</t>
         </is>
       </c>
-      <c r="M103" s="7" t="inlineStr">
+      <c r="M103" s="5" t="inlineStr">
         <is>
           <t>自然光</t>
         </is>
       </c>
-      <c r="N103" s="7" t="inlineStr">
+      <c r="N103" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O103" s="7" t="n">
+      <c r="O103" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P103" s="7" t="inlineStr">
+      <c r="P103" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R103" s="7" t="inlineStr">
+      <c r="R103" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -10456,38 +10394,38 @@
         </is>
       </c>
     </row>
-    <row r="104" customFormat="1" s="7">
-      <c r="A104" s="7" t="inlineStr">
+    <row r="104" customFormat="1" s="5">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-015</t>
         </is>
       </c>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B104" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>光影增强-红血丝模式</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr">
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-红血丝模式</t>
         </is>
       </c>
-      <c r="E104" s="7" t="inlineStr">
+      <c r="E104" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F104" s="7" t="inlineStr">
+      <c r="F104" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G104" s="7" t="inlineStr">
+      <c r="G104" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10496,50 +10434,50 @@
 5.光影增强-红血丝模式</t>
         </is>
       </c>
-      <c r="H104" s="7" t="inlineStr">
+      <c r="H104" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=红血丝</t>
         </is>
       </c>
-      <c r="I104" s="7" t="inlineStr">
+      <c r="I104" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J104" s="7" t="inlineStr">
+      <c r="J104" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K104" s="7" t="inlineStr">
+      <c r="K104" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L104" s="7" t="inlineStr">
+      <c r="L104" s="5" t="inlineStr">
         <is>
           <t>切换到「红血丝」图谱模式成功</t>
         </is>
       </c>
-      <c r="M104" s="7" t="inlineStr">
+      <c r="M104" s="5" t="inlineStr">
         <is>
           <t>红血丝</t>
         </is>
       </c>
-      <c r="N104" s="7" t="inlineStr">
+      <c r="N104" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O104" s="7" t="n">
+      <c r="O104" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P104" s="7" t="inlineStr">
+      <c r="P104" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R104" s="7" t="inlineStr">
+      <c r="R104" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -10550,38 +10488,38 @@
         </is>
       </c>
     </row>
-    <row r="105" customFormat="1" s="7">
-      <c r="A105" s="7" t="inlineStr">
+    <row r="105" customFormat="1" s="5">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-016</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B105" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C105" s="5" t="inlineStr">
         <is>
           <t>光影增强-标准红区模式</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-标准红区模式</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="E105" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr">
+      <c r="F105" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G105" s="7" t="inlineStr">
+      <c r="G105" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10590,50 +10528,50 @@
 5.光影增强-标准红区模式</t>
         </is>
       </c>
-      <c r="H105" s="7" t="inlineStr">
+      <c r="H105" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=标准红区</t>
         </is>
       </c>
-      <c r="I105" s="7" t="inlineStr">
+      <c r="I105" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J105" s="7" t="inlineStr">
+      <c r="J105" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K105" s="7" t="inlineStr">
+      <c r="K105" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L105" s="7" t="inlineStr">
+      <c r="L105" s="5" t="inlineStr">
         <is>
           <t>切换到「标准红区」图谱模式成功</t>
         </is>
       </c>
-      <c r="M105" s="7" t="inlineStr">
+      <c r="M105" s="5" t="inlineStr">
         <is>
           <t>标准红区</t>
         </is>
       </c>
-      <c r="N105" s="7" t="inlineStr">
+      <c r="N105" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O105" s="7" t="n">
+      <c r="O105" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P105" s="7" t="inlineStr">
+      <c r="P105" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R105" s="7" t="inlineStr">
+      <c r="R105" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -10644,38 +10582,38 @@
         </is>
       </c>
     </row>
-    <row r="106" customFormat="1" s="7">
-      <c r="A106" s="7" t="inlineStr">
+    <row r="106" customFormat="1" s="5">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-017</t>
         </is>
       </c>
-      <c r="B106" s="7" t="inlineStr">
+      <c r="B106" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C106" s="7" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>光影增强-增强红区模式</t>
         </is>
       </c>
-      <c r="D106" s="7" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-增强红区模式</t>
         </is>
       </c>
-      <c r="E106" s="7" t="inlineStr">
+      <c r="E106" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F106" s="7" t="inlineStr">
+      <c r="F106" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G106" s="7" t="inlineStr">
+      <c r="G106" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10684,50 +10622,50 @@
 5.光影增强-增强红区模式</t>
         </is>
       </c>
-      <c r="H106" s="7" t="inlineStr">
+      <c r="H106" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=增强红区</t>
         </is>
       </c>
-      <c r="I106" s="7" t="inlineStr">
+      <c r="I106" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J106" s="7" t="inlineStr">
+      <c r="J106" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K106" s="7" t="inlineStr">
+      <c r="K106" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L106" s="7" t="inlineStr">
+      <c r="L106" s="5" t="inlineStr">
         <is>
           <t>切换到「增强红区」图谱模式成功</t>
         </is>
       </c>
-      <c r="M106" s="7" t="inlineStr">
+      <c r="M106" s="5" t="inlineStr">
         <is>
           <t>增强红区</t>
         </is>
       </c>
-      <c r="N106" s="7" t="inlineStr">
+      <c r="N106" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O106" s="7" t="n">
+      <c r="O106" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P106" s="7" t="inlineStr">
+      <c r="P106" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R106" s="7" t="inlineStr">
+      <c r="R106" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -10738,38 +10676,38 @@
         </is>
       </c>
     </row>
-    <row r="107" customFormat="1" s="7">
-      <c r="A107" s="7" t="inlineStr">
+    <row r="107" customFormat="1" s="5">
+      <c r="A107" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-018</t>
         </is>
       </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C107" s="7" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>光影增强-红区热力模式</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-红区热力模式</t>
         </is>
       </c>
-      <c r="E107" s="7" t="inlineStr">
+      <c r="E107" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F107" s="7" t="inlineStr">
+      <c r="F107" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G107" s="7" t="inlineStr">
+      <c r="G107" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10778,50 +10716,50 @@
 5.光影增强-红区热力模式</t>
         </is>
       </c>
-      <c r="H107" s="7" t="inlineStr">
+      <c r="H107" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=红区热力</t>
         </is>
       </c>
-      <c r="I107" s="7" t="inlineStr">
+      <c r="I107" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J107" s="7" t="inlineStr">
+      <c r="J107" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K107" s="7" t="inlineStr">
+      <c r="K107" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L107" s="7" t="inlineStr">
+      <c r="L107" s="5" t="inlineStr">
         <is>
           <t>切换到「红区热力」图谱模式成功</t>
         </is>
       </c>
-      <c r="M107" s="7" t="inlineStr">
+      <c r="M107" s="5" t="inlineStr">
         <is>
           <t>红区热力</t>
         </is>
       </c>
-      <c r="N107" s="7" t="inlineStr">
+      <c r="N107" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O107" s="7" t="n">
+      <c r="O107" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P107" s="7" t="inlineStr">
+      <c r="P107" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R107" s="7" t="inlineStr">
+      <c r="R107" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -10832,38 +10770,38 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="67.5" customFormat="1" customHeight="1" s="7">
-      <c r="A108" s="7" t="inlineStr">
+    <row r="108" ht="67.5" customFormat="1" customHeight="1" s="5">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-019</t>
         </is>
       </c>
-      <c r="B108" s="7" t="inlineStr">
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>光影增强-标准棕区模式</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-标准棕区模式</t>
         </is>
       </c>
-      <c r="E108" s="7" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F108" s="7" t="inlineStr">
+      <c r="F108" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G108" s="22" t="inlineStr">
+      <c r="G108" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10872,50 +10810,50 @@
 5.光影增强-标准棕区模式</t>
         </is>
       </c>
-      <c r="H108" s="7" t="inlineStr">
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=标准棕区</t>
         </is>
       </c>
-      <c r="I108" s="7" t="inlineStr">
+      <c r="I108" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J108" s="7" t="inlineStr">
+      <c r="J108" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K108" s="7" t="inlineStr">
+      <c r="K108" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L108" s="7" t="inlineStr">
+      <c r="L108" s="5" t="inlineStr">
         <is>
           <t>切换到「标准棕区」图谱模式成功</t>
         </is>
       </c>
-      <c r="M108" s="7" t="inlineStr">
+      <c r="M108" s="5" t="inlineStr">
         <is>
           <t>标准棕区</t>
         </is>
       </c>
-      <c r="N108" s="7" t="inlineStr">
+      <c r="N108" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O108" s="7" t="n">
+      <c r="O108" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P108" s="7" t="inlineStr">
+      <c r="P108" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R108" s="7" t="inlineStr">
+      <c r="R108" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -10926,38 +10864,38 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="67.5" customFormat="1" customHeight="1" s="7">
-      <c r="A109" s="7" t="inlineStr">
+    <row r="109" ht="67.5" customFormat="1" customHeight="1" s="5">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-020</t>
         </is>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
         <is>
           <t>光影增强-增强棕区模式</t>
         </is>
       </c>
-      <c r="D109" s="7" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-增强棕区模式</t>
         </is>
       </c>
-      <c r="E109" s="7" t="inlineStr">
+      <c r="E109" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F109" s="7" t="inlineStr">
+      <c r="F109" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G109" s="22" t="inlineStr">
+      <c r="G109" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -10966,50 +10904,50 @@
 5.光影增强-增强棕区模式</t>
         </is>
       </c>
-      <c r="H109" s="7" t="inlineStr">
+      <c r="H109" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=增强棕区</t>
         </is>
       </c>
-      <c r="I109" s="7" t="inlineStr">
+      <c r="I109" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J109" s="7" t="inlineStr">
+      <c r="J109" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K109" s="7" t="inlineStr">
+      <c r="K109" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L109" s="7" t="inlineStr">
+      <c r="L109" s="5" t="inlineStr">
         <is>
           <t>切换到「增强棕区」图谱模式成功</t>
         </is>
       </c>
-      <c r="M109" s="7" t="inlineStr">
+      <c r="M109" s="5" t="inlineStr">
         <is>
           <t>增强棕区</t>
         </is>
       </c>
-      <c r="N109" s="7" t="inlineStr">
+      <c r="N109" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O109" s="7" t="n">
+      <c r="O109" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P109" s="7" t="inlineStr">
+      <c r="P109" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R109" s="7" t="inlineStr">
+      <c r="R109" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -11020,38 +10958,38 @@
         </is>
       </c>
     </row>
-    <row r="110" customFormat="1" s="7">
-      <c r="A110" s="7" t="inlineStr">
+    <row r="110" customFormat="1" s="5">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-021</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B110" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C110" s="7" t="inlineStr">
+      <c r="C110" s="5" t="inlineStr">
         <is>
           <t>光影增强-深层棕区模式</t>
         </is>
       </c>
-      <c r="D110" s="7" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-深层棕区模式</t>
         </is>
       </c>
-      <c r="E110" s="7" t="inlineStr">
+      <c r="E110" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F110" s="7" t="inlineStr">
+      <c r="F110" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G110" s="7" t="inlineStr">
+      <c r="G110" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -11060,50 +10998,50 @@
 5.光影增强-深层棕区模式</t>
         </is>
       </c>
-      <c r="H110" s="7" t="inlineStr">
+      <c r="H110" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=深层棕区</t>
         </is>
       </c>
-      <c r="I110" s="7" t="inlineStr">
+      <c r="I110" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J110" s="7" t="inlineStr">
+      <c r="J110" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K110" s="7" t="inlineStr">
+      <c r="K110" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L110" s="7" t="inlineStr">
+      <c r="L110" s="5" t="inlineStr">
         <is>
           <t>切换到「深层棕区」图谱模式成功</t>
         </is>
       </c>
-      <c r="M110" s="7" t="inlineStr">
+      <c r="M110" s="5" t="inlineStr">
         <is>
           <t>深层棕区</t>
         </is>
       </c>
-      <c r="N110" s="7" t="inlineStr">
+      <c r="N110" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O110" s="7" t="n">
+      <c r="O110" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P110" s="7" t="inlineStr">
+      <c r="P110" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R110" s="7" t="inlineStr">
+      <c r="R110" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -11114,38 +11052,38 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="67.5" customFormat="1" customHeight="1" s="7">
-      <c r="A111" s="7" t="inlineStr">
+    <row r="111" ht="67.5" customFormat="1" customHeight="1" s="5">
+      <c r="A111" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-022</t>
         </is>
       </c>
-      <c r="B111" s="7" t="inlineStr">
+      <c r="B111" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C111" s="7" t="inlineStr">
+      <c r="C111" s="5" t="inlineStr">
         <is>
           <t>光影增强-浅层棕区模式</t>
         </is>
       </c>
-      <c r="D111" s="7" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-浅层棕区模式</t>
         </is>
       </c>
-      <c r="E111" s="7" t="inlineStr">
+      <c r="E111" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F111" s="7" t="inlineStr">
+      <c r="F111" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G111" s="22" t="inlineStr">
+      <c r="G111" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -11154,50 +11092,50 @@
 5.光影增强-浅层棕区模式</t>
         </is>
       </c>
-      <c r="H111" s="7" t="inlineStr">
+      <c r="H111" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=浅层棕区</t>
         </is>
       </c>
-      <c r="I111" s="7" t="inlineStr">
+      <c r="I111" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J111" s="7" t="inlineStr">
+      <c r="J111" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K111" s="7" t="inlineStr">
+      <c r="K111" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L111" s="7" t="inlineStr">
+      <c r="L111" s="5" t="inlineStr">
         <is>
           <t>切换到「浅层棕区」图谱模式成功</t>
         </is>
       </c>
-      <c r="M111" s="7" t="inlineStr">
+      <c r="M111" s="5" t="inlineStr">
         <is>
           <t>浅层棕区</t>
         </is>
       </c>
-      <c r="N111" s="7" t="inlineStr">
+      <c r="N111" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O111" s="7" t="n">
+      <c r="O111" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P111" s="7" t="inlineStr">
+      <c r="P111" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R111" s="7" t="inlineStr">
+      <c r="R111" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -11208,38 +11146,38 @@
         </is>
       </c>
     </row>
-    <row r="112" customFormat="1" s="7">
-      <c r="A112" s="7" t="inlineStr">
+    <row r="112" customFormat="1" s="5">
+      <c r="A112" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-023</t>
         </is>
       </c>
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B112" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C112" s="7" t="inlineStr">
+      <c r="C112" s="5" t="inlineStr">
         <is>
           <t>光影增强-棕区热力模式</t>
         </is>
       </c>
-      <c r="D112" s="7" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-棕区热力模式</t>
         </is>
       </c>
-      <c r="E112" s="7" t="inlineStr">
+      <c r="E112" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F112" s="7" t="inlineStr">
+      <c r="F112" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G112" s="7" t="inlineStr">
+      <c r="G112" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -11248,50 +11186,50 @@
 5.光影增强-棕区热力模式</t>
         </is>
       </c>
-      <c r="H112" s="7" t="inlineStr">
+      <c r="H112" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=棕区热力</t>
         </is>
       </c>
-      <c r="I112" s="7" t="inlineStr">
+      <c r="I112" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J112" s="7" t="inlineStr">
+      <c r="J112" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K112" s="7" t="inlineStr">
+      <c r="K112" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L112" s="7" t="inlineStr">
+      <c r="L112" s="5" t="inlineStr">
         <is>
           <t>切换到「棕区热力」图谱模式成功</t>
         </is>
       </c>
-      <c r="M112" s="7" t="inlineStr">
+      <c r="M112" s="5" t="inlineStr">
         <is>
           <t>棕区热力</t>
         </is>
       </c>
-      <c r="N112" s="7" t="inlineStr">
+      <c r="N112" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O112" s="7" t="n">
+      <c r="O112" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P112" s="7" t="inlineStr">
+      <c r="P112" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R112" s="7" t="inlineStr">
+      <c r="R112" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -11302,38 +11240,38 @@
         </is>
       </c>
     </row>
-    <row r="113" customFormat="1" s="7">
-      <c r="A113" s="7" t="inlineStr">
+    <row r="113" customFormat="1" s="5">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-024</t>
         </is>
       </c>
-      <c r="B113" s="7" t="inlineStr">
+      <c r="B113" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C113" s="7" t="inlineStr">
+      <c r="C113" s="5" t="inlineStr">
         <is>
           <t>光影增强-紫外线模式</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr">
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-紫外线模式</t>
         </is>
       </c>
-      <c r="E113" s="7" t="inlineStr">
+      <c r="E113" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F113" s="7" t="inlineStr">
+      <c r="F113" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G113" s="7" t="inlineStr">
+      <c r="G113" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -11342,50 +11280,50 @@
 5.光影增强-紫外线模式</t>
         </is>
       </c>
-      <c r="H113" s="7" t="inlineStr">
+      <c r="H113" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=紫外线</t>
         </is>
       </c>
-      <c r="I113" s="7" t="inlineStr">
+      <c r="I113" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J113" s="7" t="inlineStr">
+      <c r="J113" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K113" s="7" t="inlineStr">
+      <c r="K113" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L113" s="7" t="inlineStr">
+      <c r="L113" s="5" t="inlineStr">
         <is>
           <t>切换到「紫外线」图谱模式成功</t>
         </is>
       </c>
-      <c r="M113" s="7" t="inlineStr">
+      <c r="M113" s="5" t="inlineStr">
         <is>
           <t>紫外线</t>
         </is>
       </c>
-      <c r="N113" s="7" t="inlineStr">
+      <c r="N113" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O113" s="7" t="n">
+      <c r="O113" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P113" s="7" t="inlineStr">
+      <c r="P113" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R113" s="7" t="inlineStr">
+      <c r="R113" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -11396,38 +11334,38 @@
         </is>
       </c>
     </row>
-    <row r="114" customFormat="1" s="7">
-      <c r="A114" s="7" t="inlineStr">
+    <row r="114" customFormat="1" s="5">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-025</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C114" s="7" t="inlineStr">
+      <c r="C114" s="5" t="inlineStr">
         <is>
           <t>光影增强-紫外线斑模式</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-紫外线斑模式</t>
         </is>
       </c>
-      <c r="E114" s="7" t="inlineStr">
+      <c r="E114" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F114" s="7" t="inlineStr">
+      <c r="F114" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G114" s="7" t="inlineStr">
+      <c r="G114" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -11436,50 +11374,50 @@
 5.光影增强-紫外线斑模式</t>
         </is>
       </c>
-      <c r="H114" s="7" t="inlineStr">
+      <c r="H114" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=紫外线斑</t>
         </is>
       </c>
-      <c r="I114" s="7" t="inlineStr">
+      <c r="I114" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J114" s="7" t="inlineStr">
+      <c r="J114" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K114" s="7" t="inlineStr">
+      <c r="K114" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L114" s="7" t="inlineStr">
+      <c r="L114" s="5" t="inlineStr">
         <is>
           <t>切换到「紫外线斑」图谱模式成功</t>
         </is>
       </c>
-      <c r="M114" s="7" t="inlineStr">
+      <c r="M114" s="5" t="inlineStr">
         <is>
           <t>紫外线斑</t>
         </is>
       </c>
-      <c r="N114" s="7" t="inlineStr">
+      <c r="N114" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O114" s="7" t="n">
+      <c r="O114" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P114" s="7" t="inlineStr">
+      <c r="P114" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R114" s="7" t="inlineStr">
+      <c r="R114" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -11490,38 +11428,38 @@
         </is>
       </c>
     </row>
-    <row r="115" customFormat="1" s="7">
-      <c r="A115" s="7" t="inlineStr">
+    <row r="115" customFormat="1" s="5">
+      <c r="A115" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-026</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="B115" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C115" s="7" t="inlineStr">
+      <c r="C115" s="5" t="inlineStr">
         <is>
           <t>光影增强-平行偏振模式</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr">
+      <c r="D115" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-平行偏振模式</t>
         </is>
       </c>
-      <c r="E115" s="7" t="inlineStr">
+      <c r="E115" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F115" s="7" t="inlineStr">
+      <c r="F115" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G115" s="7" t="inlineStr">
+      <c r="G115" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -11530,50 +11468,50 @@
 5.光影增强-平行偏振模式</t>
         </is>
       </c>
-      <c r="H115" s="7" t="inlineStr">
+      <c r="H115" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=平行偏振</t>
         </is>
       </c>
-      <c r="I115" s="7" t="inlineStr">
+      <c r="I115" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J115" s="7" t="inlineStr">
+      <c r="J115" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K115" s="7" t="inlineStr">
+      <c r="K115" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L115" s="7" t="inlineStr">
+      <c r="L115" s="5" t="inlineStr">
         <is>
           <t>切换到「平行偏振」图谱模式成功</t>
         </is>
       </c>
-      <c r="M115" s="7" t="inlineStr">
+      <c r="M115" s="5" t="inlineStr">
         <is>
           <t>平行偏振</t>
         </is>
       </c>
-      <c r="N115" s="7" t="inlineStr">
+      <c r="N115" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O115" s="7" t="n">
+      <c r="O115" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P115" s="7" t="inlineStr">
+      <c r="P115" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R115" s="7" t="inlineStr">
+      <c r="R115" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -11584,38 +11522,38 @@
         </is>
       </c>
     </row>
-    <row r="116" customFormat="1" s="7">
-      <c r="A116" s="7" t="inlineStr">
+    <row r="116" customFormat="1" s="5">
+      <c r="A116" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-027</t>
         </is>
       </c>
-      <c r="B116" s="7" t="inlineStr">
+      <c r="B116" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C116" s="7" t="inlineStr">
+      <c r="C116" s="5" t="inlineStr">
         <is>
           <t>光影增强-交叉偏振模式</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-交叉偏振模式</t>
         </is>
       </c>
-      <c r="E116" s="7" t="inlineStr">
+      <c r="E116" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F116" s="7" t="inlineStr">
+      <c r="F116" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G116" s="7" t="inlineStr">
+      <c r="G116" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -11624,50 +11562,50 @@
 5.光影增强-交叉偏振模式</t>
         </is>
       </c>
-      <c r="H116" s="7" t="inlineStr">
+      <c r="H116" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=交叉偏振</t>
         </is>
       </c>
-      <c r="I116" s="7" t="inlineStr">
+      <c r="I116" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J116" s="7" t="inlineStr">
+      <c r="J116" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K116" s="7" t="inlineStr">
+      <c r="K116" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L116" s="7" t="inlineStr">
+      <c r="L116" s="5" t="inlineStr">
         <is>
           <t>切换到「交叉偏振」图谱模式成功</t>
         </is>
       </c>
-      <c r="M116" s="7" t="inlineStr">
+      <c r="M116" s="5" t="inlineStr">
         <is>
           <t>交叉偏振</t>
         </is>
       </c>
-      <c r="N116" s="7" t="inlineStr">
+      <c r="N116" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O116" s="7" t="n">
+      <c r="O116" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P116" s="7" t="inlineStr">
+      <c r="P116" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R116" s="7" t="inlineStr">
+      <c r="R116" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -11678,38 +11616,38 @@
         </is>
       </c>
     </row>
-    <row r="117" customFormat="1" s="7">
-      <c r="A117" s="7" t="inlineStr">
+    <row r="117" customFormat="1" s="5">
+      <c r="A117" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-028</t>
         </is>
       </c>
-      <c r="B117" s="7" t="inlineStr">
+      <c r="B117" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr">
+      <c r="C117" s="5" t="inlineStr">
         <is>
           <t>光影增强-灰度模式</t>
         </is>
       </c>
-      <c r="D117" s="7" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>验证光影增强-灰度模式</t>
         </is>
       </c>
-      <c r="E117" s="7" t="inlineStr">
+      <c r="E117" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F117" s="7" t="inlineStr">
+      <c r="F117" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G117" s="7" t="inlineStr">
+      <c r="G117" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -11718,50 +11656,50 @@
 5.光影增强-灰度模式</t>
         </is>
       </c>
-      <c r="H117" s="7" t="inlineStr">
+      <c r="H117" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=灰度</t>
         </is>
       </c>
-      <c r="I117" s="7" t="inlineStr">
+      <c r="I117" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J117" s="7" t="inlineStr">
+      <c r="J117" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K117" s="7" t="inlineStr">
+      <c r="K117" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L117" s="7" t="inlineStr">
+      <c r="L117" s="5" t="inlineStr">
         <is>
           <t>切换到「灰度」图谱模式成功</t>
         </is>
       </c>
-      <c r="M117" s="7" t="inlineStr">
+      <c r="M117" s="5" t="inlineStr">
         <is>
           <t>灰度</t>
         </is>
       </c>
-      <c r="N117" s="7" t="inlineStr">
+      <c r="N117" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O117" s="7" t="n">
+      <c r="O117" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P117" s="7" t="inlineStr">
+      <c r="P117" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R117" s="7" t="inlineStr">
+      <c r="R117" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -11772,38 +11710,38 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="67.5" customFormat="1" customHeight="1" s="7">
-      <c r="A118" s="7" t="inlineStr">
+    <row r="118" ht="67.5" customFormat="1" customHeight="1" s="5">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-029</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B118" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C118" s="7" t="inlineStr">
+      <c r="C118" s="5" t="inlineStr">
         <is>
           <t>模式对比-无对比</t>
         </is>
       </c>
-      <c r="D118" s="7" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>验证模式对比-无对比</t>
         </is>
       </c>
-      <c r="E118" s="7" t="inlineStr">
+      <c r="E118" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F118" s="7" t="inlineStr">
+      <c r="F118" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G118" s="22" t="inlineStr">
+      <c r="G118" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -11812,50 +11750,50 @@
 5.模式对比-无对比</t>
         </is>
       </c>
-      <c r="H118" s="7" t="inlineStr">
+      <c r="H118" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=无对比</t>
         </is>
       </c>
-      <c r="I118" s="7" t="inlineStr">
+      <c r="I118" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J118" s="7" t="inlineStr">
+      <c r="J118" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K118" s="7" t="inlineStr">
+      <c r="K118" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L118" s="7" t="inlineStr">
+      <c r="L118" s="5" t="inlineStr">
         <is>
           <t>默认无对比模式正常</t>
         </is>
       </c>
-      <c r="M118" s="7" t="inlineStr">
+      <c r="M118" s="5" t="inlineStr">
         <is>
           <t>无对比</t>
         </is>
       </c>
-      <c r="N118" s="7" t="inlineStr">
+      <c r="N118" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O118" s="7" t="n">
+      <c r="O118" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P118" s="7" t="inlineStr">
+      <c r="P118" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R118" s="7" t="inlineStr">
+      <c r="R118" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -11866,38 +11804,38 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="67.5" customFormat="1" customHeight="1" s="7">
-      <c r="A119" s="7" t="inlineStr">
+    <row r="119" ht="67.5" customFormat="1" customHeight="1" s="5">
+      <c r="A119" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-030</t>
         </is>
       </c>
-      <c r="B119" s="7" t="inlineStr">
+      <c r="B119" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C119" s="7" t="inlineStr">
+      <c r="C119" s="5" t="inlineStr">
         <is>
           <t>AI综合分析-评分显示</t>
         </is>
       </c>
-      <c r="D119" s="7" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>验证AI综合分析-评分显示</t>
         </is>
       </c>
-      <c r="E119" s="7" t="inlineStr">
+      <c r="E119" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F119" s="7" t="inlineStr">
+      <c r="F119" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G119" s="22" t="inlineStr">
+      <c r="G119" s="13" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -11906,50 +11844,50 @@
 5.AI综合分析-评分显示</t>
         </is>
       </c>
-      <c r="H119" s="7" t="inlineStr">
+      <c r="H119" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=AI综合分析</t>
         </is>
       </c>
-      <c r="I119" s="7" t="inlineStr">
+      <c r="I119" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J119" s="7" t="inlineStr">
+      <c r="J119" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K119" s="7" t="inlineStr">
+      <c r="K119" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L119" s="7" t="inlineStr">
+      <c r="L119" s="5" t="inlineStr">
         <is>
           <t>AI综合分析评分（炎敏/肤色/色素/亮度/红区）正常显示</t>
         </is>
       </c>
-      <c r="M119" s="7" t="inlineStr">
+      <c r="M119" s="5" t="inlineStr">
         <is>
           <t>炎敏</t>
         </is>
       </c>
-      <c r="N119" s="7" t="inlineStr">
+      <c r="N119" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O119" s="7" t="n">
+      <c r="O119" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P119" s="7" t="inlineStr">
+      <c r="P119" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R119" s="7" t="inlineStr">
+      <c r="R119" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -11960,38 +11898,38 @@
         </is>
       </c>
     </row>
-    <row r="120" customFormat="1" s="7">
-      <c r="A120" s="7" t="inlineStr">
+    <row r="120" customFormat="1" s="5">
+      <c r="A120" s="5" t="inlineStr">
         <is>
           <t>TC-IMAGE-031</t>
         </is>
       </c>
-      <c r="B120" s="7" t="inlineStr">
+      <c r="B120" s="5" t="inlineStr">
         <is>
           <t>影像阅览</t>
         </is>
       </c>
-      <c r="C120" s="7" t="inlineStr">
+      <c r="C120" s="5" t="inlineStr">
         <is>
           <t>AI综合分析-图谱说明</t>
         </is>
       </c>
-      <c r="D120" s="7" t="inlineStr">
+      <c r="D120" s="5" t="inlineStr">
         <is>
           <t>验证AI综合分析-图谱说明</t>
         </is>
       </c>
-      <c r="E120" s="7" t="inlineStr">
+      <c r="E120" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F120" s="7" t="inlineStr">
+      <c r="F120" s="5" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="G120" s="7" t="inlineStr">
+      <c r="G120" s="5" t="inlineStr">
         <is>
           <t>1.进入顾客列表
 2.搜索「咨询单特定」
@@ -12000,50 +11938,50 @@
 5.AI综合分析-图谱说明</t>
         </is>
       </c>
-      <c r="H120" s="7" t="inlineStr">
+      <c r="H120" s="5" t="inlineStr">
         <is>
           <t>div:text-is('顾客档案'), 3, input[placeholder='请输入关键字'], input[placeholder='请输入关键字'], button:has-text('搜 索'), 3, a:has-text('详情'), a:has-text('详情'), 3, [data-layout="column"][data-layout-align="center center"], [data-layout="column"][data-layout-align="center center"], 15, text=图谱说明</t>
         </is>
       </c>
-      <c r="I120" s="7" t="inlineStr">
+      <c r="I120" s="5" t="inlineStr">
         <is>
           <t>click, wait, verify, input, click, wait, verify, click, wait, verify, click, wait, click</t>
         </is>
       </c>
-      <c r="J120" s="7" t="inlineStr">
+      <c r="J120" s="5" t="inlineStr">
         <is>
           <t>咨询单特定</t>
         </is>
       </c>
-      <c r="K120" s="7" t="inlineStr">
+      <c r="K120" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L120" s="7" t="inlineStr">
+      <c r="L120" s="5" t="inlineStr">
         <is>
           <t>图谱说明面板正常打开</t>
         </is>
       </c>
-      <c r="M120" s="7" t="inlineStr">
+      <c r="M120" s="5" t="inlineStr">
         <is>
           <t>图谱说明</t>
         </is>
       </c>
-      <c r="N120" s="7" t="inlineStr">
+      <c r="N120" s="5" t="inlineStr">
         <is>
           <t>text_visible</t>
         </is>
       </c>
-      <c r="O120" s="7" t="n">
+      <c r="O120" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="P120" s="7" t="inlineStr">
+      <c r="P120" s="5" t="inlineStr">
         <is>
           <t>需要「咨询单特定」测试用户且有历史影像</t>
         </is>
       </c>
-      <c r="R120" s="7" t="inlineStr">
+      <c r="R120" s="5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -12055,7 +11993,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="14" t="inlineStr">
         <is>
           <t>TC-IMAGE-032</t>
         </is>
@@ -12130,7 +12068,7 @@
         </is>
       </c>
       <c r="O121" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
@@ -12229,7 +12167,7 @@
         </is>
       </c>
       <c r="O122" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -12328,7 +12266,7 @@
         </is>
       </c>
       <c r="O123" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -12368,10 +12306,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="15" customWidth="1" style="14" min="1" max="1"/>
-    <col width="40" customWidth="1" style="14" min="2" max="3"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12659,13 +12597,13 @@
       </c>
       <c r="C17" s="2" t="n"/>
     </row>
-    <row r="18" ht="34" customHeight="1" s="14">
+    <row r="18" ht="34" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
           <t>执行分组</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>并发分组：A/B；共享数据用 SERIAL；AUTO 或空值按模块自动分配</t>
         </is>
@@ -12688,11 +12626,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="18" customWidth="1" style="14" min="1" max="1"/>
-    <col width="30" customWidth="1" style="14" min="2" max="2"/>
-    <col width="50" customWidth="1" style="14" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12996,11 +12934,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="15" customWidth="1" style="14" min="1" max="1"/>
-    <col width="20" customWidth="1" style="14" min="2" max="2"/>
-    <col width="50" customWidth="1" style="14" min="3" max="3"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
